--- a/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
+++ b/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one down\普物實驗\6 密立根油滴實驗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eric Wang\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26583B62-E750-48F9-A927-6D5734E4C56E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8C3506-A3B8-4470-96FD-F54C4BDA2F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
   </bookViews>
@@ -50,34 +50,6 @@
     <t>T(s)</t>
   </si>
   <si>
-    <r>
-      <t>V</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">1(m/s) </t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>U</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>0(V)</t>
-    </r>
-  </si>
-  <si>
     <t>Q(coulomb)</t>
   </si>
   <si>
@@ -89,12 +61,18 @@
   <si>
     <t>大於5.0E-19</t>
   </si>
+  <si>
+    <t xml:space="preserve">V1(m/s) </t>
+  </si>
+  <si>
+    <t>U0(V)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -119,22 +97,30 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="DFKai-SB"/>
+      <color theme="1"/>
+      <name val="標楷體"/>
       <family val="4"/>
       <charset val="136"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="11"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
+      <name val="標楷體"/>
+      <family val="4"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="3">
@@ -180,11 +166,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -193,11 +176,23 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -536,23 +531,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3419739-BEEB-4B53-8EC5-6DC56A0166CA}">
-  <dimension ref="A1:N102"/>
+  <dimension ref="B2:N102"/>
   <sheetFormatPr defaultRowHeight="17"/>
   <cols>
     <col min="2" max="2" width="11.81640625" customWidth="1"/>
+    <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-    </row>
-    <row r="2" spans="1:14">
-      <c r="A2" s="1"/>
+    <row r="2" spans="2:14">
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
@@ -566,25 +556,24 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="7"/>
+      <c r="L2" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="M2" s="8"/>
+      <c r="N2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="4"/>
-      <c r="L2" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="M2" s="4"/>
-      <c r="N2" s="2" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" s="1"/>
+    </row>
+    <row r="3" spans="2:14">
       <c r="B3" s="2">
         <v>1</v>
       </c>
@@ -594,25 +583,30 @@
       <c r="D3" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E3" s="5"/>
-      <c r="F3" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="L3" s="6">
+      <c r="E3" s="4">
+        <v>22.8</v>
+      </c>
+      <c r="F3" s="2">
+        <f>D3/E3</f>
+        <v>1.6754385964912282E-5</v>
+      </c>
+      <c r="G3" s="5">
+        <v>72.3</v>
+      </c>
+      <c r="H3" s="7">
+        <f>1.945*10^-10*F3^1.5/G3</f>
+        <v>1.8449053158903017E-19</v>
+      </c>
+      <c r="I3" s="7"/>
+      <c r="L3" s="9">
         <v>9.9999999999999995E-21</v>
       </c>
-      <c r="M3" s="6"/>
-      <c r="N3" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
-      <c r="A4" s="1"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:14">
       <c r="B4" s="2">
         <v>2</v>
       </c>
@@ -622,25 +616,30 @@
       <c r="D4" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="L4" s="6">
+      <c r="E4" s="4">
+        <v>7.32</v>
+      </c>
+      <c r="F4" s="2">
+        <f t="shared" ref="F4:F67" si="0">D4/E4</f>
+        <v>5.2185792349726774E-5</v>
+      </c>
+      <c r="G4" s="5">
+        <v>168.6</v>
+      </c>
+      <c r="H4" s="7">
+        <f t="shared" ref="H4:H67" si="1">1.945*10^-10*F4^1.5/G4</f>
+        <v>4.3490105195356502E-19</v>
+      </c>
+      <c r="I4" s="7"/>
+      <c r="L4" s="9">
         <v>1.9999999999999999E-20</v>
       </c>
-      <c r="M4" s="6"/>
-      <c r="N4" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
-      <c r="A5" s="1"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="2:14">
       <c r="B5" s="2">
         <v>3</v>
       </c>
@@ -650,25 +649,30 @@
       <c r="D5" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G5" s="5"/>
-      <c r="H5" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="L5" s="6">
+      <c r="E5" s="4">
+        <v>14.47</v>
+      </c>
+      <c r="F5" s="2">
+        <f t="shared" si="0"/>
+        <v>2.6399447131997236E-5</v>
+      </c>
+      <c r="G5" s="5">
+        <v>62.6</v>
+      </c>
+      <c r="H5" s="7">
+        <f t="shared" si="1"/>
+        <v>4.2144171456566916E-19</v>
+      </c>
+      <c r="I5" s="7"/>
+      <c r="L5" s="9">
         <v>3.0000000000000003E-20</v>
       </c>
-      <c r="M5" s="6"/>
-      <c r="N5" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" s="1"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="2:14">
       <c r="B6" s="2">
         <v>4</v>
       </c>
@@ -678,25 +682,30 @@
       <c r="D6" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E6" s="5"/>
-      <c r="F6" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="L6" s="6">
+      <c r="E6" s="4">
+        <v>14.98</v>
+      </c>
+      <c r="F6" s="2">
+        <f t="shared" si="0"/>
+        <v>2.5500667556742323E-5</v>
+      </c>
+      <c r="G6" s="5">
+        <v>68.599999999999994</v>
+      </c>
+      <c r="H6" s="7">
+        <f t="shared" si="1"/>
+        <v>3.6510923183134183E-19</v>
+      </c>
+      <c r="I6" s="7"/>
+      <c r="L6" s="9">
         <v>3.9999999999999998E-20</v>
       </c>
-      <c r="M6" s="6"/>
-      <c r="N6" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="1"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14">
       <c r="B7" s="2">
         <v>5</v>
       </c>
@@ -706,25 +715,30 @@
       <c r="D7" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G7" s="5"/>
-      <c r="H7" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="L7" s="6">
+      <c r="E7" s="4">
+        <v>3.72</v>
+      </c>
+      <c r="F7" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0268817204301075E-4</v>
+      </c>
+      <c r="G7" s="5">
+        <v>284.2</v>
+      </c>
+      <c r="H7" s="7">
+        <f t="shared" si="1"/>
+        <v>7.1215768734266231E-19</v>
+      </c>
+      <c r="I7" s="7"/>
+      <c r="L7" s="9">
         <v>4.9999999999999999E-20</v>
       </c>
-      <c r="M7" s="6"/>
-      <c r="N7" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="1"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14">
       <c r="B8" s="2">
         <v>6</v>
       </c>
@@ -734,25 +748,30 @@
       <c r="D8" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E8" s="5"/>
-      <c r="F8" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G8" s="5"/>
-      <c r="H8" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I8" s="4"/>
-      <c r="L8" s="6">
+      <c r="E8" s="4">
+        <v>4.05</v>
+      </c>
+      <c r="F8" s="2">
+        <f t="shared" si="0"/>
+        <v>9.432098765432099E-5</v>
+      </c>
+      <c r="G8" s="5">
+        <v>351.7</v>
+      </c>
+      <c r="H8" s="7">
+        <f t="shared" si="1"/>
+        <v>5.0659365601111741E-19</v>
+      </c>
+      <c r="I8" s="7"/>
+      <c r="L8" s="9">
         <v>6.0000000000000006E-20</v>
       </c>
-      <c r="M8" s="6"/>
-      <c r="N8" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="1"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14">
       <c r="B9" s="2">
         <v>7</v>
       </c>
@@ -762,25 +781,30 @@
       <c r="D9" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E9" s="5"/>
-      <c r="F9" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G9" s="5"/>
-      <c r="H9" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I9" s="4"/>
-      <c r="L9" s="6">
+      <c r="E9" s="4">
+        <v>10.6</v>
+      </c>
+      <c r="F9" s="2">
+        <f t="shared" si="0"/>
+        <v>3.6037735849056609E-5</v>
+      </c>
+      <c r="G9" s="5">
+        <v>126</v>
+      </c>
+      <c r="H9" s="7">
+        <f t="shared" si="1"/>
+        <v>3.339529675490588E-19</v>
+      </c>
+      <c r="I9" s="7"/>
+      <c r="L9" s="9">
         <v>7.0000000000000001E-20</v>
       </c>
-      <c r="M9" s="6"/>
-      <c r="N9" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="1"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14">
       <c r="B10" s="2">
         <v>8</v>
       </c>
@@ -790,25 +814,30 @@
       <c r="D10" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E10" s="5"/>
-      <c r="F10" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I10" s="4"/>
-      <c r="L10" s="6">
+      <c r="E10" s="4">
+        <v>9.75</v>
+      </c>
+      <c r="F10" s="2">
+        <f t="shared" si="0"/>
+        <v>3.917948717948718E-5</v>
+      </c>
+      <c r="G10" s="5">
+        <v>120.1</v>
+      </c>
+      <c r="H10" s="7">
+        <f t="shared" si="1"/>
+        <v>3.971592840015501E-19</v>
+      </c>
+      <c r="I10" s="7"/>
+      <c r="L10" s="9">
         <v>7.9999999999999996E-20</v>
       </c>
-      <c r="M10" s="6"/>
-      <c r="N10" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="1"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14">
       <c r="B11" s="2">
         <v>9</v>
       </c>
@@ -818,25 +847,30 @@
       <c r="D11" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E11" s="5"/>
-      <c r="F11" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I11" s="4"/>
-      <c r="L11" s="6">
+      <c r="E11" s="4">
+        <v>8.11</v>
+      </c>
+      <c r="F11" s="2">
+        <f t="shared" si="0"/>
+        <v>4.710234278668311E-5</v>
+      </c>
+      <c r="G11" s="5">
+        <v>170.8</v>
+      </c>
+      <c r="H11" s="7">
+        <f t="shared" si="1"/>
+        <v>3.6812516124506652E-19</v>
+      </c>
+      <c r="I11" s="7"/>
+      <c r="L11" s="9">
         <v>9.0000000000000003E-20</v>
       </c>
-      <c r="M11" s="6"/>
-      <c r="N11" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="1"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14">
       <c r="B12" s="2">
         <v>10</v>
       </c>
@@ -846,25 +880,30 @@
       <c r="D12" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E12" s="5"/>
-      <c r="F12" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G12" s="5"/>
-      <c r="H12" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I12" s="4"/>
-      <c r="L12" s="6">
+      <c r="E12" s="4">
+        <v>22.15</v>
+      </c>
+      <c r="F12" s="2">
+        <f t="shared" si="0"/>
+        <v>1.7246049661399549E-5</v>
+      </c>
+      <c r="G12" s="5">
+        <v>88.4</v>
+      </c>
+      <c r="H12" s="7">
+        <f t="shared" si="1"/>
+        <v>1.5758025146171712E-19</v>
+      </c>
+      <c r="I12" s="7"/>
+      <c r="L12" s="9">
         <v>9.9999999999999998E-20</v>
       </c>
-      <c r="M12" s="6"/>
-      <c r="N12" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="1"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14">
       <c r="B13" s="2">
         <v>11</v>
       </c>
@@ -874,25 +913,30 @@
       <c r="D13" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E13" s="5"/>
-      <c r="F13" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G13" s="5"/>
-      <c r="H13" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I13" s="4"/>
-      <c r="L13" s="6">
+      <c r="E13" s="4">
+        <v>8.76</v>
+      </c>
+      <c r="F13" s="2">
+        <f t="shared" si="0"/>
+        <v>4.3607305936073063E-5</v>
+      </c>
+      <c r="G13" s="5">
+        <v>126.6</v>
+      </c>
+      <c r="H13" s="7">
+        <f t="shared" si="1"/>
+        <v>4.4240984732649361E-19</v>
+      </c>
+      <c r="I13" s="7"/>
+      <c r="L13" s="9">
         <v>1.0999999999999999E-19</v>
       </c>
-      <c r="M13" s="6"/>
-      <c r="N13" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="1"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14">
       <c r="B14" s="2">
         <v>12</v>
       </c>
@@ -902,25 +946,30 @@
       <c r="D14" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E14" s="5"/>
-      <c r="F14" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I14" s="4"/>
-      <c r="L14" s="6">
+      <c r="E14" s="4">
+        <v>9.11</v>
+      </c>
+      <c r="F14" s="2">
+        <f t="shared" si="0"/>
+        <v>4.1931942919868279E-5</v>
+      </c>
+      <c r="G14" s="5">
+        <v>128.4</v>
+      </c>
+      <c r="H14" s="7">
+        <f t="shared" si="1"/>
+        <v>4.1131264461271426E-19</v>
+      </c>
+      <c r="I14" s="7"/>
+      <c r="L14" s="9">
         <v>1.2000000000000001E-19</v>
       </c>
-      <c r="M14" s="6"/>
-      <c r="N14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="1"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14">
       <c r="B15" s="2">
         <v>13</v>
       </c>
@@ -930,25 +979,30 @@
       <c r="D15" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E15" s="5"/>
-      <c r="F15" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G15" s="5"/>
-      <c r="H15" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I15" s="4"/>
-      <c r="L15" s="6">
+      <c r="E15" s="4">
+        <v>23.48</v>
+      </c>
+      <c r="F15" s="2">
+        <f t="shared" si="0"/>
+        <v>1.6269165247018739E-5</v>
+      </c>
+      <c r="G15" s="5">
+        <v>41.9</v>
+      </c>
+      <c r="H15" s="7">
+        <f t="shared" si="1"/>
+        <v>3.0461654514538201E-19</v>
+      </c>
+      <c r="I15" s="7"/>
+      <c r="L15" s="9">
         <v>1.3000000000000001E-19</v>
       </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="1"/>
+      <c r="M15" s="9"/>
+      <c r="N15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14">
       <c r="B16" s="2">
         <v>14</v>
       </c>
@@ -958,25 +1012,30 @@
       <c r="D16" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E16" s="5"/>
-      <c r="F16" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G16" s="5"/>
-      <c r="H16" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I16" s="4"/>
-      <c r="L16" s="6">
+      <c r="E16" s="4">
+        <v>12.36</v>
+      </c>
+      <c r="F16" s="2">
+        <f t="shared" si="0"/>
+        <v>3.0906148867313921E-5</v>
+      </c>
+      <c r="G16" s="5">
+        <v>83.9</v>
+      </c>
+      <c r="H16" s="7">
+        <f t="shared" si="1"/>
+        <v>3.9831346048250973E-19</v>
+      </c>
+      <c r="I16" s="7"/>
+      <c r="L16" s="9">
         <v>1.4E-19</v>
       </c>
-      <c r="M16" s="6"/>
-      <c r="N16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="1"/>
+      <c r="M16" s="9"/>
+      <c r="N16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
       <c r="B17" s="2">
         <v>15</v>
       </c>
@@ -986,25 +1045,30 @@
       <c r="D17" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E17" s="5"/>
-      <c r="F17" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G17" s="5"/>
-      <c r="H17" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I17" s="4"/>
-      <c r="L17" s="6">
+      <c r="E17" s="4">
+        <v>13.6</v>
+      </c>
+      <c r="F17" s="2">
+        <f t="shared" si="0"/>
+        <v>2.8088235294117648E-5</v>
+      </c>
+      <c r="G17" s="5">
+        <v>173.6</v>
+      </c>
+      <c r="H17" s="7">
+        <f t="shared" si="1"/>
+        <v>1.6678483768588152E-19</v>
+      </c>
+      <c r="I17" s="7"/>
+      <c r="L17" s="9">
         <v>1.5E-19</v>
       </c>
-      <c r="M17" s="6"/>
-      <c r="N17" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="1"/>
+      <c r="M17" s="9"/>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
       <c r="B18" s="2">
         <v>16</v>
       </c>
@@ -1014,25 +1078,30 @@
       <c r="D18" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E18" s="5"/>
-      <c r="F18" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I18" s="4"/>
-      <c r="L18" s="6">
+      <c r="E18" s="4">
+        <v>9.5299999999999994</v>
+      </c>
+      <c r="F18" s="2">
+        <f t="shared" si="0"/>
+        <v>4.008394543546695E-5</v>
+      </c>
+      <c r="G18" s="5">
+        <v>232.8</v>
+      </c>
+      <c r="H18" s="7">
+        <f t="shared" si="1"/>
+        <v>2.120275636869835E-19</v>
+      </c>
+      <c r="I18" s="7"/>
+      <c r="L18" s="9">
         <v>1.5999999999999999E-19</v>
       </c>
-      <c r="M18" s="6"/>
-      <c r="N18" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="1"/>
+      <c r="M18" s="9"/>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
       <c r="B19" s="2">
         <v>17</v>
       </c>
@@ -1042,24 +1111,30 @@
       <c r="D19" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E19" s="5"/>
-      <c r="F19" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G19" s="5"/>
-      <c r="H19" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I19" s="4"/>
-      <c r="L19" s="6">
+      <c r="E19" s="4">
+        <v>17.25</v>
+      </c>
+      <c r="F19" s="2">
+        <f t="shared" si="0"/>
+        <v>2.2144927536231886E-5</v>
+      </c>
+      <c r="G19" s="5">
+        <v>115.9</v>
+      </c>
+      <c r="H19" s="7">
+        <f t="shared" si="1"/>
+        <v>1.7488298802142485E-19</v>
+      </c>
+      <c r="I19" s="7"/>
+      <c r="L19" s="9">
         <v>1.7000000000000001E-19</v>
       </c>
-      <c r="M19" s="6"/>
-      <c r="N19" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="M19" s="9"/>
+      <c r="N19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
       <c r="B20" s="2">
         <v>18</v>
       </c>
@@ -1069,24 +1144,30 @@
       <c r="D20" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E20" s="5"/>
-      <c r="F20" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G20" s="5"/>
-      <c r="H20" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I20" s="4"/>
-      <c r="L20" s="6">
+      <c r="E20" s="4">
+        <v>19.329999999999998</v>
+      </c>
+      <c r="F20" s="2">
+        <f t="shared" si="0"/>
+        <v>1.9762027935851012E-5</v>
+      </c>
+      <c r="G20" s="5">
+        <v>69.599999999999994</v>
+      </c>
+      <c r="H20" s="7">
+        <f t="shared" si="1"/>
+        <v>2.455034668682092E-19</v>
+      </c>
+      <c r="I20" s="7"/>
+      <c r="L20" s="9">
         <v>1.8000000000000001E-19</v>
       </c>
-      <c r="M20" s="6"/>
-      <c r="N20" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+      <c r="M20" s="9"/>
+      <c r="N20" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
       <c r="B21" s="2">
         <v>19</v>
       </c>
@@ -1096,24 +1177,30 @@
       <c r="D21" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E21" s="5"/>
-      <c r="F21" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" s="5"/>
-      <c r="H21" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I21" s="4"/>
-      <c r="L21" s="6">
+      <c r="E21" s="4">
+        <v>12.57</v>
+      </c>
+      <c r="F21" s="2">
+        <f t="shared" si="0"/>
+        <v>3.0389817024661894E-5</v>
+      </c>
+      <c r="G21" s="5">
+        <v>211.8</v>
+      </c>
+      <c r="H21" s="7">
+        <f t="shared" si="1"/>
+        <v>1.5384584720296341E-19</v>
+      </c>
+      <c r="I21" s="7"/>
+      <c r="L21" s="9">
         <v>1.9E-19</v>
       </c>
-      <c r="M21" s="6"/>
-      <c r="N21" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+      <c r="M21" s="9"/>
+      <c r="N21" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
       <c r="B22" s="2">
         <v>20</v>
       </c>
@@ -1123,24 +1210,30 @@
       <c r="D22" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E22" s="5"/>
-      <c r="F22" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I22" s="4"/>
-      <c r="L22" s="6">
+      <c r="E22" s="4">
+        <v>4.07</v>
+      </c>
+      <c r="F22" s="2">
+        <f t="shared" si="0"/>
+        <v>9.385749385749386E-5</v>
+      </c>
+      <c r="G22" s="5">
+        <v>225.3</v>
+      </c>
+      <c r="H22" s="7">
+        <f t="shared" si="1"/>
+        <v>7.8498587920631624E-19</v>
+      </c>
+      <c r="I22" s="7"/>
+      <c r="L22" s="9">
         <v>2E-19</v>
       </c>
-      <c r="M22" s="6"/>
-      <c r="N22" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+      <c r="M22" s="9"/>
+      <c r="N22" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
       <c r="B23" s="2">
         <v>21</v>
       </c>
@@ -1150,24 +1243,30 @@
       <c r="D23" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E23" s="5"/>
-      <c r="F23" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G23" s="5"/>
-      <c r="H23" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I23" s="4"/>
-      <c r="L23" s="6">
+      <c r="E23" s="4">
+        <v>8.24</v>
+      </c>
+      <c r="F23" s="2">
+        <f t="shared" si="0"/>
+        <v>4.6359223300970875E-5</v>
+      </c>
+      <c r="G23" s="5">
+        <v>42.2</v>
+      </c>
+      <c r="H23" s="7">
+        <f t="shared" si="1"/>
+        <v>1.4548270972574926E-18</v>
+      </c>
+      <c r="I23" s="7"/>
+      <c r="L23" s="9">
         <v>2.0999999999999999E-19</v>
       </c>
-      <c r="M23" s="6"/>
-      <c r="N23" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+      <c r="M23" s="9"/>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
       <c r="B24" s="2">
         <v>22</v>
       </c>
@@ -1177,24 +1276,30 @@
       <c r="D24" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E24" s="5"/>
-      <c r="F24" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G24" s="5"/>
-      <c r="H24" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I24" s="4"/>
-      <c r="L24" s="6">
+      <c r="E24" s="4">
+        <v>20.83</v>
+      </c>
+      <c r="F24" s="2">
+        <f t="shared" si="0"/>
+        <v>1.8338934229476717E-5</v>
+      </c>
+      <c r="G24" s="5">
+        <v>92.9</v>
+      </c>
+      <c r="H24" s="7">
+        <f t="shared" si="1"/>
+        <v>1.6442393256488777E-19</v>
+      </c>
+      <c r="I24" s="7"/>
+      <c r="L24" s="9">
         <v>2.1999999999999998E-19</v>
       </c>
-      <c r="M24" s="6"/>
-      <c r="N24" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+      <c r="M24" s="9"/>
+      <c r="N24" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
       <c r="B25" s="2">
         <v>23</v>
       </c>
@@ -1204,24 +1309,30 @@
       <c r="D25" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E25" s="5"/>
-      <c r="F25" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G25" s="5"/>
-      <c r="H25" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I25" s="4"/>
-      <c r="L25" s="6">
+      <c r="E25" s="4">
+        <v>24.08</v>
+      </c>
+      <c r="F25" s="2">
+        <f t="shared" si="0"/>
+        <v>1.5863787375415285E-5</v>
+      </c>
+      <c r="G25" s="5">
+        <v>72.900000000000006</v>
+      </c>
+      <c r="H25" s="7">
+        <f t="shared" si="1"/>
+        <v>1.6857858253870438E-19</v>
+      </c>
+      <c r="I25" s="7"/>
+      <c r="L25" s="9">
         <v>2.2999999999999998E-19</v>
       </c>
-      <c r="M25" s="6"/>
-      <c r="N25" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+      <c r="M25" s="9"/>
+      <c r="N25" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
       <c r="B26" s="2">
         <v>24</v>
       </c>
@@ -1231,24 +1342,30 @@
       <c r="D26" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E26" s="5"/>
-      <c r="F26" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G26" s="5"/>
-      <c r="H26" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I26" s="4"/>
-      <c r="L26" s="6">
+      <c r="E26" s="4">
+        <v>21.72</v>
+      </c>
+      <c r="F26" s="2">
+        <f t="shared" si="0"/>
+        <v>1.7587476979742175E-5</v>
+      </c>
+      <c r="G26" s="5">
+        <v>288.10000000000002</v>
+      </c>
+      <c r="H26" s="7">
+        <f t="shared" si="1"/>
+        <v>4.9794532621128721E-20</v>
+      </c>
+      <c r="I26" s="7"/>
+      <c r="L26" s="9">
         <v>2.4000000000000002E-19</v>
       </c>
-      <c r="M26" s="6"/>
-      <c r="N26" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+      <c r="M26" s="9"/>
+      <c r="N26" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
       <c r="B27" s="2">
         <v>25</v>
       </c>
@@ -1258,24 +1375,30 @@
       <c r="D27" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E27" s="5"/>
-      <c r="F27" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G27" s="5"/>
-      <c r="H27" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I27" s="4"/>
-      <c r="L27" s="6">
+      <c r="E27" s="4">
+        <v>15.03</v>
+      </c>
+      <c r="F27" s="2">
+        <f t="shared" si="0"/>
+        <v>2.5415834996673323E-5</v>
+      </c>
+      <c r="G27" s="5">
+        <v>227.7</v>
+      </c>
+      <c r="H27" s="7">
+        <f t="shared" si="1"/>
+        <v>1.0944934037775462E-19</v>
+      </c>
+      <c r="I27" s="7"/>
+      <c r="L27" s="9">
         <v>2.5000000000000002E-19</v>
       </c>
-      <c r="M27" s="6"/>
-      <c r="N27" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+      <c r="M27" s="9"/>
+      <c r="N27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
       <c r="B28" s="2">
         <v>26</v>
       </c>
@@ -1285,24 +1408,30 @@
       <c r="D28" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E28" s="5"/>
-      <c r="F28" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I28" s="4"/>
-      <c r="L28" s="6">
+      <c r="E28" s="4">
+        <v>21.33</v>
+      </c>
+      <c r="F28" s="2">
+        <f t="shared" si="0"/>
+        <v>1.7909048288795127E-5</v>
+      </c>
+      <c r="G28" s="5">
+        <v>236.3</v>
+      </c>
+      <c r="H28" s="7">
+        <f t="shared" si="1"/>
+        <v>6.2382768602547688E-20</v>
+      </c>
+      <c r="I28" s="7"/>
+      <c r="L28" s="9">
         <v>2.6000000000000001E-19</v>
       </c>
-      <c r="M28" s="6"/>
-      <c r="N28" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+      <c r="M28" s="9"/>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
       <c r="B29" s="2">
         <v>27</v>
       </c>
@@ -1312,24 +1441,30 @@
       <c r="D29" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E29" s="5"/>
-      <c r="F29" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G29" s="5"/>
-      <c r="H29" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I29" s="4"/>
-      <c r="L29" s="6">
+      <c r="E29" s="4">
+        <v>18.649999999999999</v>
+      </c>
+      <c r="F29" s="2">
+        <f t="shared" si="0"/>
+        <v>2.0482573726541557E-5</v>
+      </c>
+      <c r="G29" s="5">
+        <v>138.4</v>
+      </c>
+      <c r="H29" s="7">
+        <f t="shared" si="1"/>
+        <v>1.3027476717986452E-19</v>
+      </c>
+      <c r="I29" s="7"/>
+      <c r="L29" s="9">
         <v>2.7000000000000001E-19</v>
       </c>
-      <c r="M29" s="6"/>
-      <c r="N29" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+      <c r="M29" s="9"/>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
       <c r="B30" s="2">
         <v>28</v>
       </c>
@@ -1339,24 +1474,30 @@
       <c r="D30" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E30" s="5"/>
-      <c r="F30" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I30" s="4"/>
-      <c r="L30" s="6">
+      <c r="E30" s="4">
+        <v>5.22</v>
+      </c>
+      <c r="F30" s="2">
+        <f t="shared" si="0"/>
+        <v>7.3180076628352495E-5</v>
+      </c>
+      <c r="G30" s="5">
+        <v>134.5</v>
+      </c>
+      <c r="H30" s="7">
+        <f t="shared" si="1"/>
+        <v>9.05287682212827E-19</v>
+      </c>
+      <c r="I30" s="7"/>
+      <c r="L30" s="9">
         <v>2.8E-19</v>
       </c>
-      <c r="M30" s="6"/>
-      <c r="N30" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+      <c r="M30" s="9"/>
+      <c r="N30" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14">
       <c r="B31" s="2">
         <v>29</v>
       </c>
@@ -1366,24 +1507,30 @@
       <c r="D31" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E31" s="5"/>
-      <c r="F31" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G31" s="5"/>
-      <c r="H31" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I31" s="4"/>
-      <c r="L31" s="6">
+      <c r="E31" s="4">
+        <v>17.170000000000002</v>
+      </c>
+      <c r="F31" s="2">
+        <f t="shared" si="0"/>
+        <v>2.224810716365754E-5</v>
+      </c>
+      <c r="G31" s="5">
+        <v>111.2</v>
+      </c>
+      <c r="H31" s="7">
+        <f t="shared" si="1"/>
+        <v>1.835500131871435E-19</v>
+      </c>
+      <c r="I31" s="7"/>
+      <c r="L31" s="9">
         <v>2.9E-19</v>
       </c>
-      <c r="M31" s="6"/>
-      <c r="N31" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+      <c r="M31" s="9"/>
+      <c r="N31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
       <c r="B32" s="2">
         <v>30</v>
       </c>
@@ -1393,20 +1540,26 @@
       <c r="D32" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E32" s="5"/>
-      <c r="F32" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G32" s="5"/>
-      <c r="H32" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I32" s="4"/>
-      <c r="L32" s="6">
+      <c r="E32" s="4">
+        <v>9.24</v>
+      </c>
+      <c r="F32" s="2">
+        <f t="shared" si="0"/>
+        <v>4.1341991341991342E-5</v>
+      </c>
+      <c r="G32" s="5">
+        <v>247.1</v>
+      </c>
+      <c r="H32" s="7">
+        <f t="shared" si="1"/>
+        <v>2.0923481425821882E-19</v>
+      </c>
+      <c r="I32" s="7"/>
+      <c r="L32" s="9">
         <v>2.9999999999999999E-19</v>
       </c>
-      <c r="M32" s="6"/>
-      <c r="N32" s="2">
+      <c r="M32" s="9"/>
+      <c r="N32" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1420,20 +1573,26 @@
       <c r="D33" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E33" s="5"/>
-      <c r="F33" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G33" s="5"/>
-      <c r="H33" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I33" s="4"/>
-      <c r="L33" s="6">
+      <c r="E33" s="4">
+        <v>7.18</v>
+      </c>
+      <c r="F33" s="2">
+        <f t="shared" si="0"/>
+        <v>5.3203342618384407E-5</v>
+      </c>
+      <c r="G33" s="5">
+        <v>169</v>
+      </c>
+      <c r="H33" s="7">
+        <f t="shared" si="1"/>
+        <v>4.4662320015468356E-19</v>
+      </c>
+      <c r="I33" s="7"/>
+      <c r="L33" s="9">
         <v>3.0999999999999999E-19</v>
       </c>
-      <c r="M33" s="6"/>
-      <c r="N33" s="2">
+      <c r="M33" s="9"/>
+      <c r="N33" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1447,20 +1606,26 @@
       <c r="D34" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E34" s="5"/>
-      <c r="F34" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G34" s="5"/>
-      <c r="H34" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I34" s="4"/>
-      <c r="L34" s="6">
+      <c r="E34" s="4">
+        <v>24.77</v>
+      </c>
+      <c r="F34" s="2">
+        <f t="shared" si="0"/>
+        <v>1.5421881308033913E-5</v>
+      </c>
+      <c r="G34" s="5">
+        <v>272.8</v>
+      </c>
+      <c r="H34" s="7">
+        <f t="shared" si="1"/>
+        <v>4.3179864400352903E-20</v>
+      </c>
+      <c r="I34" s="7"/>
+      <c r="L34" s="9">
         <v>3.1999999999999998E-19</v>
       </c>
-      <c r="M34" s="6"/>
-      <c r="N34" s="2">
+      <c r="M34" s="9"/>
+      <c r="N34" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1474,20 +1639,26 @@
       <c r="D35" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E35" s="5"/>
-      <c r="F35" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G35" s="5"/>
-      <c r="H35" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I35" s="4"/>
-      <c r="L35" s="6">
+      <c r="E35" s="4">
+        <v>21.62</v>
+      </c>
+      <c r="F35" s="2">
+        <f t="shared" si="0"/>
+        <v>1.766882516188714E-5</v>
+      </c>
+      <c r="G35" s="5">
+        <v>50.9</v>
+      </c>
+      <c r="H35" s="7">
+        <f t="shared" si="1"/>
+        <v>2.8380061566768923E-19</v>
+      </c>
+      <c r="I35" s="7"/>
+      <c r="L35" s="9">
         <v>3.2999999999999998E-19</v>
       </c>
-      <c r="M35" s="6"/>
-      <c r="N35" s="2">
+      <c r="M35" s="9"/>
+      <c r="N35" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1501,20 +1672,26 @@
       <c r="D36" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E36" s="5"/>
-      <c r="F36" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G36" s="5"/>
-      <c r="H36" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I36" s="4"/>
-      <c r="L36" s="6">
+      <c r="E36" s="4">
+        <v>8.11</v>
+      </c>
+      <c r="F36" s="2">
+        <f t="shared" si="0"/>
+        <v>4.710234278668311E-5</v>
+      </c>
+      <c r="G36" s="5">
+        <v>170.8</v>
+      </c>
+      <c r="H36" s="7">
+        <f t="shared" si="1"/>
+        <v>3.6812516124506652E-19</v>
+      </c>
+      <c r="I36" s="7"/>
+      <c r="L36" s="9">
         <v>3.4000000000000002E-19</v>
       </c>
-      <c r="M36" s="6"/>
-      <c r="N36" s="2">
+      <c r="M36" s="9"/>
+      <c r="N36" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1528,20 +1705,26 @@
       <c r="D37" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E37" s="5"/>
-      <c r="F37" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G37" s="5"/>
-      <c r="H37" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I37" s="4"/>
-      <c r="L37" s="6">
+      <c r="E37" s="4">
+        <v>22.34</v>
+      </c>
+      <c r="F37" s="2">
+        <f t="shared" si="0"/>
+        <v>1.70993733213966E-5</v>
+      </c>
+      <c r="G37" s="5">
+        <v>174.5</v>
+      </c>
+      <c r="H37" s="7">
+        <f t="shared" si="1"/>
+        <v>7.8812384156677962E-20</v>
+      </c>
+      <c r="I37" s="7"/>
+      <c r="L37" s="9">
         <v>3.5000000000000002E-19</v>
       </c>
-      <c r="M37" s="6"/>
-      <c r="N37" s="2">
+      <c r="M37" s="9"/>
+      <c r="N37" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1555,20 +1738,26 @@
       <c r="D38" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E38" s="5"/>
-      <c r="F38" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G38" s="5"/>
-      <c r="H38" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I38" s="4"/>
-      <c r="L38" s="6">
+      <c r="E38" s="4">
+        <v>23.16</v>
+      </c>
+      <c r="F38" s="2">
+        <f t="shared" si="0"/>
+        <v>1.6493955094991366E-5</v>
+      </c>
+      <c r="G38" s="5">
+        <v>123.9</v>
+      </c>
+      <c r="H38" s="7">
+        <f t="shared" si="1"/>
+        <v>1.0515635189613713E-19</v>
+      </c>
+      <c r="I38" s="7"/>
+      <c r="L38" s="9">
         <v>3.6000000000000001E-19</v>
       </c>
-      <c r="M38" s="6"/>
-      <c r="N38" s="2">
+      <c r="M38" s="9"/>
+      <c r="N38" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1582,20 +1771,26 @@
       <c r="D39" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E39" s="5"/>
-      <c r="F39" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G39" s="5"/>
-      <c r="H39" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I39" s="4"/>
-      <c r="L39" s="6">
+      <c r="E39" s="4">
+        <v>15.57</v>
+      </c>
+      <c r="F39" s="2">
+        <f t="shared" si="0"/>
+        <v>2.4534360950545924E-5</v>
+      </c>
+      <c r="G39" s="5">
+        <v>345.3</v>
+      </c>
+      <c r="H39" s="7">
+        <f t="shared" si="1"/>
+        <v>6.8451844141021412E-20</v>
+      </c>
+      <c r="I39" s="7"/>
+      <c r="L39" s="9">
         <v>3.7000000000000001E-19</v>
       </c>
-      <c r="M39" s="6"/>
-      <c r="N39" s="2">
+      <c r="M39" s="9"/>
+      <c r="N39" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1609,20 +1804,26 @@
       <c r="D40" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E40" s="5"/>
-      <c r="F40" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G40" s="5"/>
-      <c r="H40" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I40" s="4"/>
-      <c r="L40" s="6">
+      <c r="E40" s="4">
+        <v>12.09</v>
+      </c>
+      <c r="F40" s="2">
+        <f t="shared" si="0"/>
+        <v>3.1596360628618697E-5</v>
+      </c>
+      <c r="G40" s="5">
+        <v>213.2</v>
+      </c>
+      <c r="H40" s="7">
+        <f t="shared" si="1"/>
+        <v>1.6202722663136051E-19</v>
+      </c>
+      <c r="I40" s="7"/>
+      <c r="L40" s="9">
         <v>3.8E-19</v>
       </c>
-      <c r="M40" s="6"/>
-      <c r="N40" s="2">
+      <c r="M40" s="9"/>
+      <c r="N40" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1636,20 +1837,26 @@
       <c r="D41" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E41" s="5"/>
-      <c r="F41" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G41" s="5"/>
-      <c r="H41" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I41" s="4"/>
-      <c r="L41" s="6">
+      <c r="E41" s="4">
+        <v>5.45</v>
+      </c>
+      <c r="F41" s="2">
+        <f t="shared" si="0"/>
+        <v>7.009174311926605E-5</v>
+      </c>
+      <c r="G41" s="5">
+        <v>253.3</v>
+      </c>
+      <c r="H41" s="7">
+        <f t="shared" si="1"/>
+        <v>4.5059327617437475E-19</v>
+      </c>
+      <c r="I41" s="7"/>
+      <c r="L41" s="9">
         <v>3.9E-19</v>
       </c>
-      <c r="M41" s="6"/>
-      <c r="N41" s="2">
+      <c r="M41" s="9"/>
+      <c r="N41" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1663,20 +1870,26 @@
       <c r="D42" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E42" s="5"/>
-      <c r="F42" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I42" s="4"/>
-      <c r="L42" s="6">
+      <c r="E42" s="4">
+        <v>20.53</v>
+      </c>
+      <c r="F42" s="2">
+        <f t="shared" si="0"/>
+        <v>1.8606916707257671E-5</v>
+      </c>
+      <c r="G42" s="5">
+        <v>169.8</v>
+      </c>
+      <c r="H42" s="7">
+        <f t="shared" si="1"/>
+        <v>9.193767993870622E-20</v>
+      </c>
+      <c r="I42" s="7"/>
+      <c r="L42" s="9">
         <v>3.9999999999999999E-19</v>
       </c>
-      <c r="M42" s="6"/>
-      <c r="N42" s="2">
+      <c r="M42" s="9"/>
+      <c r="N42" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1690,20 +1903,26 @@
       <c r="D43" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E43" s="5"/>
-      <c r="F43" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G43" s="5"/>
-      <c r="H43" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I43" s="4"/>
-      <c r="L43" s="6">
+      <c r="E43" s="4">
+        <v>24.92</v>
+      </c>
+      <c r="F43" s="2">
+        <f t="shared" si="0"/>
+        <v>1.5329052969502406E-5</v>
+      </c>
+      <c r="G43" s="5">
+        <v>332.7</v>
+      </c>
+      <c r="H43" s="7">
+        <f t="shared" si="1"/>
+        <v>3.5086479332700357E-20</v>
+      </c>
+      <c r="I43" s="7"/>
+      <c r="L43" s="9">
         <v>4.0999999999999999E-19</v>
       </c>
-      <c r="M43" s="6"/>
-      <c r="N43" s="2">
+      <c r="M43" s="9"/>
+      <c r="N43" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1717,20 +1936,26 @@
       <c r="D44" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E44" s="5"/>
-      <c r="F44" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G44" s="5"/>
-      <c r="H44" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I44" s="4"/>
-      <c r="L44" s="6">
+      <c r="E44" s="4">
+        <v>3.75</v>
+      </c>
+      <c r="F44" s="2">
+        <f t="shared" si="0"/>
+        <v>1.0186666666666667E-4</v>
+      </c>
+      <c r="G44" s="5">
+        <v>222.6</v>
+      </c>
+      <c r="H44" s="7">
+        <f t="shared" si="1"/>
+        <v>8.98343828154446E-19</v>
+      </c>
+      <c r="I44" s="7"/>
+      <c r="L44" s="9">
         <v>4.1999999999999998E-19</v>
       </c>
-      <c r="M44" s="6"/>
-      <c r="N44" s="2">
+      <c r="M44" s="9"/>
+      <c r="N44" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1744,20 +1969,26 @@
       <c r="D45" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E45" s="5"/>
-      <c r="F45" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G45" s="5"/>
-      <c r="H45" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I45" s="4"/>
-      <c r="L45" s="6">
+      <c r="E45" s="4">
+        <v>9.24</v>
+      </c>
+      <c r="F45" s="2">
+        <f t="shared" si="0"/>
+        <v>4.1341991341991342E-5</v>
+      </c>
+      <c r="G45" s="5">
+        <v>187.8</v>
+      </c>
+      <c r="H45" s="7">
+        <f t="shared" si="1"/>
+        <v>2.7530310225349235E-19</v>
+      </c>
+      <c r="I45" s="7"/>
+      <c r="L45" s="9">
         <v>4.3000000000000002E-19</v>
       </c>
-      <c r="M45" s="6"/>
-      <c r="N45" s="2">
+      <c r="M45" s="9"/>
+      <c r="N45" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1771,20 +2002,26 @@
       <c r="D46" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E46" s="5"/>
-      <c r="F46" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I46" s="4"/>
-      <c r="L46" s="6">
+      <c r="E46" s="4">
+        <v>13.26</v>
+      </c>
+      <c r="F46" s="2">
+        <f t="shared" si="0"/>
+        <v>2.8808446455505282E-5</v>
+      </c>
+      <c r="G46" s="5">
+        <v>129.6</v>
+      </c>
+      <c r="H46" s="7">
+        <f t="shared" si="1"/>
+        <v>2.3205683379361788E-19</v>
+      </c>
+      <c r="I46" s="7"/>
+      <c r="L46" s="9">
         <v>4.3999999999999997E-19</v>
       </c>
-      <c r="M46" s="6"/>
-      <c r="N46" s="2">
+      <c r="M46" s="9"/>
+      <c r="N46" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1798,20 +2035,26 @@
       <c r="D47" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E47" s="5"/>
-      <c r="F47" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G47" s="5"/>
-      <c r="H47" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I47" s="4"/>
-      <c r="L47" s="6">
+      <c r="E47" s="4">
+        <v>14.26</v>
+      </c>
+      <c r="F47" s="2">
+        <f t="shared" si="0"/>
+        <v>2.6788218793828895E-5</v>
+      </c>
+      <c r="G47" s="5">
+        <v>336</v>
+      </c>
+      <c r="H47" s="7">
+        <f t="shared" si="1"/>
+        <v>8.0259432458438495E-20</v>
+      </c>
+      <c r="I47" s="7"/>
+      <c r="L47" s="9">
         <v>4.5000000000000001E-19</v>
       </c>
-      <c r="M47" s="6"/>
-      <c r="N47" s="2">
+      <c r="M47" s="9"/>
+      <c r="N47" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1825,20 +2068,26 @@
       <c r="D48" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E48" s="5"/>
-      <c r="F48" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G48" s="5"/>
-      <c r="H48" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I48" s="4"/>
-      <c r="L48" s="6">
+      <c r="E48" s="4">
+        <v>9.92</v>
+      </c>
+      <c r="F48" s="2">
+        <f t="shared" si="0"/>
+        <v>3.8508064516129036E-5</v>
+      </c>
+      <c r="G48" s="5">
+        <v>92</v>
+      </c>
+      <c r="H48" s="7">
+        <f t="shared" si="1"/>
+        <v>5.0519531504841948E-19</v>
+      </c>
+      <c r="I48" s="7"/>
+      <c r="L48" s="9">
         <v>4.5999999999999996E-19</v>
       </c>
-      <c r="M48" s="6"/>
-      <c r="N48" s="2">
+      <c r="M48" s="9"/>
+      <c r="N48" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1852,20 +2101,26 @@
       <c r="D49" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E49" s="5"/>
-      <c r="F49" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G49" s="5"/>
-      <c r="H49" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I49" s="4"/>
-      <c r="L49" s="6">
+      <c r="E49" s="4">
+        <v>19.89</v>
+      </c>
+      <c r="F49" s="2">
+        <f t="shared" si="0"/>
+        <v>1.9205630970336851E-5</v>
+      </c>
+      <c r="G49" s="5">
+        <v>220.3</v>
+      </c>
+      <c r="H49" s="7">
+        <f t="shared" si="1"/>
+        <v>7.4310122663013932E-20</v>
+      </c>
+      <c r="I49" s="7"/>
+      <c r="L49" s="9">
         <v>4.7E-19</v>
       </c>
-      <c r="M49" s="6"/>
-      <c r="N49" s="2">
+      <c r="M49" s="9"/>
+      <c r="N49" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1879,20 +2134,26 @@
       <c r="D50" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E50" s="5"/>
-      <c r="F50" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I50" s="4"/>
-      <c r="L50" s="6">
+      <c r="E50" s="4">
+        <v>8.11</v>
+      </c>
+      <c r="F50" s="2">
+        <f t="shared" si="0"/>
+        <v>4.710234278668311E-5</v>
+      </c>
+      <c r="G50" s="6">
+        <v>170.8</v>
+      </c>
+      <c r="H50" s="7">
+        <f t="shared" si="1"/>
+        <v>3.6812516124506652E-19</v>
+      </c>
+      <c r="I50" s="7"/>
+      <c r="L50" s="9">
         <v>4.8000000000000005E-19</v>
       </c>
-      <c r="M50" s="6"/>
-      <c r="N50" s="2">
+      <c r="M50" s="9"/>
+      <c r="N50" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1906,20 +2167,26 @@
       <c r="D51" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E51" s="5"/>
-      <c r="F51" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G51" s="5"/>
-      <c r="H51" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I51" s="4"/>
-      <c r="L51" s="6">
+      <c r="E51" s="4">
+        <v>22.39</v>
+      </c>
+      <c r="F51" s="2">
+        <f t="shared" si="0"/>
+        <v>1.7061188030370701E-5</v>
+      </c>
+      <c r="G51" s="5">
+        <v>59.7</v>
+      </c>
+      <c r="H51" s="7">
+        <f t="shared" si="1"/>
+        <v>2.2959328319809843E-19</v>
+      </c>
+      <c r="I51" s="7"/>
+      <c r="L51" s="9">
         <v>4.8999999999999999E-19</v>
       </c>
-      <c r="M51" s="6"/>
-      <c r="N51" s="2">
+      <c r="M51" s="9"/>
+      <c r="N51" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1933,20 +2200,26 @@
       <c r="D52" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E52" s="5"/>
-      <c r="F52" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G52" s="5"/>
-      <c r="H52" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I52" s="4"/>
-      <c r="L52" s="6">
+      <c r="E52" s="4">
+        <v>22.38</v>
+      </c>
+      <c r="F52" s="2">
+        <f t="shared" si="0"/>
+        <v>1.706881143878463E-5</v>
+      </c>
+      <c r="G52" s="5">
+        <v>205.2</v>
+      </c>
+      <c r="H52" s="7">
+        <f t="shared" si="1"/>
+        <v>6.6841651277123587E-20</v>
+      </c>
+      <c r="I52" s="7"/>
+      <c r="L52" s="9">
         <v>5.0000000000000004E-19</v>
       </c>
-      <c r="M52" s="6"/>
-      <c r="N52" s="2">
+      <c r="M52" s="9"/>
+      <c r="N52" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1960,20 +2233,22 @@
       <c r="D53" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E53" s="5"/>
+      <c r="E53" s="4"/>
       <c r="F53" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G53" s="5"/>
-      <c r="H53" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I53" s="4"/>
-      <c r="L53" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M53" s="4"/>
-      <c r="N53" s="2">
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G53" s="4"/>
+      <c r="H53" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I53" s="7"/>
+      <c r="L53" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="M53" s="8"/>
+      <c r="N53" s="1">
         <v>0</v>
       </c>
     </row>
@@ -1987,15 +2262,17 @@
       <c r="D54" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E54" s="5"/>
+      <c r="E54" s="4"/>
       <c r="F54" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G54" s="5"/>
-      <c r="H54" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I54" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G54" s="4"/>
+      <c r="H54" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I54" s="7"/>
     </row>
     <row r="55" spans="2:14">
       <c r="B55" s="2">
@@ -2007,15 +2284,17 @@
       <c r="D55" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E55" s="5"/>
+      <c r="E55" s="4"/>
       <c r="F55" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G55" s="5"/>
-      <c r="H55" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I55" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G55" s="4"/>
+      <c r="H55" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I55" s="7"/>
     </row>
     <row r="56" spans="2:14">
       <c r="B56" s="2">
@@ -2027,15 +2306,17 @@
       <c r="D56" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E56" s="5"/>
+      <c r="E56" s="4"/>
       <c r="F56" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G56" s="5"/>
-      <c r="H56" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I56" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G56" s="4"/>
+      <c r="H56" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I56" s="7"/>
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="2">
@@ -2047,15 +2328,17 @@
       <c r="D57" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E57" s="5"/>
+      <c r="E57" s="4"/>
       <c r="F57" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G57" s="5"/>
-      <c r="H57" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I57" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G57" s="4"/>
+      <c r="H57" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I57" s="7"/>
     </row>
     <row r="58" spans="2:14">
       <c r="B58" s="2">
@@ -2067,15 +2350,17 @@
       <c r="D58" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E58" s="5"/>
+      <c r="E58" s="4"/>
       <c r="F58" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G58" s="5"/>
-      <c r="H58" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I58" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G58" s="4"/>
+      <c r="H58" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I58" s="7"/>
     </row>
     <row r="59" spans="2:14">
       <c r="B59" s="2">
@@ -2087,15 +2372,17 @@
       <c r="D59" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E59" s="5"/>
+      <c r="E59" s="4"/>
       <c r="F59" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G59" s="5"/>
-      <c r="H59" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I59" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G59" s="4"/>
+      <c r="H59" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I59" s="7"/>
     </row>
     <row r="60" spans="2:14">
       <c r="B60" s="2">
@@ -2107,15 +2394,17 @@
       <c r="D60" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E60" s="5"/>
+      <c r="E60" s="4"/>
       <c r="F60" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G60" s="5"/>
-      <c r="H60" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I60" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G60" s="4"/>
+      <c r="H60" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I60" s="7"/>
     </row>
     <row r="61" spans="2:14">
       <c r="B61" s="2">
@@ -2127,15 +2416,17 @@
       <c r="D61" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E61" s="5"/>
+      <c r="E61" s="4"/>
       <c r="F61" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G61" s="5"/>
-      <c r="H61" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I61" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G61" s="4"/>
+      <c r="H61" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I61" s="7"/>
     </row>
     <row r="62" spans="2:14">
       <c r="B62" s="2">
@@ -2147,15 +2438,17 @@
       <c r="D62" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E62" s="5"/>
+      <c r="E62" s="4"/>
       <c r="F62" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G62" s="5"/>
-      <c r="H62" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I62" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G62" s="4"/>
+      <c r="H62" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I62" s="7"/>
     </row>
     <row r="63" spans="2:14">
       <c r="B63" s="2">
@@ -2167,15 +2460,17 @@
       <c r="D63" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E63" s="5"/>
+      <c r="E63" s="4"/>
       <c r="F63" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G63" s="5"/>
-      <c r="H63" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I63" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G63" s="4"/>
+      <c r="H63" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I63" s="7"/>
     </row>
     <row r="64" spans="2:14">
       <c r="B64" s="2">
@@ -2187,15 +2482,17 @@
       <c r="D64" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E64" s="5"/>
+      <c r="E64" s="4"/>
       <c r="F64" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G64" s="5"/>
-      <c r="H64" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I64" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G64" s="4"/>
+      <c r="H64" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I64" s="7"/>
     </row>
     <row r="65" spans="2:9">
       <c r="B65" s="2">
@@ -2207,15 +2504,17 @@
       <c r="D65" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E65" s="5"/>
+      <c r="E65" s="4"/>
       <c r="F65" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G65" s="5"/>
-      <c r="H65" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I65" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G65" s="4"/>
+      <c r="H65" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I65" s="7"/>
     </row>
     <row r="66" spans="2:9">
       <c r="B66" s="2">
@@ -2227,15 +2526,17 @@
       <c r="D66" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E66" s="5"/>
+      <c r="E66" s="4"/>
       <c r="F66" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G66" s="5"/>
-      <c r="H66" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I66" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G66" s="4"/>
+      <c r="H66" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I66" s="7"/>
     </row>
     <row r="67" spans="2:9">
       <c r="B67" s="2">
@@ -2247,15 +2548,17 @@
       <c r="D67" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E67" s="5"/>
+      <c r="E67" s="4"/>
       <c r="F67" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G67" s="5"/>
-      <c r="H67" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I67" s="4"/>
+        <f t="shared" si="0"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G67" s="4"/>
+      <c r="H67" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I67" s="7"/>
     </row>
     <row r="68" spans="2:9">
       <c r="B68" s="2">
@@ -2267,15 +2570,17 @@
       <c r="D68" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E68" s="5"/>
+      <c r="E68" s="4"/>
       <c r="F68" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G68" s="5"/>
-      <c r="H68" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I68" s="4"/>
+        <f t="shared" ref="F68:F102" si="2">D68/E68</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G68" s="4"/>
+      <c r="H68" s="7" t="e">
+        <f t="shared" ref="H68:H102" si="3">1.945*10^-10*F68^1.5/G68</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I68" s="7"/>
     </row>
     <row r="69" spans="2:9">
       <c r="B69" s="2">
@@ -2287,15 +2592,17 @@
       <c r="D69" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E69" s="5"/>
+      <c r="E69" s="4"/>
       <c r="F69" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G69" s="5"/>
-      <c r="H69" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I69" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G69" s="4"/>
+      <c r="H69" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I69" s="7"/>
     </row>
     <row r="70" spans="2:9">
       <c r="B70" s="2">
@@ -2307,15 +2614,17 @@
       <c r="D70" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E70" s="5"/>
+      <c r="E70" s="4"/>
       <c r="F70" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G70" s="5"/>
-      <c r="H70" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I70" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G70" s="4"/>
+      <c r="H70" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I70" s="7"/>
     </row>
     <row r="71" spans="2:9">
       <c r="B71" s="2">
@@ -2327,15 +2636,17 @@
       <c r="D71" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E71" s="5"/>
+      <c r="E71" s="4"/>
       <c r="F71" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G71" s="5"/>
-      <c r="H71" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I71" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G71" s="4"/>
+      <c r="H71" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I71" s="7"/>
     </row>
     <row r="72" spans="2:9">
       <c r="B72" s="2">
@@ -2347,15 +2658,17 @@
       <c r="D72" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E72" s="5"/>
+      <c r="E72" s="4"/>
       <c r="F72" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G72" s="5"/>
-      <c r="H72" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I72" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G72" s="4"/>
+      <c r="H72" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I72" s="7"/>
     </row>
     <row r="73" spans="2:9">
       <c r="B73" s="2">
@@ -2367,15 +2680,17 @@
       <c r="D73" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E73" s="5"/>
+      <c r="E73" s="4"/>
       <c r="F73" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G73" s="5"/>
-      <c r="H73" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I73" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G73" s="4"/>
+      <c r="H73" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I73" s="7"/>
     </row>
     <row r="74" spans="2:9">
       <c r="B74" s="2">
@@ -2387,15 +2702,17 @@
       <c r="D74" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E74" s="5"/>
+      <c r="E74" s="4"/>
       <c r="F74" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G74" s="5"/>
-      <c r="H74" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I74" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G74" s="4"/>
+      <c r="H74" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I74" s="7"/>
     </row>
     <row r="75" spans="2:9">
       <c r="B75" s="2">
@@ -2407,15 +2724,17 @@
       <c r="D75" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E75" s="5"/>
+      <c r="E75" s="4"/>
       <c r="F75" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G75" s="5"/>
-      <c r="H75" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I75" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G75" s="4"/>
+      <c r="H75" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I75" s="7"/>
     </row>
     <row r="76" spans="2:9">
       <c r="B76" s="2">
@@ -2427,15 +2746,17 @@
       <c r="D76" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E76" s="5"/>
+      <c r="E76" s="4"/>
       <c r="F76" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G76" s="5"/>
-      <c r="H76" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I76" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G76" s="4"/>
+      <c r="H76" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I76" s="7"/>
     </row>
     <row r="77" spans="2:9">
       <c r="B77" s="2">
@@ -2447,15 +2768,17 @@
       <c r="D77" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E77" s="5"/>
+      <c r="E77" s="4"/>
       <c r="F77" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G77" s="5"/>
-      <c r="H77" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I77" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G77" s="4"/>
+      <c r="H77" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I77" s="7"/>
     </row>
     <row r="78" spans="2:9">
       <c r="B78" s="2">
@@ -2467,15 +2790,17 @@
       <c r="D78" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E78" s="5"/>
+      <c r="E78" s="4"/>
       <c r="F78" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G78" s="5"/>
-      <c r="H78" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I78" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G78" s="4"/>
+      <c r="H78" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I78" s="7"/>
     </row>
     <row r="79" spans="2:9">
       <c r="B79" s="2">
@@ -2487,15 +2812,17 @@
       <c r="D79" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E79" s="5"/>
+      <c r="E79" s="4"/>
       <c r="F79" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G79" s="5"/>
-      <c r="H79" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I79" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G79" s="4"/>
+      <c r="H79" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I79" s="7"/>
     </row>
     <row r="80" spans="2:9">
       <c r="B80" s="2">
@@ -2507,15 +2834,17 @@
       <c r="D80" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E80" s="5"/>
+      <c r="E80" s="4"/>
       <c r="F80" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G80" s="5"/>
-      <c r="H80" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I80" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G80" s="4"/>
+      <c r="H80" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I80" s="7"/>
     </row>
     <row r="81" spans="2:9">
       <c r="B81" s="2">
@@ -2527,15 +2856,17 @@
       <c r="D81" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E81" s="5"/>
+      <c r="E81" s="4"/>
       <c r="F81" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G81" s="5"/>
-      <c r="H81" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I81" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G81" s="4"/>
+      <c r="H81" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I81" s="7"/>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="2">
@@ -2547,15 +2878,17 @@
       <c r="D82" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E82" s="5"/>
+      <c r="E82" s="4"/>
       <c r="F82" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G82" s="5"/>
-      <c r="H82" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I82" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G82" s="4"/>
+      <c r="H82" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I82" s="7"/>
     </row>
     <row r="83" spans="2:9">
       <c r="B83" s="2">
@@ -2567,15 +2900,17 @@
       <c r="D83" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E83" s="5"/>
+      <c r="E83" s="4"/>
       <c r="F83" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G83" s="5"/>
-      <c r="H83" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I83" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G83" s="4"/>
+      <c r="H83" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I83" s="7"/>
     </row>
     <row r="84" spans="2:9">
       <c r="B84" s="2">
@@ -2587,15 +2922,17 @@
       <c r="D84" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E84" s="5"/>
+      <c r="E84" s="4"/>
       <c r="F84" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G84" s="5"/>
-      <c r="H84" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I84" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G84" s="4"/>
+      <c r="H84" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I84" s="7"/>
     </row>
     <row r="85" spans="2:9">
       <c r="B85" s="2">
@@ -2607,15 +2944,17 @@
       <c r="D85" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E85" s="5"/>
+      <c r="E85" s="4"/>
       <c r="F85" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G85" s="5"/>
-      <c r="H85" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I85" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G85" s="4"/>
+      <c r="H85" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I85" s="7"/>
     </row>
     <row r="86" spans="2:9">
       <c r="B86" s="2">
@@ -2627,15 +2966,17 @@
       <c r="D86" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E86" s="5"/>
+      <c r="E86" s="4"/>
       <c r="F86" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G86" s="5"/>
-      <c r="H86" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I86" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G86" s="4"/>
+      <c r="H86" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I86" s="7"/>
     </row>
     <row r="87" spans="2:9">
       <c r="B87" s="2">
@@ -2647,15 +2988,17 @@
       <c r="D87" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E87" s="5"/>
+      <c r="E87" s="4"/>
       <c r="F87" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G87" s="5"/>
-      <c r="H87" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I87" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G87" s="4"/>
+      <c r="H87" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I87" s="7"/>
     </row>
     <row r="88" spans="2:9">
       <c r="B88" s="2">
@@ -2667,15 +3010,17 @@
       <c r="D88" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E88" s="5"/>
+      <c r="E88" s="4"/>
       <c r="F88" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G88" s="5"/>
-      <c r="H88" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I88" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G88" s="4"/>
+      <c r="H88" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I88" s="7"/>
     </row>
     <row r="89" spans="2:9">
       <c r="B89" s="2">
@@ -2687,15 +3032,17 @@
       <c r="D89" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E89" s="5"/>
+      <c r="E89" s="4"/>
       <c r="F89" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G89" s="5"/>
-      <c r="H89" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I89" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G89" s="4"/>
+      <c r="H89" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I89" s="7"/>
     </row>
     <row r="90" spans="2:9">
       <c r="B90" s="2">
@@ -2707,15 +3054,17 @@
       <c r="D90" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E90" s="5"/>
+      <c r="E90" s="4"/>
       <c r="F90" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G90" s="5"/>
-      <c r="H90" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I90" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G90" s="4"/>
+      <c r="H90" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I90" s="7"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" s="2">
@@ -2727,15 +3076,17 @@
       <c r="D91" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E91" s="5"/>
+      <c r="E91" s="4"/>
       <c r="F91" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G91" s="5"/>
-      <c r="H91" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I91" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G91" s="4"/>
+      <c r="H91" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I91" s="7"/>
     </row>
     <row r="92" spans="2:9">
       <c r="B92" s="2">
@@ -2747,15 +3098,17 @@
       <c r="D92" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E92" s="5"/>
+      <c r="E92" s="4"/>
       <c r="F92" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G92" s="5"/>
-      <c r="H92" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I92" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G92" s="4"/>
+      <c r="H92" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I92" s="7"/>
     </row>
     <row r="93" spans="2:9">
       <c r="B93" s="2">
@@ -2767,15 +3120,17 @@
       <c r="D93" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E93" s="5"/>
+      <c r="E93" s="4"/>
       <c r="F93" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G93" s="5"/>
-      <c r="H93" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I93" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G93" s="4"/>
+      <c r="H93" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I93" s="7"/>
     </row>
     <row r="94" spans="2:9">
       <c r="B94" s="2">
@@ -2787,15 +3142,17 @@
       <c r="D94" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E94" s="5"/>
+      <c r="E94" s="4"/>
       <c r="F94" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G94" s="5"/>
-      <c r="H94" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I94" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G94" s="4"/>
+      <c r="H94" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I94" s="7"/>
     </row>
     <row r="95" spans="2:9">
       <c r="B95" s="2">
@@ -2807,15 +3164,17 @@
       <c r="D95" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E95" s="5"/>
+      <c r="E95" s="4"/>
       <c r="F95" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G95" s="5"/>
-      <c r="H95" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I95" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G95" s="4"/>
+      <c r="H95" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I95" s="7"/>
     </row>
     <row r="96" spans="2:9">
       <c r="B96" s="2">
@@ -2827,15 +3186,17 @@
       <c r="D96" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E96" s="5"/>
+      <c r="E96" s="4"/>
       <c r="F96" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G96" s="5"/>
-      <c r="H96" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I96" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G96" s="4"/>
+      <c r="H96" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I96" s="7"/>
     </row>
     <row r="97" spans="2:9">
       <c r="B97" s="2">
@@ -2847,15 +3208,17 @@
       <c r="D97" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E97" s="5"/>
+      <c r="E97" s="4"/>
       <c r="F97" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G97" s="5"/>
-      <c r="H97" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I97" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G97" s="4"/>
+      <c r="H97" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I97" s="7"/>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="2">
@@ -2867,15 +3230,17 @@
       <c r="D98" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E98" s="5"/>
+      <c r="E98" s="4"/>
       <c r="F98" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G98" s="5"/>
-      <c r="H98" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I98" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G98" s="4"/>
+      <c r="H98" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I98" s="7"/>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="2">
@@ -2887,15 +3252,17 @@
       <c r="D99" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E99" s="5"/>
+      <c r="E99" s="4"/>
       <c r="F99" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G99" s="5"/>
-      <c r="H99" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I99" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G99" s="4"/>
+      <c r="H99" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I99" s="7"/>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="2">
@@ -2907,15 +3274,17 @@
       <c r="D100" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E100" s="5"/>
+      <c r="E100" s="4"/>
       <c r="F100" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G100" s="5"/>
-      <c r="H100" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I100" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G100" s="4"/>
+      <c r="H100" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I100" s="7"/>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="2">
@@ -2927,15 +3296,17 @@
       <c r="D101" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E101" s="5"/>
+      <c r="E101" s="4"/>
       <c r="F101" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G101" s="5"/>
-      <c r="H101" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I101" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G101" s="4"/>
+      <c r="H101" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I101" s="7"/>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="2">
@@ -2947,15 +3318,17 @@
       <c r="D102" s="2">
         <v>3.8200000000000002E-4</v>
       </c>
-      <c r="E102" s="5"/>
+      <c r="E102" s="4"/>
       <c r="F102" s="2" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G102" s="5"/>
-      <c r="H102" s="4" t="e">
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I102" s="4"/>
+        <f t="shared" si="2"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G102" s="4"/>
+      <c r="H102" s="7" t="e">
+        <f t="shared" si="3"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I102" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="153">

--- a/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
+++ b/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
@@ -5,16 +5,46 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Eric Wang\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one down\普物實驗\6 密立根油滴實驗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD8C3506-A3B8-4470-96FD-F54C4BDA2F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776E5D79-157E-46E9-90A6-4DBCB5DC7394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlchart.v1.0" hidden="1">工作表1!$L$2</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">工作表1!$L$3:$L$52</definedName>
+    <definedName name="_xlchart.v1.10" hidden="1">工作表1!$N$2</definedName>
+    <definedName name="_xlchart.v1.11" hidden="1">工作表1!$N$3:$N$52</definedName>
+    <definedName name="_xlchart.v1.12" hidden="1">工作表1!$L$2</definedName>
+    <definedName name="_xlchart.v1.13" hidden="1">工作表1!$L$3:$L$52</definedName>
+    <definedName name="_xlchart.v1.14" hidden="1">工作表1!$M$2</definedName>
+    <definedName name="_xlchart.v1.15" hidden="1">工作表1!$M$3:$M$52</definedName>
+    <definedName name="_xlchart.v1.16" hidden="1">工作表1!$N$2</definedName>
+    <definedName name="_xlchart.v1.17" hidden="1">工作表1!$N$3:$N$52</definedName>
+    <definedName name="_xlchart.v1.18" hidden="1">工作表1!$L$2</definedName>
+    <definedName name="_xlchart.v1.19" hidden="1">工作表1!$L$3:$L$52</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">工作表1!$M$2</definedName>
+    <definedName name="_xlchart.v1.20" hidden="1">工作表1!$M$2</definedName>
+    <definedName name="_xlchart.v1.21" hidden="1">工作表1!$M$3:$M$52</definedName>
+    <definedName name="_xlchart.v1.22" hidden="1">工作表1!$N$2</definedName>
+    <definedName name="_xlchart.v1.23" hidden="1">工作表1!$N$3:$N$52</definedName>
+    <definedName name="_xlchart.v1.24" hidden="1">工作表1!$H$3:$H$52</definedName>
+    <definedName name="_xlchart.v1.25" hidden="1">工作表1!$I$3:$I$52</definedName>
+    <definedName name="_xlchart.v1.26" hidden="1">工作表1!$H$3:$H$52</definedName>
+    <definedName name="_xlchart.v1.27" hidden="1">工作表1!$I$3:$I$52</definedName>
+    <definedName name="_xlchart.v1.3" hidden="1">工作表1!$M$3:$M$52</definedName>
+    <definedName name="_xlchart.v1.4" hidden="1">工作表1!$N$2</definedName>
+    <definedName name="_xlchart.v1.5" hidden="1">工作表1!$N$3:$N$52</definedName>
+    <definedName name="_xlchart.v1.6" hidden="1">工作表1!$L$2</definedName>
+    <definedName name="_xlchart.v1.7" hidden="1">工作表1!$L$3:$L$52</definedName>
+    <definedName name="_xlchart.v1.8" hidden="1">工作表1!$M$2</definedName>
+    <definedName name="_xlchart.v1.9" hidden="1">工作表1!$M$3:$M$52</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -59,13 +89,14 @@
     <t>個數</t>
   </si>
   <si>
-    <t>大於5.0E-19</t>
-  </si>
-  <si>
     <t xml:space="preserve">V1(m/s) </t>
   </si>
   <si>
     <t>U0(V)</t>
+  </si>
+  <si>
+    <t>大於5.0E-19</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -188,13 +219,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -212,6 +243,711 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chartEx1.xml><?xml version="1.0" encoding="utf-8"?>
+<cx:chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex">
+  <cx:chartData>
+    <cx:data id="0">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.1</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="1">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.3</cx:f>
+      </cx:numDim>
+    </cx:data>
+    <cx:data id="2">
+      <cx:numDim type="val">
+        <cx:f>_xlchart.v1.5</cx:f>
+      </cx:numDim>
+    </cx:data>
+  </cx:chartData>
+  <cx:chart>
+    <cx:title pos="t" align="ctr" overlay="0"/>
+    <cx:plotArea>
+      <cx:plotAreaRegion>
+        <cx:series layoutId="clusteredColumn" uniqueId="{EFB47B4B-4C1F-4CF9-A965-E782A27B7B23}" formatIdx="0">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.0</cx:f>
+              <cx:v>區間</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="0"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="clusteredColumn" hidden="1" uniqueId="{5597F895-2740-437A-B876-2D7FD89BF48C}" formatIdx="1">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.2</cx:f>
+              <cx:v/>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="1"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+        <cx:series layoutId="clusteredColumn" hidden="1" uniqueId="{13374917-7E77-4835-ADAD-B237BC2EB100}" formatIdx="2">
+          <cx:tx>
+            <cx:txData>
+              <cx:f>_xlchart.v1.4</cx:f>
+              <cx:v>個數</cx:v>
+            </cx:txData>
+          </cx:tx>
+          <cx:dataId val="2"/>
+          <cx:layoutPr>
+            <cx:binning intervalClosed="r"/>
+          </cx:layoutPr>
+        </cx:series>
+      </cx:plotAreaRegion>
+      <cx:axis id="0">
+        <cx:catScaling gapWidth="0"/>
+        <cx:tickLabels/>
+      </cx:axis>
+      <cx:axis id="1">
+        <cx:valScaling/>
+        <cx:majorGridlines/>
+        <cx:tickLabels/>
+      </cx:axis>
+    </cx:plotArea>
+  </cx:chart>
+</cx:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="366">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat">
+        <a:solidFill>
+          <a:srgbClr val="D9D9D9"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDash"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>447477</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>37306</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>177602</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>161131</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="圖表 4">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2C3D6D5-CF4B-E6DD-8171-6AF41FFA0B7E}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="10319743" y="5494337"/>
+              <a:ext cx="4572000" cy="2743200"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="zh-TW" altLang="en-US" sz="1100"/>
+                <a:t>此圖表在您的 Excel 版本中無法使用。
+若編輯此圖案或將此活頁簿儲存為不同格式，將永久破壞圖表。</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -556,15 +1292,15 @@
         <v>3</v>
       </c>
       <c r="F2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="7"/>
+      <c r="I2" s="9"/>
       <c r="L2" s="8" t="s">
         <v>5</v>
       </c>
@@ -593,16 +1329,17 @@
       <c r="G3" s="5">
         <v>72.3</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="9">
         <f>1.945*10^-10*F3^1.5/G3</f>
         <v>1.8449053158903017E-19</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="L3" s="9">
+      <c r="I3" s="9"/>
+      <c r="L3" s="7">
         <v>9.9999999999999995E-21</v>
       </c>
-      <c r="M3" s="9"/>
+      <c r="M3" s="7"/>
       <c r="N3" s="1">
+        <f t="array" ref="N3:N52">FREQUENCY(H3:I52,L3:M52)</f>
         <v>0</v>
       </c>
     </row>
@@ -626,15 +1363,15 @@
       <c r="G4" s="5">
         <v>168.6</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="9">
         <f t="shared" ref="H4:H67" si="1">1.945*10^-10*F4^1.5/G4</f>
         <v>4.3490105195356502E-19</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="L4" s="9">
+      <c r="I4" s="9"/>
+      <c r="L4" s="7">
         <v>1.9999999999999999E-20</v>
       </c>
-      <c r="M4" s="9"/>
+      <c r="M4" s="7"/>
       <c r="N4" s="1">
         <v>0</v>
       </c>
@@ -659,15 +1396,15 @@
       <c r="G5" s="5">
         <v>62.6</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <f t="shared" si="1"/>
         <v>4.2144171456566916E-19</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="L5" s="9">
+      <c r="I5" s="9"/>
+      <c r="L5" s="7">
         <v>3.0000000000000003E-20</v>
       </c>
-      <c r="M5" s="9"/>
+      <c r="M5" s="7"/>
       <c r="N5" s="1">
         <v>0</v>
       </c>
@@ -692,17 +1429,17 @@
       <c r="G6" s="5">
         <v>68.599999999999994</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <f t="shared" si="1"/>
         <v>3.6510923183134183E-19</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="L6" s="9">
+      <c r="I6" s="9"/>
+      <c r="L6" s="7">
         <v>3.9999999999999998E-20</v>
       </c>
-      <c r="M6" s="9"/>
+      <c r="M6" s="7"/>
       <c r="N6" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="2:14">
@@ -725,17 +1462,17 @@
       <c r="G7" s="5">
         <v>284.2</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="9">
         <f t="shared" si="1"/>
         <v>7.1215768734266231E-19</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="L7" s="9">
+      <c r="I7" s="9"/>
+      <c r="L7" s="7">
         <v>4.9999999999999999E-20</v>
       </c>
-      <c r="M7" s="9"/>
+      <c r="M7" s="7"/>
       <c r="N7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:14">
@@ -758,15 +1495,15 @@
       <c r="G8" s="5">
         <v>351.7</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="9">
         <f t="shared" si="1"/>
         <v>5.0659365601111741E-19</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="L8" s="9">
+      <c r="I8" s="9"/>
+      <c r="L8" s="7">
         <v>6.0000000000000006E-20</v>
       </c>
-      <c r="M8" s="9"/>
+      <c r="M8" s="7"/>
       <c r="N8" s="1">
         <v>0</v>
       </c>
@@ -791,17 +1528,17 @@
       <c r="G9" s="5">
         <v>126</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="9">
         <f t="shared" si="1"/>
         <v>3.339529675490588E-19</v>
       </c>
-      <c r="I9" s="7"/>
-      <c r="L9" s="9">
+      <c r="I9" s="9"/>
+      <c r="L9" s="7">
         <v>7.0000000000000001E-20</v>
       </c>
-      <c r="M9" s="9"/>
+      <c r="M9" s="7"/>
       <c r="N9" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="2:14">
@@ -824,17 +1561,17 @@
       <c r="G10" s="5">
         <v>120.1</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="9">
         <f t="shared" si="1"/>
         <v>3.971592840015501E-19</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="L10" s="9">
+      <c r="I10" s="9"/>
+      <c r="L10" s="7">
         <v>7.9999999999999996E-20</v>
       </c>
-      <c r="M10" s="9"/>
+      <c r="M10" s="7"/>
       <c r="N10" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11" spans="2:14">
@@ -857,17 +1594,17 @@
       <c r="G11" s="5">
         <v>170.8</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="9">
         <f t="shared" si="1"/>
         <v>3.6812516124506652E-19</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="L11" s="9">
+      <c r="I11" s="9"/>
+      <c r="L11" s="7">
         <v>9.0000000000000003E-20</v>
       </c>
-      <c r="M11" s="9"/>
+      <c r="M11" s="7"/>
       <c r="N11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="2:14">
@@ -890,17 +1627,17 @@
       <c r="G12" s="5">
         <v>88.4</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="9">
         <f t="shared" si="1"/>
         <v>1.5758025146171712E-19</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="L12" s="9">
+      <c r="I12" s="9"/>
+      <c r="L12" s="7">
         <v>9.9999999999999998E-20</v>
       </c>
-      <c r="M12" s="9"/>
+      <c r="M12" s="7"/>
       <c r="N12" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -923,17 +1660,17 @@
       <c r="G13" s="5">
         <v>126.6</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="9">
         <f t="shared" si="1"/>
         <v>4.4240984732649361E-19</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="L13" s="9">
+      <c r="I13" s="9"/>
+      <c r="L13" s="7">
         <v>1.0999999999999999E-19</v>
       </c>
-      <c r="M13" s="9"/>
+      <c r="M13" s="7"/>
       <c r="N13" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="2:14">
@@ -956,15 +1693,15 @@
       <c r="G14" s="5">
         <v>128.4</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="9">
         <f t="shared" si="1"/>
         <v>4.1131264461271426E-19</v>
       </c>
-      <c r="I14" s="7"/>
-      <c r="L14" s="9">
+      <c r="I14" s="9"/>
+      <c r="L14" s="7">
         <v>1.2000000000000001E-19</v>
       </c>
-      <c r="M14" s="9"/>
+      <c r="M14" s="7"/>
       <c r="N14" s="1">
         <v>0</v>
       </c>
@@ -989,15 +1726,15 @@
       <c r="G15" s="5">
         <v>41.9</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="9">
         <f t="shared" si="1"/>
         <v>3.0461654514538201E-19</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="L15" s="9">
+      <c r="I15" s="9"/>
+      <c r="L15" s="7">
         <v>1.3000000000000001E-19</v>
       </c>
-      <c r="M15" s="9"/>
+      <c r="M15" s="7"/>
       <c r="N15" s="1">
         <v>0</v>
       </c>
@@ -1022,17 +1759,17 @@
       <c r="G16" s="5">
         <v>83.9</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="9">
         <f t="shared" si="1"/>
         <v>3.9831346048250973E-19</v>
       </c>
-      <c r="I16" s="7"/>
-      <c r="L16" s="9">
+      <c r="I16" s="9"/>
+      <c r="L16" s="7">
         <v>1.4E-19</v>
       </c>
-      <c r="M16" s="9"/>
+      <c r="M16" s="7"/>
       <c r="N16" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -1055,15 +1792,15 @@
       <c r="G17" s="5">
         <v>173.6</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="9">
         <f t="shared" si="1"/>
         <v>1.6678483768588152E-19</v>
       </c>
-      <c r="I17" s="7"/>
-      <c r="L17" s="9">
+      <c r="I17" s="9"/>
+      <c r="L17" s="7">
         <v>1.5E-19</v>
       </c>
-      <c r="M17" s="9"/>
+      <c r="M17" s="7"/>
       <c r="N17" s="1">
         <v>0</v>
       </c>
@@ -1088,17 +1825,17 @@
       <c r="G18" s="5">
         <v>232.8</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="9">
         <f t="shared" si="1"/>
         <v>2.120275636869835E-19</v>
       </c>
-      <c r="I18" s="7"/>
-      <c r="L18" s="9">
+      <c r="I18" s="9"/>
+      <c r="L18" s="7">
         <v>1.5999999999999999E-19</v>
       </c>
-      <c r="M18" s="9"/>
+      <c r="M18" s="7"/>
       <c r="N18" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -1121,17 +1858,17 @@
       <c r="G19" s="5">
         <v>115.9</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="9">
         <f t="shared" si="1"/>
         <v>1.7488298802142485E-19</v>
       </c>
-      <c r="I19" s="7"/>
-      <c r="L19" s="9">
+      <c r="I19" s="9"/>
+      <c r="L19" s="7">
         <v>1.7000000000000001E-19</v>
       </c>
-      <c r="M19" s="9"/>
+      <c r="M19" s="7"/>
       <c r="N19" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -1154,17 +1891,17 @@
       <c r="G20" s="5">
         <v>69.599999999999994</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="9">
         <f t="shared" si="1"/>
         <v>2.455034668682092E-19</v>
       </c>
-      <c r="I20" s="7"/>
-      <c r="L20" s="9">
+      <c r="I20" s="9"/>
+      <c r="L20" s="7">
         <v>1.8000000000000001E-19</v>
       </c>
-      <c r="M20" s="9"/>
+      <c r="M20" s="7"/>
       <c r="N20" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -1187,17 +1924,17 @@
       <c r="G21" s="5">
         <v>211.8</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="9">
         <f t="shared" si="1"/>
         <v>1.5384584720296341E-19</v>
       </c>
-      <c r="I21" s="7"/>
-      <c r="L21" s="9">
+      <c r="I21" s="9"/>
+      <c r="L21" s="7">
         <v>1.9E-19</v>
       </c>
-      <c r="M21" s="9"/>
+      <c r="M21" s="7"/>
       <c r="N21" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -1220,15 +1957,15 @@
       <c r="G22" s="5">
         <v>225.3</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="9">
         <f t="shared" si="1"/>
         <v>7.8498587920631624E-19</v>
       </c>
-      <c r="I22" s="7"/>
-      <c r="L22" s="9">
+      <c r="I22" s="9"/>
+      <c r="L22" s="7">
         <v>2E-19</v>
       </c>
-      <c r="M22" s="9"/>
+      <c r="M22" s="7"/>
       <c r="N22" s="1">
         <v>0</v>
       </c>
@@ -1253,17 +1990,17 @@
       <c r="G23" s="5">
         <v>42.2</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="9">
         <f t="shared" si="1"/>
         <v>1.4548270972574926E-18</v>
       </c>
-      <c r="I23" s="7"/>
-      <c r="L23" s="9">
+      <c r="I23" s="9"/>
+      <c r="L23" s="7">
         <v>2.0999999999999999E-19</v>
       </c>
-      <c r="M23" s="9"/>
+      <c r="M23" s="7"/>
       <c r="N23" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="2:14">
@@ -1286,17 +2023,17 @@
       <c r="G24" s="5">
         <v>92.9</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="9">
         <f t="shared" si="1"/>
         <v>1.6442393256488777E-19</v>
       </c>
-      <c r="I24" s="7"/>
-      <c r="L24" s="9">
+      <c r="I24" s="9"/>
+      <c r="L24" s="7">
         <v>2.1999999999999998E-19</v>
       </c>
-      <c r="M24" s="9"/>
+      <c r="M24" s="7"/>
       <c r="N24" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="2:14">
@@ -1319,17 +2056,17 @@
       <c r="G25" s="5">
         <v>72.900000000000006</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="9">
         <f t="shared" si="1"/>
         <v>1.6857858253870438E-19</v>
       </c>
-      <c r="I25" s="7"/>
-      <c r="L25" s="9">
+      <c r="I25" s="9"/>
+      <c r="L25" s="7">
         <v>2.2999999999999998E-19</v>
       </c>
-      <c r="M25" s="9"/>
+      <c r="M25" s="7"/>
       <c r="N25" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="2:14">
@@ -1352,17 +2089,17 @@
       <c r="G26" s="5">
         <v>288.10000000000002</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="9">
         <f t="shared" si="1"/>
         <v>4.9794532621128721E-20</v>
       </c>
-      <c r="I26" s="7"/>
-      <c r="L26" s="9">
+      <c r="I26" s="9"/>
+      <c r="L26" s="7">
         <v>2.4000000000000002E-19</v>
       </c>
-      <c r="M26" s="9"/>
+      <c r="M26" s="7"/>
       <c r="N26" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="2:14">
@@ -1385,17 +2122,17 @@
       <c r="G27" s="5">
         <v>227.7</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="9">
         <f t="shared" si="1"/>
         <v>1.0944934037775462E-19</v>
       </c>
-      <c r="I27" s="7"/>
-      <c r="L27" s="9">
+      <c r="I27" s="9"/>
+      <c r="L27" s="7">
         <v>2.5000000000000002E-19</v>
       </c>
-      <c r="M27" s="9"/>
+      <c r="M27" s="7"/>
       <c r="N27" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="2:14">
@@ -1418,15 +2155,15 @@
       <c r="G28" s="5">
         <v>236.3</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="9">
         <f t="shared" si="1"/>
         <v>6.2382768602547688E-20</v>
       </c>
-      <c r="I28" s="7"/>
-      <c r="L28" s="9">
+      <c r="I28" s="9"/>
+      <c r="L28" s="7">
         <v>2.6000000000000001E-19</v>
       </c>
-      <c r="M28" s="9"/>
+      <c r="M28" s="7"/>
       <c r="N28" s="1">
         <v>0</v>
       </c>
@@ -1451,15 +2188,15 @@
       <c r="G29" s="5">
         <v>138.4</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="9">
         <f t="shared" si="1"/>
         <v>1.3027476717986452E-19</v>
       </c>
-      <c r="I29" s="7"/>
-      <c r="L29" s="9">
+      <c r="I29" s="9"/>
+      <c r="L29" s="7">
         <v>2.7000000000000001E-19</v>
       </c>
-      <c r="M29" s="9"/>
+      <c r="M29" s="7"/>
       <c r="N29" s="1">
         <v>0</v>
       </c>
@@ -1484,17 +2221,17 @@
       <c r="G30" s="5">
         <v>134.5</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="9">
         <f t="shared" si="1"/>
         <v>9.05287682212827E-19</v>
       </c>
-      <c r="I30" s="7"/>
-      <c r="L30" s="9">
+      <c r="I30" s="9"/>
+      <c r="L30" s="7">
         <v>2.8E-19</v>
       </c>
-      <c r="M30" s="9"/>
+      <c r="M30" s="7"/>
       <c r="N30" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="2:14">
@@ -1517,17 +2254,17 @@
       <c r="G31" s="5">
         <v>111.2</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="9">
         <f t="shared" si="1"/>
         <v>1.835500131871435E-19</v>
       </c>
-      <c r="I31" s="7"/>
-      <c r="L31" s="9">
+      <c r="I31" s="9"/>
+      <c r="L31" s="7">
         <v>2.9E-19</v>
       </c>
-      <c r="M31" s="9"/>
+      <c r="M31" s="7"/>
       <c r="N31" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="2:14">
@@ -1550,15 +2287,15 @@
       <c r="G32" s="5">
         <v>247.1</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="9">
         <f t="shared" si="1"/>
         <v>2.0923481425821882E-19</v>
       </c>
-      <c r="I32" s="7"/>
-      <c r="L32" s="9">
+      <c r="I32" s="9"/>
+      <c r="L32" s="7">
         <v>2.9999999999999999E-19</v>
       </c>
-      <c r="M32" s="9"/>
+      <c r="M32" s="7"/>
       <c r="N32" s="1">
         <v>0</v>
       </c>
@@ -1583,17 +2320,17 @@
       <c r="G33" s="5">
         <v>169</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="9">
         <f t="shared" si="1"/>
         <v>4.4662320015468356E-19</v>
       </c>
-      <c r="I33" s="7"/>
-      <c r="L33" s="9">
+      <c r="I33" s="9"/>
+      <c r="L33" s="7">
         <v>3.0999999999999999E-19</v>
       </c>
-      <c r="M33" s="9"/>
+      <c r="M33" s="7"/>
       <c r="N33" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="2:14">
@@ -1616,15 +2353,15 @@
       <c r="G34" s="5">
         <v>272.8</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="9">
         <f t="shared" si="1"/>
         <v>4.3179864400352903E-20</v>
       </c>
-      <c r="I34" s="7"/>
-      <c r="L34" s="9">
+      <c r="I34" s="9"/>
+      <c r="L34" s="7">
         <v>3.1999999999999998E-19</v>
       </c>
-      <c r="M34" s="9"/>
+      <c r="M34" s="7"/>
       <c r="N34" s="1">
         <v>0</v>
       </c>
@@ -1649,15 +2386,15 @@
       <c r="G35" s="5">
         <v>50.9</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="9">
         <f t="shared" si="1"/>
         <v>2.8380061566768923E-19</v>
       </c>
-      <c r="I35" s="7"/>
-      <c r="L35" s="9">
+      <c r="I35" s="9"/>
+      <c r="L35" s="7">
         <v>3.2999999999999998E-19</v>
       </c>
-      <c r="M35" s="9"/>
+      <c r="M35" s="7"/>
       <c r="N35" s="1">
         <v>0</v>
       </c>
@@ -1682,17 +2419,17 @@
       <c r="G36" s="5">
         <v>170.8</v>
       </c>
-      <c r="H36" s="7">
+      <c r="H36" s="9">
         <f t="shared" si="1"/>
         <v>3.6812516124506652E-19</v>
       </c>
-      <c r="I36" s="7"/>
-      <c r="L36" s="9">
+      <c r="I36" s="9"/>
+      <c r="L36" s="7">
         <v>3.4000000000000002E-19</v>
       </c>
-      <c r="M36" s="9"/>
+      <c r="M36" s="7"/>
       <c r="N36" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="2:14">
@@ -1715,15 +2452,15 @@
       <c r="G37" s="5">
         <v>174.5</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="9">
         <f t="shared" si="1"/>
         <v>7.8812384156677962E-20</v>
       </c>
-      <c r="I37" s="7"/>
-      <c r="L37" s="9">
+      <c r="I37" s="9"/>
+      <c r="L37" s="7">
         <v>3.5000000000000002E-19</v>
       </c>
-      <c r="M37" s="9"/>
+      <c r="M37" s="7"/>
       <c r="N37" s="1">
         <v>0</v>
       </c>
@@ -1748,15 +2485,15 @@
       <c r="G38" s="5">
         <v>123.9</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38" s="9">
         <f t="shared" si="1"/>
         <v>1.0515635189613713E-19</v>
       </c>
-      <c r="I38" s="7"/>
-      <c r="L38" s="9">
+      <c r="I38" s="9"/>
+      <c r="L38" s="7">
         <v>3.6000000000000001E-19</v>
       </c>
-      <c r="M38" s="9"/>
+      <c r="M38" s="7"/>
       <c r="N38" s="1">
         <v>0</v>
       </c>
@@ -1781,17 +2518,17 @@
       <c r="G39" s="5">
         <v>345.3</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="9">
         <f t="shared" si="1"/>
         <v>6.8451844141021412E-20</v>
       </c>
-      <c r="I39" s="7"/>
-      <c r="L39" s="9">
+      <c r="I39" s="9"/>
+      <c r="L39" s="7">
         <v>3.7000000000000001E-19</v>
       </c>
-      <c r="M39" s="9"/>
+      <c r="M39" s="7"/>
       <c r="N39" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="2:14">
@@ -1814,15 +2551,15 @@
       <c r="G40" s="5">
         <v>213.2</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="9">
         <f t="shared" si="1"/>
         <v>1.6202722663136051E-19</v>
       </c>
-      <c r="I40" s="7"/>
-      <c r="L40" s="9">
+      <c r="I40" s="9"/>
+      <c r="L40" s="7">
         <v>3.8E-19</v>
       </c>
-      <c r="M40" s="9"/>
+      <c r="M40" s="7"/>
       <c r="N40" s="1">
         <v>0</v>
       </c>
@@ -1847,15 +2584,15 @@
       <c r="G41" s="5">
         <v>253.3</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41" s="9">
         <f t="shared" si="1"/>
         <v>4.5059327617437475E-19</v>
       </c>
-      <c r="I41" s="7"/>
-      <c r="L41" s="9">
+      <c r="I41" s="9"/>
+      <c r="L41" s="7">
         <v>3.9E-19</v>
       </c>
-      <c r="M41" s="9"/>
+      <c r="M41" s="7"/>
       <c r="N41" s="1">
         <v>0</v>
       </c>
@@ -1880,17 +2617,17 @@
       <c r="G42" s="5">
         <v>169.8</v>
       </c>
-      <c r="H42" s="7">
+      <c r="H42" s="9">
         <f t="shared" si="1"/>
         <v>9.193767993870622E-20</v>
       </c>
-      <c r="I42" s="7"/>
-      <c r="L42" s="9">
+      <c r="I42" s="9"/>
+      <c r="L42" s="7">
         <v>3.9999999999999999E-19</v>
       </c>
-      <c r="M42" s="9"/>
+      <c r="M42" s="7"/>
       <c r="N42" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="2:14">
@@ -1913,15 +2650,15 @@
       <c r="G43" s="5">
         <v>332.7</v>
       </c>
-      <c r="H43" s="7">
+      <c r="H43" s="9">
         <f t="shared" si="1"/>
         <v>3.5086479332700357E-20</v>
       </c>
-      <c r="I43" s="7"/>
-      <c r="L43" s="9">
+      <c r="I43" s="9"/>
+      <c r="L43" s="7">
         <v>4.0999999999999999E-19</v>
       </c>
-      <c r="M43" s="9"/>
+      <c r="M43" s="7"/>
       <c r="N43" s="1">
         <v>0</v>
       </c>
@@ -1946,17 +2683,17 @@
       <c r="G44" s="5">
         <v>222.6</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="9">
         <f t="shared" si="1"/>
         <v>8.98343828154446E-19</v>
       </c>
-      <c r="I44" s="7"/>
-      <c r="L44" s="9">
+      <c r="I44" s="9"/>
+      <c r="L44" s="7">
         <v>4.1999999999999998E-19</v>
       </c>
-      <c r="M44" s="9"/>
+      <c r="M44" s="7"/>
       <c r="N44" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="2:14">
@@ -1979,17 +2716,17 @@
       <c r="G45" s="5">
         <v>187.8</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="9">
         <f t="shared" si="1"/>
         <v>2.7530310225349235E-19</v>
       </c>
-      <c r="I45" s="7"/>
-      <c r="L45" s="9">
+      <c r="I45" s="9"/>
+      <c r="L45" s="7">
         <v>4.3000000000000002E-19</v>
       </c>
-      <c r="M45" s="9"/>
+      <c r="M45" s="7"/>
       <c r="N45" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="2:14">
@@ -2012,17 +2749,17 @@
       <c r="G46" s="5">
         <v>129.6</v>
       </c>
-      <c r="H46" s="7">
+      <c r="H46" s="9">
         <f t="shared" si="1"/>
         <v>2.3205683379361788E-19</v>
       </c>
-      <c r="I46" s="7"/>
-      <c r="L46" s="9">
+      <c r="I46" s="9"/>
+      <c r="L46" s="7">
         <v>4.3999999999999997E-19</v>
       </c>
-      <c r="M46" s="9"/>
+      <c r="M46" s="7"/>
       <c r="N46" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="2:14">
@@ -2045,17 +2782,17 @@
       <c r="G47" s="5">
         <v>336</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H47" s="9">
         <f t="shared" si="1"/>
         <v>8.0259432458438495E-20</v>
       </c>
-      <c r="I47" s="7"/>
-      <c r="L47" s="9">
+      <c r="I47" s="9"/>
+      <c r="L47" s="7">
         <v>4.5000000000000001E-19</v>
       </c>
-      <c r="M47" s="9"/>
+      <c r="M47" s="7"/>
       <c r="N47" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="2:14">
@@ -2078,17 +2815,17 @@
       <c r="G48" s="5">
         <v>92</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H48" s="9">
         <f t="shared" si="1"/>
         <v>5.0519531504841948E-19</v>
       </c>
-      <c r="I48" s="7"/>
-      <c r="L48" s="9">
+      <c r="I48" s="9"/>
+      <c r="L48" s="7">
         <v>4.5999999999999996E-19</v>
       </c>
-      <c r="M48" s="9"/>
+      <c r="M48" s="7"/>
       <c r="N48" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="2:14">
@@ -2111,15 +2848,15 @@
       <c r="G49" s="5">
         <v>220.3</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="9">
         <f t="shared" si="1"/>
         <v>7.4310122663013932E-20</v>
       </c>
-      <c r="I49" s="7"/>
-      <c r="L49" s="9">
+      <c r="I49" s="9"/>
+      <c r="L49" s="7">
         <v>4.7E-19</v>
       </c>
-      <c r="M49" s="9"/>
+      <c r="M49" s="7"/>
       <c r="N49" s="1">
         <v>0</v>
       </c>
@@ -2144,15 +2881,15 @@
       <c r="G50" s="6">
         <v>170.8</v>
       </c>
-      <c r="H50" s="7">
+      <c r="H50" s="9">
         <f t="shared" si="1"/>
         <v>3.6812516124506652E-19</v>
       </c>
-      <c r="I50" s="7"/>
-      <c r="L50" s="9">
+      <c r="I50" s="9"/>
+      <c r="L50" s="7">
         <v>4.8000000000000005E-19</v>
       </c>
-      <c r="M50" s="9"/>
+      <c r="M50" s="7"/>
       <c r="N50" s="1">
         <v>0</v>
       </c>
@@ -2177,15 +2914,15 @@
       <c r="G51" s="5">
         <v>59.7</v>
       </c>
-      <c r="H51" s="7">
+      <c r="H51" s="9">
         <f t="shared" si="1"/>
         <v>2.2959328319809843E-19</v>
       </c>
-      <c r="I51" s="7"/>
-      <c r="L51" s="9">
+      <c r="I51" s="9"/>
+      <c r="L51" s="7">
         <v>4.8999999999999999E-19</v>
       </c>
-      <c r="M51" s="9"/>
+      <c r="M51" s="7"/>
       <c r="N51" s="1">
         <v>0</v>
       </c>
@@ -2210,15 +2947,15 @@
       <c r="G52" s="5">
         <v>205.2</v>
       </c>
-      <c r="H52" s="7">
+      <c r="H52" s="9">
         <f t="shared" si="1"/>
         <v>6.6841651277123587E-20</v>
       </c>
-      <c r="I52" s="7"/>
-      <c r="L52" s="9">
+      <c r="I52" s="9"/>
+      <c r="L52" s="7">
         <v>5.0000000000000004E-19</v>
       </c>
-      <c r="M52" s="9"/>
+      <c r="M52" s="7"/>
       <c r="N52" s="1">
         <v>0</v>
       </c>
@@ -2239,17 +2976,17 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G53" s="4"/>
-      <c r="H53" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I53" s="7"/>
+      <c r="H53" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I53" s="9"/>
       <c r="L53" s="8" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M53" s="8"/>
       <c r="N53" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="2:14">
@@ -2268,11 +3005,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G54" s="4"/>
-      <c r="H54" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I54" s="7"/>
+      <c r="H54" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I54" s="9"/>
     </row>
     <row r="55" spans="2:14">
       <c r="B55" s="2">
@@ -2290,11 +3027,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G55" s="4"/>
-      <c r="H55" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I55" s="7"/>
+      <c r="H55" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I55" s="9"/>
     </row>
     <row r="56" spans="2:14">
       <c r="B56" s="2">
@@ -2312,11 +3049,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G56" s="4"/>
-      <c r="H56" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I56" s="7"/>
+      <c r="H56" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I56" s="9"/>
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="2">
@@ -2334,11 +3071,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G57" s="4"/>
-      <c r="H57" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I57" s="7"/>
+      <c r="H57" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I57" s="9"/>
     </row>
     <row r="58" spans="2:14">
       <c r="B58" s="2">
@@ -2356,11 +3093,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G58" s="4"/>
-      <c r="H58" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I58" s="7"/>
+      <c r="H58" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I58" s="9"/>
     </row>
     <row r="59" spans="2:14">
       <c r="B59" s="2">
@@ -2378,11 +3115,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G59" s="4"/>
-      <c r="H59" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I59" s="7"/>
+      <c r="H59" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I59" s="9"/>
     </row>
     <row r="60" spans="2:14">
       <c r="B60" s="2">
@@ -2400,11 +3137,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G60" s="4"/>
-      <c r="H60" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I60" s="7"/>
+      <c r="H60" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I60" s="9"/>
     </row>
     <row r="61" spans="2:14">
       <c r="B61" s="2">
@@ -2422,11 +3159,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G61" s="4"/>
-      <c r="H61" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I61" s="7"/>
+      <c r="H61" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I61" s="9"/>
     </row>
     <row r="62" spans="2:14">
       <c r="B62" s="2">
@@ -2444,11 +3181,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G62" s="4"/>
-      <c r="H62" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I62" s="7"/>
+      <c r="H62" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I62" s="9"/>
     </row>
     <row r="63" spans="2:14">
       <c r="B63" s="2">
@@ -2466,11 +3203,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G63" s="4"/>
-      <c r="H63" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I63" s="7"/>
+      <c r="H63" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I63" s="9"/>
     </row>
     <row r="64" spans="2:14">
       <c r="B64" s="2">
@@ -2488,11 +3225,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G64" s="4"/>
-      <c r="H64" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I64" s="7"/>
+      <c r="H64" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I64" s="9"/>
     </row>
     <row r="65" spans="2:9">
       <c r="B65" s="2">
@@ -2510,11 +3247,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G65" s="4"/>
-      <c r="H65" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I65" s="7"/>
+      <c r="H65" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I65" s="9"/>
     </row>
     <row r="66" spans="2:9">
       <c r="B66" s="2">
@@ -2532,11 +3269,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G66" s="4"/>
-      <c r="H66" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I66" s="7"/>
+      <c r="H66" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I66" s="9"/>
     </row>
     <row r="67" spans="2:9">
       <c r="B67" s="2">
@@ -2554,11 +3291,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G67" s="4"/>
-      <c r="H67" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I67" s="7"/>
+      <c r="H67" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I67" s="9"/>
     </row>
     <row r="68" spans="2:9">
       <c r="B68" s="2">
@@ -2576,11 +3313,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G68" s="4"/>
-      <c r="H68" s="7" t="e">
+      <c r="H68" s="9" t="e">
         <f t="shared" ref="H68:H102" si="3">1.945*10^-10*F68^1.5/G68</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I68" s="7"/>
+      <c r="I68" s="9"/>
     </row>
     <row r="69" spans="2:9">
       <c r="B69" s="2">
@@ -2598,11 +3335,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G69" s="4"/>
-      <c r="H69" s="7" t="e">
+      <c r="H69" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I69" s="7"/>
+      <c r="I69" s="9"/>
     </row>
     <row r="70" spans="2:9">
       <c r="B70" s="2">
@@ -2620,11 +3357,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G70" s="4"/>
-      <c r="H70" s="7" t="e">
+      <c r="H70" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I70" s="7"/>
+      <c r="I70" s="9"/>
     </row>
     <row r="71" spans="2:9">
       <c r="B71" s="2">
@@ -2642,11 +3379,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G71" s="4"/>
-      <c r="H71" s="7" t="e">
+      <c r="H71" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I71" s="7"/>
+      <c r="I71" s="9"/>
     </row>
     <row r="72" spans="2:9">
       <c r="B72" s="2">
@@ -2664,11 +3401,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G72" s="4"/>
-      <c r="H72" s="7" t="e">
+      <c r="H72" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I72" s="7"/>
+      <c r="I72" s="9"/>
     </row>
     <row r="73" spans="2:9">
       <c r="B73" s="2">
@@ -2686,11 +3423,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G73" s="4"/>
-      <c r="H73" s="7" t="e">
+      <c r="H73" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I73" s="7"/>
+      <c r="I73" s="9"/>
     </row>
     <row r="74" spans="2:9">
       <c r="B74" s="2">
@@ -2708,11 +3445,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G74" s="4"/>
-      <c r="H74" s="7" t="e">
+      <c r="H74" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I74" s="7"/>
+      <c r="I74" s="9"/>
     </row>
     <row r="75" spans="2:9">
       <c r="B75" s="2">
@@ -2730,11 +3467,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G75" s="4"/>
-      <c r="H75" s="7" t="e">
+      <c r="H75" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I75" s="7"/>
+      <c r="I75" s="9"/>
     </row>
     <row r="76" spans="2:9">
       <c r="B76" s="2">
@@ -2752,11 +3489,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G76" s="4"/>
-      <c r="H76" s="7" t="e">
+      <c r="H76" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I76" s="7"/>
+      <c r="I76" s="9"/>
     </row>
     <row r="77" spans="2:9">
       <c r="B77" s="2">
@@ -2774,11 +3511,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G77" s="4"/>
-      <c r="H77" s="7" t="e">
+      <c r="H77" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I77" s="7"/>
+      <c r="I77" s="9"/>
     </row>
     <row r="78" spans="2:9">
       <c r="B78" s="2">
@@ -2796,11 +3533,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G78" s="4"/>
-      <c r="H78" s="7" t="e">
+      <c r="H78" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I78" s="7"/>
+      <c r="I78" s="9"/>
     </row>
     <row r="79" spans="2:9">
       <c r="B79" s="2">
@@ -2818,11 +3555,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G79" s="4"/>
-      <c r="H79" s="7" t="e">
+      <c r="H79" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I79" s="7"/>
+      <c r="I79" s="9"/>
     </row>
     <row r="80" spans="2:9">
       <c r="B80" s="2">
@@ -2840,11 +3577,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G80" s="4"/>
-      <c r="H80" s="7" t="e">
+      <c r="H80" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I80" s="7"/>
+      <c r="I80" s="9"/>
     </row>
     <row r="81" spans="2:9">
       <c r="B81" s="2">
@@ -2862,11 +3599,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G81" s="4"/>
-      <c r="H81" s="7" t="e">
+      <c r="H81" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I81" s="7"/>
+      <c r="I81" s="9"/>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="2">
@@ -2884,11 +3621,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G82" s="4"/>
-      <c r="H82" s="7" t="e">
+      <c r="H82" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I82" s="7"/>
+      <c r="I82" s="9"/>
     </row>
     <row r="83" spans="2:9">
       <c r="B83" s="2">
@@ -2906,11 +3643,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G83" s="4"/>
-      <c r="H83" s="7" t="e">
+      <c r="H83" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I83" s="7"/>
+      <c r="I83" s="9"/>
     </row>
     <row r="84" spans="2:9">
       <c r="B84" s="2">
@@ -2928,11 +3665,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G84" s="4"/>
-      <c r="H84" s="7" t="e">
+      <c r="H84" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I84" s="7"/>
+      <c r="I84" s="9"/>
     </row>
     <row r="85" spans="2:9">
       <c r="B85" s="2">
@@ -2950,11 +3687,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G85" s="4"/>
-      <c r="H85" s="7" t="e">
+      <c r="H85" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I85" s="7"/>
+      <c r="I85" s="9"/>
     </row>
     <row r="86" spans="2:9">
       <c r="B86" s="2">
@@ -2972,11 +3709,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G86" s="4"/>
-      <c r="H86" s="7" t="e">
+      <c r="H86" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I86" s="7"/>
+      <c r="I86" s="9"/>
     </row>
     <row r="87" spans="2:9">
       <c r="B87" s="2">
@@ -2994,11 +3731,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G87" s="4"/>
-      <c r="H87" s="7" t="e">
+      <c r="H87" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I87" s="7"/>
+      <c r="I87" s="9"/>
     </row>
     <row r="88" spans="2:9">
       <c r="B88" s="2">
@@ -3016,11 +3753,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G88" s="4"/>
-      <c r="H88" s="7" t="e">
+      <c r="H88" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I88" s="7"/>
+      <c r="I88" s="9"/>
     </row>
     <row r="89" spans="2:9">
       <c r="B89" s="2">
@@ -3038,11 +3775,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G89" s="4"/>
-      <c r="H89" s="7" t="e">
+      <c r="H89" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I89" s="7"/>
+      <c r="I89" s="9"/>
     </row>
     <row r="90" spans="2:9">
       <c r="B90" s="2">
@@ -3060,11 +3797,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G90" s="4"/>
-      <c r="H90" s="7" t="e">
+      <c r="H90" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I90" s="7"/>
+      <c r="I90" s="9"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" s="2">
@@ -3082,11 +3819,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G91" s="4"/>
-      <c r="H91" s="7" t="e">
+      <c r="H91" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I91" s="7"/>
+      <c r="I91" s="9"/>
     </row>
     <row r="92" spans="2:9">
       <c r="B92" s="2">
@@ -3104,11 +3841,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G92" s="4"/>
-      <c r="H92" s="7" t="e">
+      <c r="H92" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I92" s="7"/>
+      <c r="I92" s="9"/>
     </row>
     <row r="93" spans="2:9">
       <c r="B93" s="2">
@@ -3126,11 +3863,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G93" s="4"/>
-      <c r="H93" s="7" t="e">
+      <c r="H93" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I93" s="7"/>
+      <c r="I93" s="9"/>
     </row>
     <row r="94" spans="2:9">
       <c r="B94" s="2">
@@ -3148,11 +3885,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G94" s="4"/>
-      <c r="H94" s="7" t="e">
+      <c r="H94" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I94" s="7"/>
+      <c r="I94" s="9"/>
     </row>
     <row r="95" spans="2:9">
       <c r="B95" s="2">
@@ -3170,11 +3907,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="7" t="e">
+      <c r="H95" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I95" s="7"/>
+      <c r="I95" s="9"/>
     </row>
     <row r="96" spans="2:9">
       <c r="B96" s="2">
@@ -3192,11 +3929,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G96" s="4"/>
-      <c r="H96" s="7" t="e">
+      <c r="H96" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I96" s="7"/>
+      <c r="I96" s="9"/>
     </row>
     <row r="97" spans="2:9">
       <c r="B97" s="2">
@@ -3214,11 +3951,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G97" s="4"/>
-      <c r="H97" s="7" t="e">
+      <c r="H97" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I97" s="7"/>
+      <c r="I97" s="9"/>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="2">
@@ -3236,11 +3973,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G98" s="4"/>
-      <c r="H98" s="7" t="e">
+      <c r="H98" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I98" s="7"/>
+      <c r="I98" s="9"/>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="2">
@@ -3258,11 +3995,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G99" s="4"/>
-      <c r="H99" s="7" t="e">
+      <c r="H99" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I99" s="7"/>
+      <c r="I99" s="9"/>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="2">
@@ -3280,11 +4017,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G100" s="4"/>
-      <c r="H100" s="7" t="e">
+      <c r="H100" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I100" s="7"/>
+      <c r="I100" s="9"/>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="2">
@@ -3302,11 +4039,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G101" s="4"/>
-      <c r="H101" s="7" t="e">
+      <c r="H101" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I101" s="7"/>
+      <c r="I101" s="9"/>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="2">
@@ -3324,61 +4061,96 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G102" s="4"/>
-      <c r="H102" s="7" t="e">
+      <c r="H102" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I102" s="7"/>
+      <c r="I102" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="153">
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H79:I79"/>
     <mergeCell ref="H98:I98"/>
     <mergeCell ref="H99:I99"/>
     <mergeCell ref="H100:I100"/>
@@ -3403,91 +4175,57 @@
     <mergeCell ref="H91:I91"/>
     <mergeCell ref="H80:I80"/>
     <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="L48:M48"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
+++ b/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\school\one down\普物實驗\6 密立根油滴實驗\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D.tuy\Documents\GitHub\school\one down\普物實驗\6 密立根油滴實驗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{776E5D79-157E-46E9-90A6-4DBCB5DC7394}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5D72BC-28A4-463B-A585-D37A22C4DDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -20,23 +20,7 @@
     <definedName name="_xlchart.v1.1" hidden="1">工作表1!$L$3:$L$52</definedName>
     <definedName name="_xlchart.v1.10" hidden="1">工作表1!$N$2</definedName>
     <definedName name="_xlchart.v1.11" hidden="1">工作表1!$N$3:$N$52</definedName>
-    <definedName name="_xlchart.v1.12" hidden="1">工作表1!$L$2</definedName>
-    <definedName name="_xlchart.v1.13" hidden="1">工作表1!$L$3:$L$52</definedName>
-    <definedName name="_xlchart.v1.14" hidden="1">工作表1!$M$2</definedName>
-    <definedName name="_xlchart.v1.15" hidden="1">工作表1!$M$3:$M$52</definedName>
-    <definedName name="_xlchart.v1.16" hidden="1">工作表1!$N$2</definedName>
-    <definedName name="_xlchart.v1.17" hidden="1">工作表1!$N$3:$N$52</definedName>
-    <definedName name="_xlchart.v1.18" hidden="1">工作表1!$L$2</definedName>
-    <definedName name="_xlchart.v1.19" hidden="1">工作表1!$L$3:$L$52</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">工作表1!$M$2</definedName>
-    <definedName name="_xlchart.v1.20" hidden="1">工作表1!$M$2</definedName>
-    <definedName name="_xlchart.v1.21" hidden="1">工作表1!$M$3:$M$52</definedName>
-    <definedName name="_xlchart.v1.22" hidden="1">工作表1!$N$2</definedName>
-    <definedName name="_xlchart.v1.23" hidden="1">工作表1!$N$3:$N$52</definedName>
-    <definedName name="_xlchart.v1.24" hidden="1">工作表1!$H$3:$H$52</definedName>
-    <definedName name="_xlchart.v1.25" hidden="1">工作表1!$I$3:$I$52</definedName>
-    <definedName name="_xlchart.v1.26" hidden="1">工作表1!$H$3:$H$52</definedName>
-    <definedName name="_xlchart.v1.27" hidden="1">工作表1!$I$3:$I$52</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">工作表1!$M$3:$M$52</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">工作表1!$N$2</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">工作表1!$N$3:$N$52</definedName>
@@ -219,13 +203,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -275,6 +259,11 @@
               <cx:v>區間</cx:v>
             </cx:txData>
           </cx:tx>
+          <cx:spPr>
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+          </cx:spPr>
           <cx:dataId val="0"/>
           <cx:layoutPr>
             <cx:binning intervalClosed="r"/>
@@ -871,16 +860,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>447477</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>37306</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>435570</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>144461</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>177602</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>161131</xdr:rowOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>185820</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>65880</xdr:rowOff>
     </xdr:to>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" Requires="cx1">
@@ -916,8 +905,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="10319743" y="5494337"/>
-              <a:ext cx="4572000" cy="2743200"/>
+              <a:off x="9651008" y="2168524"/>
+              <a:ext cx="4608000" cy="2552700"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1268,13 +1257,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3419739-BEEB-4B53-8EC5-6DC56A0166CA}">
   <dimension ref="B2:N102"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
-    <col min="2" max="2" width="11.81640625" customWidth="1"/>
+    <col min="2" max="2" width="11.77734375" customWidth="1"/>
     <col min="3" max="3" width="9" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.453125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.1796875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1297,10 +1286,10 @@
       <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="9"/>
+      <c r="I2" s="7"/>
       <c r="L2" s="8" t="s">
         <v>5</v>
       </c>
@@ -1329,15 +1318,15 @@
       <c r="G3" s="5">
         <v>72.3</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="7">
         <f>1.945*10^-10*F3^1.5/G3</f>
         <v>1.8449053158903017E-19</v>
       </c>
-      <c r="I3" s="9"/>
-      <c r="L3" s="7">
+      <c r="I3" s="7"/>
+      <c r="L3" s="9">
         <v>9.9999999999999995E-21</v>
       </c>
-      <c r="M3" s="7"/>
+      <c r="M3" s="9"/>
       <c r="N3" s="1">
         <f t="array" ref="N3:N52">FREQUENCY(H3:I52,L3:M52)</f>
         <v>0</v>
@@ -1363,15 +1352,15 @@
       <c r="G4" s="5">
         <v>168.6</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="7">
         <f t="shared" ref="H4:H67" si="1">1.945*10^-10*F4^1.5/G4</f>
         <v>4.3490105195356502E-19</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="L4" s="7">
+      <c r="I4" s="7"/>
+      <c r="L4" s="9">
         <v>1.9999999999999999E-20</v>
       </c>
-      <c r="M4" s="7"/>
+      <c r="M4" s="9"/>
       <c r="N4" s="1">
         <v>0</v>
       </c>
@@ -1396,15 +1385,15 @@
       <c r="G5" s="5">
         <v>62.6</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="7">
         <f t="shared" si="1"/>
         <v>4.2144171456566916E-19</v>
       </c>
-      <c r="I5" s="9"/>
-      <c r="L5" s="7">
+      <c r="I5" s="7"/>
+      <c r="L5" s="9">
         <v>3.0000000000000003E-20</v>
       </c>
-      <c r="M5" s="7"/>
+      <c r="M5" s="9"/>
       <c r="N5" s="1">
         <v>0</v>
       </c>
@@ -1429,15 +1418,15 @@
       <c r="G6" s="5">
         <v>68.599999999999994</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="7">
         <f t="shared" si="1"/>
         <v>3.6510923183134183E-19</v>
       </c>
-      <c r="I6" s="9"/>
-      <c r="L6" s="7">
+      <c r="I6" s="7"/>
+      <c r="L6" s="9">
         <v>3.9999999999999998E-20</v>
       </c>
-      <c r="M6" s="7"/>
+      <c r="M6" s="9"/>
       <c r="N6" s="1">
         <v>1</v>
       </c>
@@ -1462,15 +1451,15 @@
       <c r="G7" s="5">
         <v>284.2</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="7">
         <f t="shared" si="1"/>
         <v>7.1215768734266231E-19</v>
       </c>
-      <c r="I7" s="9"/>
-      <c r="L7" s="7">
+      <c r="I7" s="7"/>
+      <c r="L7" s="9">
         <v>4.9999999999999999E-20</v>
       </c>
-      <c r="M7" s="7"/>
+      <c r="M7" s="9"/>
       <c r="N7" s="1">
         <v>2</v>
       </c>
@@ -1495,15 +1484,15 @@
       <c r="G8" s="5">
         <v>351.7</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="7">
         <f t="shared" si="1"/>
         <v>5.0659365601111741E-19</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="L8" s="7">
+      <c r="I8" s="7"/>
+      <c r="L8" s="9">
         <v>6.0000000000000006E-20</v>
       </c>
-      <c r="M8" s="7"/>
+      <c r="M8" s="9"/>
       <c r="N8" s="1">
         <v>0</v>
       </c>
@@ -1528,15 +1517,15 @@
       <c r="G9" s="5">
         <v>126</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="7">
         <f t="shared" si="1"/>
         <v>3.339529675490588E-19</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="L9" s="7">
+      <c r="I9" s="7"/>
+      <c r="L9" s="9">
         <v>7.0000000000000001E-20</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="9"/>
       <c r="N9" s="1">
         <v>3</v>
       </c>
@@ -1561,15 +1550,15 @@
       <c r="G10" s="5">
         <v>120.1</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="7">
         <f t="shared" si="1"/>
         <v>3.971592840015501E-19</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="L10" s="7">
+      <c r="I10" s="7"/>
+      <c r="L10" s="9">
         <v>7.9999999999999996E-20</v>
       </c>
-      <c r="M10" s="7"/>
+      <c r="M10" s="9"/>
       <c r="N10" s="1">
         <v>2</v>
       </c>
@@ -1594,15 +1583,15 @@
       <c r="G11" s="5">
         <v>170.8</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="7">
         <f t="shared" si="1"/>
         <v>3.6812516124506652E-19</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="L11" s="7">
+      <c r="I11" s="7"/>
+      <c r="L11" s="9">
         <v>9.0000000000000003E-20</v>
       </c>
-      <c r="M11" s="7"/>
+      <c r="M11" s="9"/>
       <c r="N11" s="1">
         <v>1</v>
       </c>
@@ -1627,15 +1616,15 @@
       <c r="G12" s="5">
         <v>88.4</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="7">
         <f t="shared" si="1"/>
         <v>1.5758025146171712E-19</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="L12" s="7">
+      <c r="I12" s="7"/>
+      <c r="L12" s="9">
         <v>9.9999999999999998E-20</v>
       </c>
-      <c r="M12" s="7"/>
+      <c r="M12" s="9"/>
       <c r="N12" s="1">
         <v>1</v>
       </c>
@@ -1660,15 +1649,15 @@
       <c r="G13" s="5">
         <v>126.6</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="7">
         <f t="shared" si="1"/>
         <v>4.4240984732649361E-19</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="L13" s="7">
+      <c r="I13" s="7"/>
+      <c r="L13" s="9">
         <v>1.0999999999999999E-19</v>
       </c>
-      <c r="M13" s="7"/>
+      <c r="M13" s="9"/>
       <c r="N13" s="1">
         <v>2</v>
       </c>
@@ -1693,15 +1682,15 @@
       <c r="G14" s="5">
         <v>128.4</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="7">
         <f t="shared" si="1"/>
         <v>4.1131264461271426E-19</v>
       </c>
-      <c r="I14" s="9"/>
-      <c r="L14" s="7">
+      <c r="I14" s="7"/>
+      <c r="L14" s="9">
         <v>1.2000000000000001E-19</v>
       </c>
-      <c r="M14" s="7"/>
+      <c r="M14" s="9"/>
       <c r="N14" s="1">
         <v>0</v>
       </c>
@@ -1726,15 +1715,15 @@
       <c r="G15" s="5">
         <v>41.9</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="7">
         <f t="shared" si="1"/>
         <v>3.0461654514538201E-19</v>
       </c>
-      <c r="I15" s="9"/>
-      <c r="L15" s="7">
+      <c r="I15" s="7"/>
+      <c r="L15" s="9">
         <v>1.3000000000000001E-19</v>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15" s="9"/>
       <c r="N15" s="1">
         <v>0</v>
       </c>
@@ -1759,15 +1748,15 @@
       <c r="G16" s="5">
         <v>83.9</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="7">
         <f t="shared" si="1"/>
         <v>3.9831346048250973E-19</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="L16" s="7">
+      <c r="I16" s="7"/>
+      <c r="L16" s="9">
         <v>1.4E-19</v>
       </c>
-      <c r="M16" s="7"/>
+      <c r="M16" s="9"/>
       <c r="N16" s="1">
         <v>1</v>
       </c>
@@ -1792,15 +1781,15 @@
       <c r="G17" s="5">
         <v>173.6</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="7">
         <f t="shared" si="1"/>
         <v>1.6678483768588152E-19</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="L17" s="7">
+      <c r="I17" s="7"/>
+      <c r="L17" s="9">
         <v>1.5E-19</v>
       </c>
-      <c r="M17" s="7"/>
+      <c r="M17" s="9"/>
       <c r="N17" s="1">
         <v>0</v>
       </c>
@@ -1825,15 +1814,15 @@
       <c r="G18" s="5">
         <v>232.8</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="7">
         <f t="shared" si="1"/>
         <v>2.120275636869835E-19</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="L18" s="7">
+      <c r="I18" s="7"/>
+      <c r="L18" s="9">
         <v>1.5999999999999999E-19</v>
       </c>
-      <c r="M18" s="7"/>
+      <c r="M18" s="9"/>
       <c r="N18" s="1">
         <v>2</v>
       </c>
@@ -1858,15 +1847,15 @@
       <c r="G19" s="5">
         <v>115.9</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="7">
         <f t="shared" si="1"/>
         <v>1.7488298802142485E-19</v>
       </c>
-      <c r="I19" s="9"/>
-      <c r="L19" s="7">
+      <c r="I19" s="7"/>
+      <c r="L19" s="9">
         <v>1.7000000000000001E-19</v>
       </c>
-      <c r="M19" s="7"/>
+      <c r="M19" s="9"/>
       <c r="N19" s="1">
         <v>4</v>
       </c>
@@ -1891,15 +1880,15 @@
       <c r="G20" s="5">
         <v>69.599999999999994</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="7">
         <f t="shared" si="1"/>
         <v>2.455034668682092E-19</v>
       </c>
-      <c r="I20" s="9"/>
-      <c r="L20" s="7">
+      <c r="I20" s="7"/>
+      <c r="L20" s="9">
         <v>1.8000000000000001E-19</v>
       </c>
-      <c r="M20" s="7"/>
+      <c r="M20" s="9"/>
       <c r="N20" s="1">
         <v>1</v>
       </c>
@@ -1924,15 +1913,15 @@
       <c r="G21" s="5">
         <v>211.8</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="7">
         <f t="shared" si="1"/>
         <v>1.5384584720296341E-19</v>
       </c>
-      <c r="I21" s="9"/>
-      <c r="L21" s="7">
+      <c r="I21" s="7"/>
+      <c r="L21" s="9">
         <v>1.9E-19</v>
       </c>
-      <c r="M21" s="7"/>
+      <c r="M21" s="9"/>
       <c r="N21" s="1">
         <v>2</v>
       </c>
@@ -1957,15 +1946,15 @@
       <c r="G22" s="5">
         <v>225.3</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="7">
         <f t="shared" si="1"/>
         <v>7.8498587920631624E-19</v>
       </c>
-      <c r="I22" s="9"/>
-      <c r="L22" s="7">
+      <c r="I22" s="7"/>
+      <c r="L22" s="9">
         <v>2E-19</v>
       </c>
-      <c r="M22" s="7"/>
+      <c r="M22" s="9"/>
       <c r="N22" s="1">
         <v>0</v>
       </c>
@@ -1990,15 +1979,15 @@
       <c r="G23" s="5">
         <v>42.2</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="7">
         <f t="shared" si="1"/>
         <v>1.4548270972574926E-18</v>
       </c>
-      <c r="I23" s="9"/>
-      <c r="L23" s="7">
+      <c r="I23" s="7"/>
+      <c r="L23" s="9">
         <v>2.0999999999999999E-19</v>
       </c>
-      <c r="M23" s="7"/>
+      <c r="M23" s="9"/>
       <c r="N23" s="1">
         <v>1</v>
       </c>
@@ -2023,15 +2012,15 @@
       <c r="G24" s="5">
         <v>92.9</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="7">
         <f t="shared" si="1"/>
         <v>1.6442393256488777E-19</v>
       </c>
-      <c r="I24" s="9"/>
-      <c r="L24" s="7">
+      <c r="I24" s="7"/>
+      <c r="L24" s="9">
         <v>2.1999999999999998E-19</v>
       </c>
-      <c r="M24" s="7"/>
+      <c r="M24" s="9"/>
       <c r="N24" s="1">
         <v>1</v>
       </c>
@@ -2056,15 +2045,15 @@
       <c r="G25" s="5">
         <v>72.900000000000006</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="7">
         <f t="shared" si="1"/>
         <v>1.6857858253870438E-19</v>
       </c>
-      <c r="I25" s="9"/>
-      <c r="L25" s="7">
+      <c r="I25" s="7"/>
+      <c r="L25" s="9">
         <v>2.2999999999999998E-19</v>
       </c>
-      <c r="M25" s="7"/>
+      <c r="M25" s="9"/>
       <c r="N25" s="1">
         <v>1</v>
       </c>
@@ -2089,15 +2078,15 @@
       <c r="G26" s="5">
         <v>288.10000000000002</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="7">
         <f t="shared" si="1"/>
         <v>4.9794532621128721E-20</v>
       </c>
-      <c r="I26" s="9"/>
-      <c r="L26" s="7">
+      <c r="I26" s="7"/>
+      <c r="L26" s="9">
         <v>2.4000000000000002E-19</v>
       </c>
-      <c r="M26" s="7"/>
+      <c r="M26" s="9"/>
       <c r="N26" s="1">
         <v>1</v>
       </c>
@@ -2122,15 +2111,15 @@
       <c r="G27" s="5">
         <v>227.7</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="7">
         <f t="shared" si="1"/>
         <v>1.0944934037775462E-19</v>
       </c>
-      <c r="I27" s="9"/>
-      <c r="L27" s="7">
+      <c r="I27" s="7"/>
+      <c r="L27" s="9">
         <v>2.5000000000000002E-19</v>
       </c>
-      <c r="M27" s="7"/>
+      <c r="M27" s="9"/>
       <c r="N27" s="1">
         <v>1</v>
       </c>
@@ -2155,15 +2144,15 @@
       <c r="G28" s="5">
         <v>236.3</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="7">
         <f t="shared" si="1"/>
         <v>6.2382768602547688E-20</v>
       </c>
-      <c r="I28" s="9"/>
-      <c r="L28" s="7">
+      <c r="I28" s="7"/>
+      <c r="L28" s="9">
         <v>2.6000000000000001E-19</v>
       </c>
-      <c r="M28" s="7"/>
+      <c r="M28" s="9"/>
       <c r="N28" s="1">
         <v>0</v>
       </c>
@@ -2188,15 +2177,15 @@
       <c r="G29" s="5">
         <v>138.4</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="7">
         <f t="shared" si="1"/>
         <v>1.3027476717986452E-19</v>
       </c>
-      <c r="I29" s="9"/>
-      <c r="L29" s="7">
+      <c r="I29" s="7"/>
+      <c r="L29" s="9">
         <v>2.7000000000000001E-19</v>
       </c>
-      <c r="M29" s="7"/>
+      <c r="M29" s="9"/>
       <c r="N29" s="1">
         <v>0</v>
       </c>
@@ -2221,15 +2210,15 @@
       <c r="G30" s="5">
         <v>134.5</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="7">
         <f t="shared" si="1"/>
         <v>9.05287682212827E-19</v>
       </c>
-      <c r="I30" s="9"/>
-      <c r="L30" s="7">
+      <c r="I30" s="7"/>
+      <c r="L30" s="9">
         <v>2.8E-19</v>
       </c>
-      <c r="M30" s="7"/>
+      <c r="M30" s="9"/>
       <c r="N30" s="1">
         <v>1</v>
       </c>
@@ -2254,15 +2243,15 @@
       <c r="G31" s="5">
         <v>111.2</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="7">
         <f t="shared" si="1"/>
         <v>1.835500131871435E-19</v>
       </c>
-      <c r="I31" s="9"/>
-      <c r="L31" s="7">
+      <c r="I31" s="7"/>
+      <c r="L31" s="9">
         <v>2.9E-19</v>
       </c>
-      <c r="M31" s="7"/>
+      <c r="M31" s="9"/>
       <c r="N31" s="1">
         <v>1</v>
       </c>
@@ -2287,15 +2276,15 @@
       <c r="G32" s="5">
         <v>247.1</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="7">
         <f t="shared" si="1"/>
         <v>2.0923481425821882E-19</v>
       </c>
-      <c r="I32" s="9"/>
-      <c r="L32" s="7">
+      <c r="I32" s="7"/>
+      <c r="L32" s="9">
         <v>2.9999999999999999E-19</v>
       </c>
-      <c r="M32" s="7"/>
+      <c r="M32" s="9"/>
       <c r="N32" s="1">
         <v>0</v>
       </c>
@@ -2320,15 +2309,15 @@
       <c r="G33" s="5">
         <v>169</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="7">
         <f t="shared" si="1"/>
         <v>4.4662320015468356E-19</v>
       </c>
-      <c r="I33" s="9"/>
-      <c r="L33" s="7">
+      <c r="I33" s="7"/>
+      <c r="L33" s="9">
         <v>3.0999999999999999E-19</v>
       </c>
-      <c r="M33" s="7"/>
+      <c r="M33" s="9"/>
       <c r="N33" s="1">
         <v>1</v>
       </c>
@@ -2353,15 +2342,15 @@
       <c r="G34" s="5">
         <v>272.8</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="7">
         <f t="shared" si="1"/>
         <v>4.3179864400352903E-20</v>
       </c>
-      <c r="I34" s="9"/>
-      <c r="L34" s="7">
+      <c r="I34" s="7"/>
+      <c r="L34" s="9">
         <v>3.1999999999999998E-19</v>
       </c>
-      <c r="M34" s="7"/>
+      <c r="M34" s="9"/>
       <c r="N34" s="1">
         <v>0</v>
       </c>
@@ -2386,15 +2375,15 @@
       <c r="G35" s="5">
         <v>50.9</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="7">
         <f t="shared" si="1"/>
         <v>2.8380061566768923E-19</v>
       </c>
-      <c r="I35" s="9"/>
-      <c r="L35" s="7">
+      <c r="I35" s="7"/>
+      <c r="L35" s="9">
         <v>3.2999999999999998E-19</v>
       </c>
-      <c r="M35" s="7"/>
+      <c r="M35" s="9"/>
       <c r="N35" s="1">
         <v>0</v>
       </c>
@@ -2419,15 +2408,15 @@
       <c r="G36" s="5">
         <v>170.8</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="7">
         <f t="shared" si="1"/>
         <v>3.6812516124506652E-19</v>
       </c>
-      <c r="I36" s="9"/>
-      <c r="L36" s="7">
+      <c r="I36" s="7"/>
+      <c r="L36" s="9">
         <v>3.4000000000000002E-19</v>
       </c>
-      <c r="M36" s="7"/>
+      <c r="M36" s="9"/>
       <c r="N36" s="1">
         <v>1</v>
       </c>
@@ -2452,15 +2441,15 @@
       <c r="G37" s="5">
         <v>174.5</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="7">
         <f t="shared" si="1"/>
         <v>7.8812384156677962E-20</v>
       </c>
-      <c r="I37" s="9"/>
-      <c r="L37" s="7">
+      <c r="I37" s="7"/>
+      <c r="L37" s="9">
         <v>3.5000000000000002E-19</v>
       </c>
-      <c r="M37" s="7"/>
+      <c r="M37" s="9"/>
       <c r="N37" s="1">
         <v>0</v>
       </c>
@@ -2485,15 +2474,15 @@
       <c r="G38" s="5">
         <v>123.9</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="7">
         <f t="shared" si="1"/>
         <v>1.0515635189613713E-19</v>
       </c>
-      <c r="I38" s="9"/>
-      <c r="L38" s="7">
+      <c r="I38" s="7"/>
+      <c r="L38" s="9">
         <v>3.6000000000000001E-19</v>
       </c>
-      <c r="M38" s="7"/>
+      <c r="M38" s="9"/>
       <c r="N38" s="1">
         <v>0</v>
       </c>
@@ -2518,15 +2507,15 @@
       <c r="G39" s="5">
         <v>345.3</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="7">
         <f t="shared" si="1"/>
         <v>6.8451844141021412E-20</v>
       </c>
-      <c r="I39" s="9"/>
-      <c r="L39" s="7">
+      <c r="I39" s="7"/>
+      <c r="L39" s="9">
         <v>3.7000000000000001E-19</v>
       </c>
-      <c r="M39" s="7"/>
+      <c r="M39" s="9"/>
       <c r="N39" s="1">
         <v>4</v>
       </c>
@@ -2551,15 +2540,15 @@
       <c r="G40" s="5">
         <v>213.2</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="7">
         <f t="shared" si="1"/>
         <v>1.6202722663136051E-19</v>
       </c>
-      <c r="I40" s="9"/>
-      <c r="L40" s="7">
+      <c r="I40" s="7"/>
+      <c r="L40" s="9">
         <v>3.8E-19</v>
       </c>
-      <c r="M40" s="7"/>
+      <c r="M40" s="9"/>
       <c r="N40" s="1">
         <v>0</v>
       </c>
@@ -2584,15 +2573,15 @@
       <c r="G41" s="5">
         <v>253.3</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="7">
         <f t="shared" si="1"/>
         <v>4.5059327617437475E-19</v>
       </c>
-      <c r="I41" s="9"/>
-      <c r="L41" s="7">
+      <c r="I41" s="7"/>
+      <c r="L41" s="9">
         <v>3.9E-19</v>
       </c>
-      <c r="M41" s="7"/>
+      <c r="M41" s="9"/>
       <c r="N41" s="1">
         <v>0</v>
       </c>
@@ -2617,15 +2606,15 @@
       <c r="G42" s="5">
         <v>169.8</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="7">
         <f t="shared" si="1"/>
         <v>9.193767993870622E-20</v>
       </c>
-      <c r="I42" s="9"/>
-      <c r="L42" s="7">
+      <c r="I42" s="7"/>
+      <c r="L42" s="9">
         <v>3.9999999999999999E-19</v>
       </c>
-      <c r="M42" s="7"/>
+      <c r="M42" s="9"/>
       <c r="N42" s="1">
         <v>2</v>
       </c>
@@ -2650,15 +2639,15 @@
       <c r="G43" s="5">
         <v>332.7</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="7">
         <f t="shared" si="1"/>
         <v>3.5086479332700357E-20</v>
       </c>
-      <c r="I43" s="9"/>
-      <c r="L43" s="7">
+      <c r="I43" s="7"/>
+      <c r="L43" s="9">
         <v>4.0999999999999999E-19</v>
       </c>
-      <c r="M43" s="7"/>
+      <c r="M43" s="9"/>
       <c r="N43" s="1">
         <v>0</v>
       </c>
@@ -2683,15 +2672,15 @@
       <c r="G44" s="5">
         <v>222.6</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="7">
         <f t="shared" si="1"/>
         <v>8.98343828154446E-19</v>
       </c>
-      <c r="I44" s="9"/>
-      <c r="L44" s="7">
+      <c r="I44" s="7"/>
+      <c r="L44" s="9">
         <v>4.1999999999999998E-19</v>
       </c>
-      <c r="M44" s="7"/>
+      <c r="M44" s="9"/>
       <c r="N44" s="1">
         <v>1</v>
       </c>
@@ -2716,15 +2705,15 @@
       <c r="G45" s="5">
         <v>187.8</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="7">
         <f t="shared" si="1"/>
         <v>2.7530310225349235E-19</v>
       </c>
-      <c r="I45" s="9"/>
-      <c r="L45" s="7">
+      <c r="I45" s="7"/>
+      <c r="L45" s="9">
         <v>4.3000000000000002E-19</v>
       </c>
-      <c r="M45" s="7"/>
+      <c r="M45" s="9"/>
       <c r="N45" s="1">
         <v>1</v>
       </c>
@@ -2749,15 +2738,15 @@
       <c r="G46" s="5">
         <v>129.6</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="7">
         <f t="shared" si="1"/>
         <v>2.3205683379361788E-19</v>
       </c>
-      <c r="I46" s="9"/>
-      <c r="L46" s="7">
+      <c r="I46" s="7"/>
+      <c r="L46" s="9">
         <v>4.3999999999999997E-19</v>
       </c>
-      <c r="M46" s="7"/>
+      <c r="M46" s="9"/>
       <c r="N46" s="1">
         <v>1</v>
       </c>
@@ -2782,15 +2771,15 @@
       <c r="G47" s="5">
         <v>336</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="7">
         <f t="shared" si="1"/>
         <v>8.0259432458438495E-20</v>
       </c>
-      <c r="I47" s="9"/>
-      <c r="L47" s="7">
+      <c r="I47" s="7"/>
+      <c r="L47" s="9">
         <v>4.5000000000000001E-19</v>
       </c>
-      <c r="M47" s="7"/>
+      <c r="M47" s="9"/>
       <c r="N47" s="1">
         <v>2</v>
       </c>
@@ -2815,15 +2804,15 @@
       <c r="G48" s="5">
         <v>92</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="7">
         <f t="shared" si="1"/>
         <v>5.0519531504841948E-19</v>
       </c>
-      <c r="I48" s="9"/>
-      <c r="L48" s="7">
+      <c r="I48" s="7"/>
+      <c r="L48" s="9">
         <v>4.5999999999999996E-19</v>
       </c>
-      <c r="M48" s="7"/>
+      <c r="M48" s="9"/>
       <c r="N48" s="1">
         <v>1</v>
       </c>
@@ -2848,15 +2837,15 @@
       <c r="G49" s="5">
         <v>220.3</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="7">
         <f t="shared" si="1"/>
         <v>7.4310122663013932E-20</v>
       </c>
-      <c r="I49" s="9"/>
-      <c r="L49" s="7">
+      <c r="I49" s="7"/>
+      <c r="L49" s="9">
         <v>4.7E-19</v>
       </c>
-      <c r="M49" s="7"/>
+      <c r="M49" s="9"/>
       <c r="N49" s="1">
         <v>0</v>
       </c>
@@ -2881,15 +2870,15 @@
       <c r="G50" s="6">
         <v>170.8</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="7">
         <f t="shared" si="1"/>
         <v>3.6812516124506652E-19</v>
       </c>
-      <c r="I50" s="9"/>
-      <c r="L50" s="7">
+      <c r="I50" s="7"/>
+      <c r="L50" s="9">
         <v>4.8000000000000005E-19</v>
       </c>
-      <c r="M50" s="7"/>
+      <c r="M50" s="9"/>
       <c r="N50" s="1">
         <v>0</v>
       </c>
@@ -2914,15 +2903,15 @@
       <c r="G51" s="5">
         <v>59.7</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="7">
         <f t="shared" si="1"/>
         <v>2.2959328319809843E-19</v>
       </c>
-      <c r="I51" s="9"/>
-      <c r="L51" s="7">
+      <c r="I51" s="7"/>
+      <c r="L51" s="9">
         <v>4.8999999999999999E-19</v>
       </c>
-      <c r="M51" s="7"/>
+      <c r="M51" s="9"/>
       <c r="N51" s="1">
         <v>0</v>
       </c>
@@ -2947,15 +2936,15 @@
       <c r="G52" s="5">
         <v>205.2</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="7">
         <f t="shared" si="1"/>
         <v>6.6841651277123587E-20</v>
       </c>
-      <c r="I52" s="9"/>
-      <c r="L52" s="7">
+      <c r="I52" s="7"/>
+      <c r="L52" s="9">
         <v>5.0000000000000004E-19</v>
       </c>
-      <c r="M52" s="7"/>
+      <c r="M52" s="9"/>
       <c r="N52" s="1">
         <v>0</v>
       </c>
@@ -2976,11 +2965,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G53" s="4"/>
-      <c r="H53" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I53" s="9"/>
+      <c r="H53" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I53" s="7"/>
       <c r="L53" s="8" t="s">
         <v>9</v>
       </c>
@@ -3005,11 +2994,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G54" s="4"/>
-      <c r="H54" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I54" s="9"/>
+      <c r="H54" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I54" s="7"/>
     </row>
     <row r="55" spans="2:14">
       <c r="B55" s="2">
@@ -3027,11 +3016,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G55" s="4"/>
-      <c r="H55" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I55" s="9"/>
+      <c r="H55" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I55" s="7"/>
     </row>
     <row r="56" spans="2:14">
       <c r="B56" s="2">
@@ -3049,11 +3038,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G56" s="4"/>
-      <c r="H56" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I56" s="9"/>
+      <c r="H56" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I56" s="7"/>
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="2">
@@ -3071,11 +3060,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G57" s="4"/>
-      <c r="H57" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I57" s="9"/>
+      <c r="H57" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I57" s="7"/>
     </row>
     <row r="58" spans="2:14">
       <c r="B58" s="2">
@@ -3093,11 +3082,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G58" s="4"/>
-      <c r="H58" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I58" s="9"/>
+      <c r="H58" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I58" s="7"/>
     </row>
     <row r="59" spans="2:14">
       <c r="B59" s="2">
@@ -3115,11 +3104,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G59" s="4"/>
-      <c r="H59" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I59" s="9"/>
+      <c r="H59" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I59" s="7"/>
     </row>
     <row r="60" spans="2:14">
       <c r="B60" s="2">
@@ -3137,11 +3126,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G60" s="4"/>
-      <c r="H60" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I60" s="9"/>
+      <c r="H60" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I60" s="7"/>
     </row>
     <row r="61" spans="2:14">
       <c r="B61" s="2">
@@ -3159,11 +3148,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G61" s="4"/>
-      <c r="H61" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I61" s="9"/>
+      <c r="H61" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I61" s="7"/>
     </row>
     <row r="62" spans="2:14">
       <c r="B62" s="2">
@@ -3181,11 +3170,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G62" s="4"/>
-      <c r="H62" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I62" s="9"/>
+      <c r="H62" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I62" s="7"/>
     </row>
     <row r="63" spans="2:14">
       <c r="B63" s="2">
@@ -3203,11 +3192,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G63" s="4"/>
-      <c r="H63" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I63" s="9"/>
+      <c r="H63" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I63" s="7"/>
     </row>
     <row r="64" spans="2:14">
       <c r="B64" s="2">
@@ -3225,11 +3214,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G64" s="4"/>
-      <c r="H64" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I64" s="9"/>
+      <c r="H64" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I64" s="7"/>
     </row>
     <row r="65" spans="2:9">
       <c r="B65" s="2">
@@ -3247,11 +3236,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G65" s="4"/>
-      <c r="H65" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I65" s="9"/>
+      <c r="H65" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I65" s="7"/>
     </row>
     <row r="66" spans="2:9">
       <c r="B66" s="2">
@@ -3269,11 +3258,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G66" s="4"/>
-      <c r="H66" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I66" s="9"/>
+      <c r="H66" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I66" s="7"/>
     </row>
     <row r="67" spans="2:9">
       <c r="B67" s="2">
@@ -3291,11 +3280,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G67" s="4"/>
-      <c r="H67" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I67" s="9"/>
+      <c r="H67" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I67" s="7"/>
     </row>
     <row r="68" spans="2:9">
       <c r="B68" s="2">
@@ -3313,11 +3302,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G68" s="4"/>
-      <c r="H68" s="9" t="e">
+      <c r="H68" s="7" t="e">
         <f t="shared" ref="H68:H102" si="3">1.945*10^-10*F68^1.5/G68</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I68" s="9"/>
+      <c r="I68" s="7"/>
     </row>
     <row r="69" spans="2:9">
       <c r="B69" s="2">
@@ -3335,11 +3324,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G69" s="4"/>
-      <c r="H69" s="9" t="e">
+      <c r="H69" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I69" s="9"/>
+      <c r="I69" s="7"/>
     </row>
     <row r="70" spans="2:9">
       <c r="B70" s="2">
@@ -3357,11 +3346,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G70" s="4"/>
-      <c r="H70" s="9" t="e">
+      <c r="H70" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I70" s="9"/>
+      <c r="I70" s="7"/>
     </row>
     <row r="71" spans="2:9">
       <c r="B71" s="2">
@@ -3379,11 +3368,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G71" s="4"/>
-      <c r="H71" s="9" t="e">
+      <c r="H71" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I71" s="9"/>
+      <c r="I71" s="7"/>
     </row>
     <row r="72" spans="2:9">
       <c r="B72" s="2">
@@ -3401,11 +3390,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G72" s="4"/>
-      <c r="H72" s="9" t="e">
+      <c r="H72" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I72" s="9"/>
+      <c r="I72" s="7"/>
     </row>
     <row r="73" spans="2:9">
       <c r="B73" s="2">
@@ -3423,11 +3412,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G73" s="4"/>
-      <c r="H73" s="9" t="e">
+      <c r="H73" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I73" s="9"/>
+      <c r="I73" s="7"/>
     </row>
     <row r="74" spans="2:9">
       <c r="B74" s="2">
@@ -3445,11 +3434,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G74" s="4"/>
-      <c r="H74" s="9" t="e">
+      <c r="H74" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I74" s="9"/>
+      <c r="I74" s="7"/>
     </row>
     <row r="75" spans="2:9">
       <c r="B75" s="2">
@@ -3467,11 +3456,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G75" s="4"/>
-      <c r="H75" s="9" t="e">
+      <c r="H75" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I75" s="9"/>
+      <c r="I75" s="7"/>
     </row>
     <row r="76" spans="2:9">
       <c r="B76" s="2">
@@ -3489,11 +3478,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G76" s="4"/>
-      <c r="H76" s="9" t="e">
+      <c r="H76" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I76" s="9"/>
+      <c r="I76" s="7"/>
     </row>
     <row r="77" spans="2:9">
       <c r="B77" s="2">
@@ -3511,11 +3500,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G77" s="4"/>
-      <c r="H77" s="9" t="e">
+      <c r="H77" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I77" s="9"/>
+      <c r="I77" s="7"/>
     </row>
     <row r="78" spans="2:9">
       <c r="B78" s="2">
@@ -3533,11 +3522,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G78" s="4"/>
-      <c r="H78" s="9" t="e">
+      <c r="H78" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I78" s="9"/>
+      <c r="I78" s="7"/>
     </row>
     <row r="79" spans="2:9">
       <c r="B79" s="2">
@@ -3555,11 +3544,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G79" s="4"/>
-      <c r="H79" s="9" t="e">
+      <c r="H79" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I79" s="9"/>
+      <c r="I79" s="7"/>
     </row>
     <row r="80" spans="2:9">
       <c r="B80" s="2">
@@ -3577,11 +3566,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G80" s="4"/>
-      <c r="H80" s="9" t="e">
+      <c r="H80" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I80" s="9"/>
+      <c r="I80" s="7"/>
     </row>
     <row r="81" spans="2:9">
       <c r="B81" s="2">
@@ -3599,11 +3588,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G81" s="4"/>
-      <c r="H81" s="9" t="e">
+      <c r="H81" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I81" s="9"/>
+      <c r="I81" s="7"/>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="2">
@@ -3621,11 +3610,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G82" s="4"/>
-      <c r="H82" s="9" t="e">
+      <c r="H82" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I82" s="9"/>
+      <c r="I82" s="7"/>
     </row>
     <row r="83" spans="2:9">
       <c r="B83" s="2">
@@ -3643,11 +3632,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G83" s="4"/>
-      <c r="H83" s="9" t="e">
+      <c r="H83" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I83" s="9"/>
+      <c r="I83" s="7"/>
     </row>
     <row r="84" spans="2:9">
       <c r="B84" s="2">
@@ -3665,11 +3654,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G84" s="4"/>
-      <c r="H84" s="9" t="e">
+      <c r="H84" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I84" s="9"/>
+      <c r="I84" s="7"/>
     </row>
     <row r="85" spans="2:9">
       <c r="B85" s="2">
@@ -3687,11 +3676,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G85" s="4"/>
-      <c r="H85" s="9" t="e">
+      <c r="H85" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I85" s="9"/>
+      <c r="I85" s="7"/>
     </row>
     <row r="86" spans="2:9">
       <c r="B86" s="2">
@@ -3709,11 +3698,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G86" s="4"/>
-      <c r="H86" s="9" t="e">
+      <c r="H86" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I86" s="9"/>
+      <c r="I86" s="7"/>
     </row>
     <row r="87" spans="2:9">
       <c r="B87" s="2">
@@ -3731,11 +3720,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G87" s="4"/>
-      <c r="H87" s="9" t="e">
+      <c r="H87" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I87" s="9"/>
+      <c r="I87" s="7"/>
     </row>
     <row r="88" spans="2:9">
       <c r="B88" s="2">
@@ -3753,11 +3742,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G88" s="4"/>
-      <c r="H88" s="9" t="e">
+      <c r="H88" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I88" s="9"/>
+      <c r="I88" s="7"/>
     </row>
     <row r="89" spans="2:9">
       <c r="B89" s="2">
@@ -3775,11 +3764,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G89" s="4"/>
-      <c r="H89" s="9" t="e">
+      <c r="H89" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I89" s="9"/>
+      <c r="I89" s="7"/>
     </row>
     <row r="90" spans="2:9">
       <c r="B90" s="2">
@@ -3797,11 +3786,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G90" s="4"/>
-      <c r="H90" s="9" t="e">
+      <c r="H90" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I90" s="9"/>
+      <c r="I90" s="7"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" s="2">
@@ -3819,11 +3808,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G91" s="4"/>
-      <c r="H91" s="9" t="e">
+      <c r="H91" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I91" s="9"/>
+      <c r="I91" s="7"/>
     </row>
     <row r="92" spans="2:9">
       <c r="B92" s="2">
@@ -3841,11 +3830,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G92" s="4"/>
-      <c r="H92" s="9" t="e">
+      <c r="H92" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I92" s="9"/>
+      <c r="I92" s="7"/>
     </row>
     <row r="93" spans="2:9">
       <c r="B93" s="2">
@@ -3863,11 +3852,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G93" s="4"/>
-      <c r="H93" s="9" t="e">
+      <c r="H93" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I93" s="9"/>
+      <c r="I93" s="7"/>
     </row>
     <row r="94" spans="2:9">
       <c r="B94" s="2">
@@ -3885,11 +3874,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G94" s="4"/>
-      <c r="H94" s="9" t="e">
+      <c r="H94" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I94" s="9"/>
+      <c r="I94" s="7"/>
     </row>
     <row r="95" spans="2:9">
       <c r="B95" s="2">
@@ -3907,11 +3896,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="9" t="e">
+      <c r="H95" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I95" s="9"/>
+      <c r="I95" s="7"/>
     </row>
     <row r="96" spans="2:9">
       <c r="B96" s="2">
@@ -3929,11 +3918,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G96" s="4"/>
-      <c r="H96" s="9" t="e">
+      <c r="H96" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I96" s="9"/>
+      <c r="I96" s="7"/>
     </row>
     <row r="97" spans="2:9">
       <c r="B97" s="2">
@@ -3951,11 +3940,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G97" s="4"/>
-      <c r="H97" s="9" t="e">
+      <c r="H97" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I97" s="9"/>
+      <c r="I97" s="7"/>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="2">
@@ -3973,11 +3962,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G98" s="4"/>
-      <c r="H98" s="9" t="e">
+      <c r="H98" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I98" s="9"/>
+      <c r="I98" s="7"/>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="2">
@@ -3995,11 +3984,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G99" s="4"/>
-      <c r="H99" s="9" t="e">
+      <c r="H99" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I99" s="9"/>
+      <c r="I99" s="7"/>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="2">
@@ -4017,11 +4006,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G100" s="4"/>
-      <c r="H100" s="9" t="e">
+      <c r="H100" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I100" s="9"/>
+      <c r="I100" s="7"/>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="2">
@@ -4039,11 +4028,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G101" s="4"/>
-      <c r="H101" s="9" t="e">
+      <c r="H101" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I101" s="9"/>
+      <c r="I101" s="7"/>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="2">
@@ -4061,96 +4050,61 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G102" s="4"/>
-      <c r="H102" s="9" t="e">
+      <c r="H102" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I102" s="9"/>
+      <c r="I102" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="153">
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L12:M12"/>
     <mergeCell ref="H98:I98"/>
     <mergeCell ref="H99:I99"/>
     <mergeCell ref="H100:I100"/>
@@ -4175,53 +4129,88 @@
     <mergeCell ref="H91:I91"/>
     <mergeCell ref="H80:I80"/>
     <mergeCell ref="H81:I81"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="L12:M12"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="L48:M48"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H79:I79"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
+++ b/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
@@ -18,16 +18,10 @@
   <definedNames>
     <definedName name="_xlchart.v1.0" hidden="1">工作表1!$L$2</definedName>
     <definedName name="_xlchart.v1.1" hidden="1">工作表1!$L$3:$L$52</definedName>
-    <definedName name="_xlchart.v1.10" hidden="1">工作表1!$N$2</definedName>
-    <definedName name="_xlchart.v1.11" hidden="1">工作表1!$N$3:$N$52</definedName>
     <definedName name="_xlchart.v1.2" hidden="1">工作表1!$M$2</definedName>
     <definedName name="_xlchart.v1.3" hidden="1">工作表1!$M$3:$M$52</definedName>
     <definedName name="_xlchart.v1.4" hidden="1">工作表1!$N$2</definedName>
     <definedName name="_xlchart.v1.5" hidden="1">工作表1!$N$3:$N$52</definedName>
-    <definedName name="_xlchart.v1.6" hidden="1">工作表1!$L$2</definedName>
-    <definedName name="_xlchart.v1.7" hidden="1">工作表1!$L$3:$L$52</definedName>
-    <definedName name="_xlchart.v1.8" hidden="1">工作表1!$M$2</definedName>
-    <definedName name="_xlchart.v1.9" hidden="1">工作表1!$M$3:$M$52</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -203,13 +197,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -905,8 +899,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="9651008" y="2168524"/>
-              <a:ext cx="4608000" cy="2552700"/>
+              <a:off x="9663390" y="2201861"/>
+              <a:ext cx="4627050" cy="2596039"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -1286,10 +1280,10 @@
       <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="H2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="7"/>
+      <c r="I2" s="9"/>
       <c r="L2" s="8" t="s">
         <v>5</v>
       </c>
@@ -1318,15 +1312,15 @@
       <c r="G3" s="5">
         <v>72.3</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="9">
         <f>1.945*10^-10*F3^1.5/G3</f>
         <v>1.8449053158903017E-19</v>
       </c>
-      <c r="I3" s="7"/>
-      <c r="L3" s="9">
+      <c r="I3" s="9"/>
+      <c r="L3" s="7">
         <v>9.9999999999999995E-21</v>
       </c>
-      <c r="M3" s="9"/>
+      <c r="M3" s="7"/>
       <c r="N3" s="1">
         <f t="array" ref="N3:N52">FREQUENCY(H3:I52,L3:M52)</f>
         <v>0</v>
@@ -1352,15 +1346,15 @@
       <c r="G4" s="5">
         <v>168.6</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="9">
         <f t="shared" ref="H4:H67" si="1">1.945*10^-10*F4^1.5/G4</f>
         <v>4.3490105195356502E-19</v>
       </c>
-      <c r="I4" s="7"/>
-      <c r="L4" s="9">
+      <c r="I4" s="9"/>
+      <c r="L4" s="7">
         <v>1.9999999999999999E-20</v>
       </c>
-      <c r="M4" s="9"/>
+      <c r="M4" s="7"/>
       <c r="N4" s="1">
         <v>0</v>
       </c>
@@ -1385,15 +1379,15 @@
       <c r="G5" s="5">
         <v>62.6</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="9">
         <f t="shared" si="1"/>
         <v>4.2144171456566916E-19</v>
       </c>
-      <c r="I5" s="7"/>
-      <c r="L5" s="9">
+      <c r="I5" s="9"/>
+      <c r="L5" s="7">
         <v>3.0000000000000003E-20</v>
       </c>
-      <c r="M5" s="9"/>
+      <c r="M5" s="7"/>
       <c r="N5" s="1">
         <v>0</v>
       </c>
@@ -1418,15 +1412,15 @@
       <c r="G6" s="5">
         <v>68.599999999999994</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="9">
         <f t="shared" si="1"/>
         <v>3.6510923183134183E-19</v>
       </c>
-      <c r="I6" s="7"/>
-      <c r="L6" s="9">
+      <c r="I6" s="9"/>
+      <c r="L6" s="7">
         <v>3.9999999999999998E-20</v>
       </c>
-      <c r="M6" s="9"/>
+      <c r="M6" s="7"/>
       <c r="N6" s="1">
         <v>1</v>
       </c>
@@ -1451,15 +1445,15 @@
       <c r="G7" s="5">
         <v>284.2</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="9">
         <f t="shared" si="1"/>
         <v>7.1215768734266231E-19</v>
       </c>
-      <c r="I7" s="7"/>
-      <c r="L7" s="9">
+      <c r="I7" s="9"/>
+      <c r="L7" s="7">
         <v>4.9999999999999999E-20</v>
       </c>
-      <c r="M7" s="9"/>
+      <c r="M7" s="7"/>
       <c r="N7" s="1">
         <v>2</v>
       </c>
@@ -1484,15 +1478,15 @@
       <c r="G8" s="5">
         <v>351.7</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="9">
         <f t="shared" si="1"/>
         <v>5.0659365601111741E-19</v>
       </c>
-      <c r="I8" s="7"/>
-      <c r="L8" s="9">
+      <c r="I8" s="9"/>
+      <c r="L8" s="7">
         <v>6.0000000000000006E-20</v>
       </c>
-      <c r="M8" s="9"/>
+      <c r="M8" s="7"/>
       <c r="N8" s="1">
         <v>0</v>
       </c>
@@ -1517,15 +1511,15 @@
       <c r="G9" s="5">
         <v>126</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="9">
         <f t="shared" si="1"/>
         <v>3.339529675490588E-19</v>
       </c>
-      <c r="I9" s="7"/>
-      <c r="L9" s="9">
+      <c r="I9" s="9"/>
+      <c r="L9" s="7">
         <v>7.0000000000000001E-20</v>
       </c>
-      <c r="M9" s="9"/>
+      <c r="M9" s="7"/>
       <c r="N9" s="1">
         <v>3</v>
       </c>
@@ -1550,15 +1544,15 @@
       <c r="G10" s="5">
         <v>120.1</v>
       </c>
-      <c r="H10" s="7">
+      <c r="H10" s="9">
         <f t="shared" si="1"/>
         <v>3.971592840015501E-19</v>
       </c>
-      <c r="I10" s="7"/>
-      <c r="L10" s="9">
+      <c r="I10" s="9"/>
+      <c r="L10" s="7">
         <v>7.9999999999999996E-20</v>
       </c>
-      <c r="M10" s="9"/>
+      <c r="M10" s="7"/>
       <c r="N10" s="1">
         <v>2</v>
       </c>
@@ -1583,15 +1577,15 @@
       <c r="G11" s="5">
         <v>170.8</v>
       </c>
-      <c r="H11" s="7">
+      <c r="H11" s="9">
         <f t="shared" si="1"/>
         <v>3.6812516124506652E-19</v>
       </c>
-      <c r="I11" s="7"/>
-      <c r="L11" s="9">
+      <c r="I11" s="9"/>
+      <c r="L11" s="7">
         <v>9.0000000000000003E-20</v>
       </c>
-      <c r="M11" s="9"/>
+      <c r="M11" s="7"/>
       <c r="N11" s="1">
         <v>1</v>
       </c>
@@ -1616,15 +1610,15 @@
       <c r="G12" s="5">
         <v>88.4</v>
       </c>
-      <c r="H12" s="7">
+      <c r="H12" s="9">
         <f t="shared" si="1"/>
         <v>1.5758025146171712E-19</v>
       </c>
-      <c r="I12" s="7"/>
-      <c r="L12" s="9">
+      <c r="I12" s="9"/>
+      <c r="L12" s="7">
         <v>9.9999999999999998E-20</v>
       </c>
-      <c r="M12" s="9"/>
+      <c r="M12" s="7"/>
       <c r="N12" s="1">
         <v>1</v>
       </c>
@@ -1649,15 +1643,15 @@
       <c r="G13" s="5">
         <v>126.6</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="9">
         <f t="shared" si="1"/>
         <v>4.4240984732649361E-19</v>
       </c>
-      <c r="I13" s="7"/>
-      <c r="L13" s="9">
+      <c r="I13" s="9"/>
+      <c r="L13" s="7">
         <v>1.0999999999999999E-19</v>
       </c>
-      <c r="M13" s="9"/>
+      <c r="M13" s="7"/>
       <c r="N13" s="1">
         <v>2</v>
       </c>
@@ -1682,15 +1676,15 @@
       <c r="G14" s="5">
         <v>128.4</v>
       </c>
-      <c r="H14" s="7">
+      <c r="H14" s="9">
         <f t="shared" si="1"/>
         <v>4.1131264461271426E-19</v>
       </c>
-      <c r="I14" s="7"/>
-      <c r="L14" s="9">
+      <c r="I14" s="9"/>
+      <c r="L14" s="7">
         <v>1.2000000000000001E-19</v>
       </c>
-      <c r="M14" s="9"/>
+      <c r="M14" s="7"/>
       <c r="N14" s="1">
         <v>0</v>
       </c>
@@ -1715,15 +1709,15 @@
       <c r="G15" s="5">
         <v>41.9</v>
       </c>
-      <c r="H15" s="7">
+      <c r="H15" s="9">
         <f t="shared" si="1"/>
         <v>3.0461654514538201E-19</v>
       </c>
-      <c r="I15" s="7"/>
-      <c r="L15" s="9">
+      <c r="I15" s="9"/>
+      <c r="L15" s="7">
         <v>1.3000000000000001E-19</v>
       </c>
-      <c r="M15" s="9"/>
+      <c r="M15" s="7"/>
       <c r="N15" s="1">
         <v>0</v>
       </c>
@@ -1748,15 +1742,15 @@
       <c r="G16" s="5">
         <v>83.9</v>
       </c>
-      <c r="H16" s="7">
+      <c r="H16" s="9">
         <f t="shared" si="1"/>
         <v>3.9831346048250973E-19</v>
       </c>
-      <c r="I16" s="7"/>
-      <c r="L16" s="9">
+      <c r="I16" s="9"/>
+      <c r="L16" s="7">
         <v>1.4E-19</v>
       </c>
-      <c r="M16" s="9"/>
+      <c r="M16" s="7"/>
       <c r="N16" s="1">
         <v>1</v>
       </c>
@@ -1781,15 +1775,15 @@
       <c r="G17" s="5">
         <v>173.6</v>
       </c>
-      <c r="H17" s="7">
+      <c r="H17" s="9">
         <f t="shared" si="1"/>
         <v>1.6678483768588152E-19</v>
       </c>
-      <c r="I17" s="7"/>
-      <c r="L17" s="9">
+      <c r="I17" s="9"/>
+      <c r="L17" s="7">
         <v>1.5E-19</v>
       </c>
-      <c r="M17" s="9"/>
+      <c r="M17" s="7"/>
       <c r="N17" s="1">
         <v>0</v>
       </c>
@@ -1814,15 +1808,15 @@
       <c r="G18" s="5">
         <v>232.8</v>
       </c>
-      <c r="H18" s="7">
+      <c r="H18" s="9">
         <f t="shared" si="1"/>
         <v>2.120275636869835E-19</v>
       </c>
-      <c r="I18" s="7"/>
-      <c r="L18" s="9">
+      <c r="I18" s="9"/>
+      <c r="L18" s="7">
         <v>1.5999999999999999E-19</v>
       </c>
-      <c r="M18" s="9"/>
+      <c r="M18" s="7"/>
       <c r="N18" s="1">
         <v>2</v>
       </c>
@@ -1847,15 +1841,15 @@
       <c r="G19" s="5">
         <v>115.9</v>
       </c>
-      <c r="H19" s="7">
+      <c r="H19" s="9">
         <f t="shared" si="1"/>
         <v>1.7488298802142485E-19</v>
       </c>
-      <c r="I19" s="7"/>
-      <c r="L19" s="9">
+      <c r="I19" s="9"/>
+      <c r="L19" s="7">
         <v>1.7000000000000001E-19</v>
       </c>
-      <c r="M19" s="9"/>
+      <c r="M19" s="7"/>
       <c r="N19" s="1">
         <v>4</v>
       </c>
@@ -1880,15 +1874,15 @@
       <c r="G20" s="5">
         <v>69.599999999999994</v>
       </c>
-      <c r="H20" s="7">
+      <c r="H20" s="9">
         <f t="shared" si="1"/>
         <v>2.455034668682092E-19</v>
       </c>
-      <c r="I20" s="7"/>
-      <c r="L20" s="9">
+      <c r="I20" s="9"/>
+      <c r="L20" s="7">
         <v>1.8000000000000001E-19</v>
       </c>
-      <c r="M20" s="9"/>
+      <c r="M20" s="7"/>
       <c r="N20" s="1">
         <v>1</v>
       </c>
@@ -1913,15 +1907,15 @@
       <c r="G21" s="5">
         <v>211.8</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="9">
         <f t="shared" si="1"/>
         <v>1.5384584720296341E-19</v>
       </c>
-      <c r="I21" s="7"/>
-      <c r="L21" s="9">
+      <c r="I21" s="9"/>
+      <c r="L21" s="7">
         <v>1.9E-19</v>
       </c>
-      <c r="M21" s="9"/>
+      <c r="M21" s="7"/>
       <c r="N21" s="1">
         <v>2</v>
       </c>
@@ -1946,15 +1940,15 @@
       <c r="G22" s="5">
         <v>225.3</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="9">
         <f t="shared" si="1"/>
         <v>7.8498587920631624E-19</v>
       </c>
-      <c r="I22" s="7"/>
-      <c r="L22" s="9">
+      <c r="I22" s="9"/>
+      <c r="L22" s="7">
         <v>2E-19</v>
       </c>
-      <c r="M22" s="9"/>
+      <c r="M22" s="7"/>
       <c r="N22" s="1">
         <v>0</v>
       </c>
@@ -1979,15 +1973,15 @@
       <c r="G23" s="5">
         <v>42.2</v>
       </c>
-      <c r="H23" s="7">
+      <c r="H23" s="9">
         <f t="shared" si="1"/>
         <v>1.4548270972574926E-18</v>
       </c>
-      <c r="I23" s="7"/>
-      <c r="L23" s="9">
+      <c r="I23" s="9"/>
+      <c r="L23" s="7">
         <v>2.0999999999999999E-19</v>
       </c>
-      <c r="M23" s="9"/>
+      <c r="M23" s="7"/>
       <c r="N23" s="1">
         <v>1</v>
       </c>
@@ -2012,15 +2006,15 @@
       <c r="G24" s="5">
         <v>92.9</v>
       </c>
-      <c r="H24" s="7">
+      <c r="H24" s="9">
         <f t="shared" si="1"/>
         <v>1.6442393256488777E-19</v>
       </c>
-      <c r="I24" s="7"/>
-      <c r="L24" s="9">
+      <c r="I24" s="9"/>
+      <c r="L24" s="7">
         <v>2.1999999999999998E-19</v>
       </c>
-      <c r="M24" s="9"/>
+      <c r="M24" s="7"/>
       <c r="N24" s="1">
         <v>1</v>
       </c>
@@ -2045,15 +2039,15 @@
       <c r="G25" s="5">
         <v>72.900000000000006</v>
       </c>
-      <c r="H25" s="7">
+      <c r="H25" s="9">
         <f t="shared" si="1"/>
         <v>1.6857858253870438E-19</v>
       </c>
-      <c r="I25" s="7"/>
-      <c r="L25" s="9">
+      <c r="I25" s="9"/>
+      <c r="L25" s="7">
         <v>2.2999999999999998E-19</v>
       </c>
-      <c r="M25" s="9"/>
+      <c r="M25" s="7"/>
       <c r="N25" s="1">
         <v>1</v>
       </c>
@@ -2078,15 +2072,15 @@
       <c r="G26" s="5">
         <v>288.10000000000002</v>
       </c>
-      <c r="H26" s="7">
+      <c r="H26" s="9">
         <f t="shared" si="1"/>
         <v>4.9794532621128721E-20</v>
       </c>
-      <c r="I26" s="7"/>
-      <c r="L26" s="9">
+      <c r="I26" s="9"/>
+      <c r="L26" s="7">
         <v>2.4000000000000002E-19</v>
       </c>
-      <c r="M26" s="9"/>
+      <c r="M26" s="7"/>
       <c r="N26" s="1">
         <v>1</v>
       </c>
@@ -2111,15 +2105,15 @@
       <c r="G27" s="5">
         <v>227.7</v>
       </c>
-      <c r="H27" s="7">
+      <c r="H27" s="9">
         <f t="shared" si="1"/>
         <v>1.0944934037775462E-19</v>
       </c>
-      <c r="I27" s="7"/>
-      <c r="L27" s="9">
+      <c r="I27" s="9"/>
+      <c r="L27" s="7">
         <v>2.5000000000000002E-19</v>
       </c>
-      <c r="M27" s="9"/>
+      <c r="M27" s="7"/>
       <c r="N27" s="1">
         <v>1</v>
       </c>
@@ -2144,15 +2138,15 @@
       <c r="G28" s="5">
         <v>236.3</v>
       </c>
-      <c r="H28" s="7">
+      <c r="H28" s="9">
         <f t="shared" si="1"/>
         <v>6.2382768602547688E-20</v>
       </c>
-      <c r="I28" s="7"/>
-      <c r="L28" s="9">
+      <c r="I28" s="9"/>
+      <c r="L28" s="7">
         <v>2.6000000000000001E-19</v>
       </c>
-      <c r="M28" s="9"/>
+      <c r="M28" s="7"/>
       <c r="N28" s="1">
         <v>0</v>
       </c>
@@ -2177,15 +2171,15 @@
       <c r="G29" s="5">
         <v>138.4</v>
       </c>
-      <c r="H29" s="7">
+      <c r="H29" s="9">
         <f t="shared" si="1"/>
         <v>1.3027476717986452E-19</v>
       </c>
-      <c r="I29" s="7"/>
-      <c r="L29" s="9">
+      <c r="I29" s="9"/>
+      <c r="L29" s="7">
         <v>2.7000000000000001E-19</v>
       </c>
-      <c r="M29" s="9"/>
+      <c r="M29" s="7"/>
       <c r="N29" s="1">
         <v>0</v>
       </c>
@@ -2210,15 +2204,15 @@
       <c r="G30" s="5">
         <v>134.5</v>
       </c>
-      <c r="H30" s="7">
+      <c r="H30" s="9">
         <f t="shared" si="1"/>
         <v>9.05287682212827E-19</v>
       </c>
-      <c r="I30" s="7"/>
-      <c r="L30" s="9">
+      <c r="I30" s="9"/>
+      <c r="L30" s="7">
         <v>2.8E-19</v>
       </c>
-      <c r="M30" s="9"/>
+      <c r="M30" s="7"/>
       <c r="N30" s="1">
         <v>1</v>
       </c>
@@ -2243,15 +2237,15 @@
       <c r="G31" s="5">
         <v>111.2</v>
       </c>
-      <c r="H31" s="7">
+      <c r="H31" s="9">
         <f t="shared" si="1"/>
         <v>1.835500131871435E-19</v>
       </c>
-      <c r="I31" s="7"/>
-      <c r="L31" s="9">
+      <c r="I31" s="9"/>
+      <c r="L31" s="7">
         <v>2.9E-19</v>
       </c>
-      <c r="M31" s="9"/>
+      <c r="M31" s="7"/>
       <c r="N31" s="1">
         <v>1</v>
       </c>
@@ -2276,15 +2270,15 @@
       <c r="G32" s="5">
         <v>247.1</v>
       </c>
-      <c r="H32" s="7">
+      <c r="H32" s="9">
         <f t="shared" si="1"/>
         <v>2.0923481425821882E-19</v>
       </c>
-      <c r="I32" s="7"/>
-      <c r="L32" s="9">
+      <c r="I32" s="9"/>
+      <c r="L32" s="7">
         <v>2.9999999999999999E-19</v>
       </c>
-      <c r="M32" s="9"/>
+      <c r="M32" s="7"/>
       <c r="N32" s="1">
         <v>0</v>
       </c>
@@ -2309,15 +2303,15 @@
       <c r="G33" s="5">
         <v>169</v>
       </c>
-      <c r="H33" s="7">
+      <c r="H33" s="9">
         <f t="shared" si="1"/>
         <v>4.4662320015468356E-19</v>
       </c>
-      <c r="I33" s="7"/>
-      <c r="L33" s="9">
+      <c r="I33" s="9"/>
+      <c r="L33" s="7">
         <v>3.0999999999999999E-19</v>
       </c>
-      <c r="M33" s="9"/>
+      <c r="M33" s="7"/>
       <c r="N33" s="1">
         <v>1</v>
       </c>
@@ -2342,15 +2336,15 @@
       <c r="G34" s="5">
         <v>272.8</v>
       </c>
-      <c r="H34" s="7">
+      <c r="H34" s="9">
         <f t="shared" si="1"/>
         <v>4.3179864400352903E-20</v>
       </c>
-      <c r="I34" s="7"/>
-      <c r="L34" s="9">
+      <c r="I34" s="9"/>
+      <c r="L34" s="7">
         <v>3.1999999999999998E-19</v>
       </c>
-      <c r="M34" s="9"/>
+      <c r="M34" s="7"/>
       <c r="N34" s="1">
         <v>0</v>
       </c>
@@ -2375,15 +2369,15 @@
       <c r="G35" s="5">
         <v>50.9</v>
       </c>
-      <c r="H35" s="7">
+      <c r="H35" s="9">
         <f t="shared" si="1"/>
         <v>2.8380061566768923E-19</v>
       </c>
-      <c r="I35" s="7"/>
-      <c r="L35" s="9">
+      <c r="I35" s="9"/>
+      <c r="L35" s="7">
         <v>3.2999999999999998E-19</v>
       </c>
-      <c r="M35" s="9"/>
+      <c r="M35" s="7"/>
       <c r="N35" s="1">
         <v>0</v>
       </c>
@@ -2408,15 +2402,15 @@
       <c r="G36" s="5">
         <v>170.8</v>
       </c>
-      <c r="H36" s="7">
+      <c r="H36" s="9">
         <f t="shared" si="1"/>
         <v>3.6812516124506652E-19</v>
       </c>
-      <c r="I36" s="7"/>
-      <c r="L36" s="9">
+      <c r="I36" s="9"/>
+      <c r="L36" s="7">
         <v>3.4000000000000002E-19</v>
       </c>
-      <c r="M36" s="9"/>
+      <c r="M36" s="7"/>
       <c r="N36" s="1">
         <v>1</v>
       </c>
@@ -2441,15 +2435,15 @@
       <c r="G37" s="5">
         <v>174.5</v>
       </c>
-      <c r="H37" s="7">
+      <c r="H37" s="9">
         <f t="shared" si="1"/>
         <v>7.8812384156677962E-20</v>
       </c>
-      <c r="I37" s="7"/>
-      <c r="L37" s="9">
+      <c r="I37" s="9"/>
+      <c r="L37" s="7">
         <v>3.5000000000000002E-19</v>
       </c>
-      <c r="M37" s="9"/>
+      <c r="M37" s="7"/>
       <c r="N37" s="1">
         <v>0</v>
       </c>
@@ -2474,15 +2468,15 @@
       <c r="G38" s="5">
         <v>123.9</v>
       </c>
-      <c r="H38" s="7">
+      <c r="H38" s="9">
         <f t="shared" si="1"/>
         <v>1.0515635189613713E-19</v>
       </c>
-      <c r="I38" s="7"/>
-      <c r="L38" s="9">
+      <c r="I38" s="9"/>
+      <c r="L38" s="7">
         <v>3.6000000000000001E-19</v>
       </c>
-      <c r="M38" s="9"/>
+      <c r="M38" s="7"/>
       <c r="N38" s="1">
         <v>0</v>
       </c>
@@ -2507,15 +2501,15 @@
       <c r="G39" s="5">
         <v>345.3</v>
       </c>
-      <c r="H39" s="7">
+      <c r="H39" s="9">
         <f t="shared" si="1"/>
         <v>6.8451844141021412E-20</v>
       </c>
-      <c r="I39" s="7"/>
-      <c r="L39" s="9">
+      <c r="I39" s="9"/>
+      <c r="L39" s="7">
         <v>3.7000000000000001E-19</v>
       </c>
-      <c r="M39" s="9"/>
+      <c r="M39" s="7"/>
       <c r="N39" s="1">
         <v>4</v>
       </c>
@@ -2540,15 +2534,15 @@
       <c r="G40" s="5">
         <v>213.2</v>
       </c>
-      <c r="H40" s="7">
+      <c r="H40" s="9">
         <f t="shared" si="1"/>
         <v>1.6202722663136051E-19</v>
       </c>
-      <c r="I40" s="7"/>
-      <c r="L40" s="9">
+      <c r="I40" s="9"/>
+      <c r="L40" s="7">
         <v>3.8E-19</v>
       </c>
-      <c r="M40" s="9"/>
+      <c r="M40" s="7"/>
       <c r="N40" s="1">
         <v>0</v>
       </c>
@@ -2573,15 +2567,15 @@
       <c r="G41" s="5">
         <v>253.3</v>
       </c>
-      <c r="H41" s="7">
+      <c r="H41" s="9">
         <f t="shared" si="1"/>
         <v>4.5059327617437475E-19</v>
       </c>
-      <c r="I41" s="7"/>
-      <c r="L41" s="9">
+      <c r="I41" s="9"/>
+      <c r="L41" s="7">
         <v>3.9E-19</v>
       </c>
-      <c r="M41" s="9"/>
+      <c r="M41" s="7"/>
       <c r="N41" s="1">
         <v>0</v>
       </c>
@@ -2606,15 +2600,15 @@
       <c r="G42" s="5">
         <v>169.8</v>
       </c>
-      <c r="H42" s="7">
+      <c r="H42" s="9">
         <f t="shared" si="1"/>
         <v>9.193767993870622E-20</v>
       </c>
-      <c r="I42" s="7"/>
-      <c r="L42" s="9">
+      <c r="I42" s="9"/>
+      <c r="L42" s="7">
         <v>3.9999999999999999E-19</v>
       </c>
-      <c r="M42" s="9"/>
+      <c r="M42" s="7"/>
       <c r="N42" s="1">
         <v>2</v>
       </c>
@@ -2639,15 +2633,15 @@
       <c r="G43" s="5">
         <v>332.7</v>
       </c>
-      <c r="H43" s="7">
+      <c r="H43" s="9">
         <f t="shared" si="1"/>
         <v>3.5086479332700357E-20</v>
       </c>
-      <c r="I43" s="7"/>
-      <c r="L43" s="9">
+      <c r="I43" s="9"/>
+      <c r="L43" s="7">
         <v>4.0999999999999999E-19</v>
       </c>
-      <c r="M43" s="9"/>
+      <c r="M43" s="7"/>
       <c r="N43" s="1">
         <v>0</v>
       </c>
@@ -2672,15 +2666,15 @@
       <c r="G44" s="5">
         <v>222.6</v>
       </c>
-      <c r="H44" s="7">
+      <c r="H44" s="9">
         <f t="shared" si="1"/>
         <v>8.98343828154446E-19</v>
       </c>
-      <c r="I44" s="7"/>
-      <c r="L44" s="9">
+      <c r="I44" s="9"/>
+      <c r="L44" s="7">
         <v>4.1999999999999998E-19</v>
       </c>
-      <c r="M44" s="9"/>
+      <c r="M44" s="7"/>
       <c r="N44" s="1">
         <v>1</v>
       </c>
@@ -2705,15 +2699,15 @@
       <c r="G45" s="5">
         <v>187.8</v>
       </c>
-      <c r="H45" s="7">
+      <c r="H45" s="9">
         <f t="shared" si="1"/>
         <v>2.7530310225349235E-19</v>
       </c>
-      <c r="I45" s="7"/>
-      <c r="L45" s="9">
+      <c r="I45" s="9"/>
+      <c r="L45" s="7">
         <v>4.3000000000000002E-19</v>
       </c>
-      <c r="M45" s="9"/>
+      <c r="M45" s="7"/>
       <c r="N45" s="1">
         <v>1</v>
       </c>
@@ -2738,15 +2732,15 @@
       <c r="G46" s="5">
         <v>129.6</v>
       </c>
-      <c r="H46" s="7">
+      <c r="H46" s="9">
         <f t="shared" si="1"/>
         <v>2.3205683379361788E-19</v>
       </c>
-      <c r="I46" s="7"/>
-      <c r="L46" s="9">
+      <c r="I46" s="9"/>
+      <c r="L46" s="7">
         <v>4.3999999999999997E-19</v>
       </c>
-      <c r="M46" s="9"/>
+      <c r="M46" s="7"/>
       <c r="N46" s="1">
         <v>1</v>
       </c>
@@ -2771,15 +2765,15 @@
       <c r="G47" s="5">
         <v>336</v>
       </c>
-      <c r="H47" s="7">
+      <c r="H47" s="9">
         <f t="shared" si="1"/>
         <v>8.0259432458438495E-20</v>
       </c>
-      <c r="I47" s="7"/>
-      <c r="L47" s="9">
+      <c r="I47" s="9"/>
+      <c r="L47" s="7">
         <v>4.5000000000000001E-19</v>
       </c>
-      <c r="M47" s="9"/>
+      <c r="M47" s="7"/>
       <c r="N47" s="1">
         <v>2</v>
       </c>
@@ -2804,15 +2798,15 @@
       <c r="G48" s="5">
         <v>92</v>
       </c>
-      <c r="H48" s="7">
+      <c r="H48" s="9">
         <f t="shared" si="1"/>
         <v>5.0519531504841948E-19</v>
       </c>
-      <c r="I48" s="7"/>
-      <c r="L48" s="9">
+      <c r="I48" s="9"/>
+      <c r="L48" s="7">
         <v>4.5999999999999996E-19</v>
       </c>
-      <c r="M48" s="9"/>
+      <c r="M48" s="7"/>
       <c r="N48" s="1">
         <v>1</v>
       </c>
@@ -2837,15 +2831,15 @@
       <c r="G49" s="5">
         <v>220.3</v>
       </c>
-      <c r="H49" s="7">
+      <c r="H49" s="9">
         <f t="shared" si="1"/>
         <v>7.4310122663013932E-20</v>
       </c>
-      <c r="I49" s="7"/>
-      <c r="L49" s="9">
+      <c r="I49" s="9"/>
+      <c r="L49" s="7">
         <v>4.7E-19</v>
       </c>
-      <c r="M49" s="9"/>
+      <c r="M49" s="7"/>
       <c r="N49" s="1">
         <v>0</v>
       </c>
@@ -2870,15 +2864,15 @@
       <c r="G50" s="6">
         <v>170.8</v>
       </c>
-      <c r="H50" s="7">
+      <c r="H50" s="9">
         <f t="shared" si="1"/>
         <v>3.6812516124506652E-19</v>
       </c>
-      <c r="I50" s="7"/>
-      <c r="L50" s="9">
+      <c r="I50" s="9"/>
+      <c r="L50" s="7">
         <v>4.8000000000000005E-19</v>
       </c>
-      <c r="M50" s="9"/>
+      <c r="M50" s="7"/>
       <c r="N50" s="1">
         <v>0</v>
       </c>
@@ -2903,15 +2897,15 @@
       <c r="G51" s="5">
         <v>59.7</v>
       </c>
-      <c r="H51" s="7">
+      <c r="H51" s="9">
         <f t="shared" si="1"/>
         <v>2.2959328319809843E-19</v>
       </c>
-      <c r="I51" s="7"/>
-      <c r="L51" s="9">
+      <c r="I51" s="9"/>
+      <c r="L51" s="7">
         <v>4.8999999999999999E-19</v>
       </c>
-      <c r="M51" s="9"/>
+      <c r="M51" s="7"/>
       <c r="N51" s="1">
         <v>0</v>
       </c>
@@ -2936,15 +2930,15 @@
       <c r="G52" s="5">
         <v>205.2</v>
       </c>
-      <c r="H52" s="7">
+      <c r="H52" s="9">
         <f t="shared" si="1"/>
         <v>6.6841651277123587E-20</v>
       </c>
-      <c r="I52" s="7"/>
-      <c r="L52" s="9">
+      <c r="I52" s="9"/>
+      <c r="L52" s="7">
         <v>5.0000000000000004E-19</v>
       </c>
-      <c r="M52" s="9"/>
+      <c r="M52" s="7"/>
       <c r="N52" s="1">
         <v>0</v>
       </c>
@@ -2965,11 +2959,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G53" s="4"/>
-      <c r="H53" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I53" s="7"/>
+      <c r="H53" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I53" s="9"/>
       <c r="L53" s="8" t="s">
         <v>9</v>
       </c>
@@ -2994,11 +2988,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G54" s="4"/>
-      <c r="H54" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I54" s="7"/>
+      <c r="H54" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I54" s="9"/>
     </row>
     <row r="55" spans="2:14">
       <c r="B55" s="2">
@@ -3016,11 +3010,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G55" s="4"/>
-      <c r="H55" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I55" s="7"/>
+      <c r="H55" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I55" s="9"/>
     </row>
     <row r="56" spans="2:14">
       <c r="B56" s="2">
@@ -3038,11 +3032,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G56" s="4"/>
-      <c r="H56" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I56" s="7"/>
+      <c r="H56" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I56" s="9"/>
     </row>
     <row r="57" spans="2:14">
       <c r="B57" s="2">
@@ -3060,11 +3054,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G57" s="4"/>
-      <c r="H57" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I57" s="7"/>
+      <c r="H57" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I57" s="9"/>
     </row>
     <row r="58" spans="2:14">
       <c r="B58" s="2">
@@ -3082,11 +3076,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G58" s="4"/>
-      <c r="H58" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I58" s="7"/>
+      <c r="H58" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I58" s="9"/>
     </row>
     <row r="59" spans="2:14">
       <c r="B59" s="2">
@@ -3104,11 +3098,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G59" s="4"/>
-      <c r="H59" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I59" s="7"/>
+      <c r="H59" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I59" s="9"/>
     </row>
     <row r="60" spans="2:14">
       <c r="B60" s="2">
@@ -3126,11 +3120,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G60" s="4"/>
-      <c r="H60" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I60" s="7"/>
+      <c r="H60" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I60" s="9"/>
     </row>
     <row r="61" spans="2:14">
       <c r="B61" s="2">
@@ -3148,11 +3142,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G61" s="4"/>
-      <c r="H61" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I61" s="7"/>
+      <c r="H61" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I61" s="9"/>
     </row>
     <row r="62" spans="2:14">
       <c r="B62" s="2">
@@ -3170,11 +3164,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G62" s="4"/>
-      <c r="H62" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I62" s="7"/>
+      <c r="H62" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I62" s="9"/>
     </row>
     <row r="63" spans="2:14">
       <c r="B63" s="2">
@@ -3192,11 +3186,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G63" s="4"/>
-      <c r="H63" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I63" s="7"/>
+      <c r="H63" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I63" s="9"/>
     </row>
     <row r="64" spans="2:14">
       <c r="B64" s="2">
@@ -3214,11 +3208,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G64" s="4"/>
-      <c r="H64" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I64" s="7"/>
+      <c r="H64" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I64" s="9"/>
     </row>
     <row r="65" spans="2:9">
       <c r="B65" s="2">
@@ -3236,11 +3230,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G65" s="4"/>
-      <c r="H65" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I65" s="7"/>
+      <c r="H65" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I65" s="9"/>
     </row>
     <row r="66" spans="2:9">
       <c r="B66" s="2">
@@ -3258,11 +3252,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G66" s="4"/>
-      <c r="H66" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I66" s="7"/>
+      <c r="H66" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I66" s="9"/>
     </row>
     <row r="67" spans="2:9">
       <c r="B67" s="2">
@@ -3280,11 +3274,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G67" s="4"/>
-      <c r="H67" s="7" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I67" s="7"/>
+      <c r="H67" s="9" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I67" s="9"/>
     </row>
     <row r="68" spans="2:9">
       <c r="B68" s="2">
@@ -3302,11 +3296,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G68" s="4"/>
-      <c r="H68" s="7" t="e">
+      <c r="H68" s="9" t="e">
         <f t="shared" ref="H68:H102" si="3">1.945*10^-10*F68^1.5/G68</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I68" s="7"/>
+      <c r="I68" s="9"/>
     </row>
     <row r="69" spans="2:9">
       <c r="B69" s="2">
@@ -3324,11 +3318,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G69" s="4"/>
-      <c r="H69" s="7" t="e">
+      <c r="H69" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I69" s="7"/>
+      <c r="I69" s="9"/>
     </row>
     <row r="70" spans="2:9">
       <c r="B70" s="2">
@@ -3346,11 +3340,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G70" s="4"/>
-      <c r="H70" s="7" t="e">
+      <c r="H70" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I70" s="7"/>
+      <c r="I70" s="9"/>
     </row>
     <row r="71" spans="2:9">
       <c r="B71" s="2">
@@ -3368,11 +3362,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G71" s="4"/>
-      <c r="H71" s="7" t="e">
+      <c r="H71" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I71" s="7"/>
+      <c r="I71" s="9"/>
     </row>
     <row r="72" spans="2:9">
       <c r="B72" s="2">
@@ -3390,11 +3384,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G72" s="4"/>
-      <c r="H72" s="7" t="e">
+      <c r="H72" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I72" s="7"/>
+      <c r="I72" s="9"/>
     </row>
     <row r="73" spans="2:9">
       <c r="B73" s="2">
@@ -3412,11 +3406,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G73" s="4"/>
-      <c r="H73" s="7" t="e">
+      <c r="H73" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I73" s="7"/>
+      <c r="I73" s="9"/>
     </row>
     <row r="74" spans="2:9">
       <c r="B74" s="2">
@@ -3434,11 +3428,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G74" s="4"/>
-      <c r="H74" s="7" t="e">
+      <c r="H74" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I74" s="7"/>
+      <c r="I74" s="9"/>
     </row>
     <row r="75" spans="2:9">
       <c r="B75" s="2">
@@ -3456,11 +3450,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G75" s="4"/>
-      <c r="H75" s="7" t="e">
+      <c r="H75" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I75" s="7"/>
+      <c r="I75" s="9"/>
     </row>
     <row r="76" spans="2:9">
       <c r="B76" s="2">
@@ -3478,11 +3472,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G76" s="4"/>
-      <c r="H76" s="7" t="e">
+      <c r="H76" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I76" s="7"/>
+      <c r="I76" s="9"/>
     </row>
     <row r="77" spans="2:9">
       <c r="B77" s="2">
@@ -3500,11 +3494,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G77" s="4"/>
-      <c r="H77" s="7" t="e">
+      <c r="H77" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I77" s="7"/>
+      <c r="I77" s="9"/>
     </row>
     <row r="78" spans="2:9">
       <c r="B78" s="2">
@@ -3522,11 +3516,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G78" s="4"/>
-      <c r="H78" s="7" t="e">
+      <c r="H78" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I78" s="7"/>
+      <c r="I78" s="9"/>
     </row>
     <row r="79" spans="2:9">
       <c r="B79" s="2">
@@ -3544,11 +3538,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G79" s="4"/>
-      <c r="H79" s="7" t="e">
+      <c r="H79" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I79" s="7"/>
+      <c r="I79" s="9"/>
     </row>
     <row r="80" spans="2:9">
       <c r="B80" s="2">
@@ -3566,11 +3560,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G80" s="4"/>
-      <c r="H80" s="7" t="e">
+      <c r="H80" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I80" s="7"/>
+      <c r="I80" s="9"/>
     </row>
     <row r="81" spans="2:9">
       <c r="B81" s="2">
@@ -3588,11 +3582,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G81" s="4"/>
-      <c r="H81" s="7" t="e">
+      <c r="H81" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I81" s="7"/>
+      <c r="I81" s="9"/>
     </row>
     <row r="82" spans="2:9">
       <c r="B82" s="2">
@@ -3610,11 +3604,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G82" s="4"/>
-      <c r="H82" s="7" t="e">
+      <c r="H82" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I82" s="7"/>
+      <c r="I82" s="9"/>
     </row>
     <row r="83" spans="2:9">
       <c r="B83" s="2">
@@ -3632,11 +3626,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G83" s="4"/>
-      <c r="H83" s="7" t="e">
+      <c r="H83" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I83" s="7"/>
+      <c r="I83" s="9"/>
     </row>
     <row r="84" spans="2:9">
       <c r="B84" s="2">
@@ -3654,11 +3648,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G84" s="4"/>
-      <c r="H84" s="7" t="e">
+      <c r="H84" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I84" s="7"/>
+      <c r="I84" s="9"/>
     </row>
     <row r="85" spans="2:9">
       <c r="B85" s="2">
@@ -3676,11 +3670,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G85" s="4"/>
-      <c r="H85" s="7" t="e">
+      <c r="H85" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I85" s="7"/>
+      <c r="I85" s="9"/>
     </row>
     <row r="86" spans="2:9">
       <c r="B86" s="2">
@@ -3698,11 +3692,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G86" s="4"/>
-      <c r="H86" s="7" t="e">
+      <c r="H86" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I86" s="7"/>
+      <c r="I86" s="9"/>
     </row>
     <row r="87" spans="2:9">
       <c r="B87" s="2">
@@ -3720,11 +3714,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G87" s="4"/>
-      <c r="H87" s="7" t="e">
+      <c r="H87" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I87" s="7"/>
+      <c r="I87" s="9"/>
     </row>
     <row r="88" spans="2:9">
       <c r="B88" s="2">
@@ -3742,11 +3736,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G88" s="4"/>
-      <c r="H88" s="7" t="e">
+      <c r="H88" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I88" s="7"/>
+      <c r="I88" s="9"/>
     </row>
     <row r="89" spans="2:9">
       <c r="B89" s="2">
@@ -3764,11 +3758,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G89" s="4"/>
-      <c r="H89" s="7" t="e">
+      <c r="H89" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I89" s="7"/>
+      <c r="I89" s="9"/>
     </row>
     <row r="90" spans="2:9">
       <c r="B90" s="2">
@@ -3786,11 +3780,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G90" s="4"/>
-      <c r="H90" s="7" t="e">
+      <c r="H90" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I90" s="7"/>
+      <c r="I90" s="9"/>
     </row>
     <row r="91" spans="2:9">
       <c r="B91" s="2">
@@ -3808,11 +3802,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G91" s="4"/>
-      <c r="H91" s="7" t="e">
+      <c r="H91" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I91" s="7"/>
+      <c r="I91" s="9"/>
     </row>
     <row r="92" spans="2:9">
       <c r="B92" s="2">
@@ -3830,11 +3824,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G92" s="4"/>
-      <c r="H92" s="7" t="e">
+      <c r="H92" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I92" s="7"/>
+      <c r="I92" s="9"/>
     </row>
     <row r="93" spans="2:9">
       <c r="B93" s="2">
@@ -3852,11 +3846,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G93" s="4"/>
-      <c r="H93" s="7" t="e">
+      <c r="H93" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I93" s="7"/>
+      <c r="I93" s="9"/>
     </row>
     <row r="94" spans="2:9">
       <c r="B94" s="2">
@@ -3874,11 +3868,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G94" s="4"/>
-      <c r="H94" s="7" t="e">
+      <c r="H94" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I94" s="7"/>
+      <c r="I94" s="9"/>
     </row>
     <row r="95" spans="2:9">
       <c r="B95" s="2">
@@ -3896,11 +3890,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="7" t="e">
+      <c r="H95" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I95" s="7"/>
+      <c r="I95" s="9"/>
     </row>
     <row r="96" spans="2:9">
       <c r="B96" s="2">
@@ -3918,11 +3912,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G96" s="4"/>
-      <c r="H96" s="7" t="e">
+      <c r="H96" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I96" s="7"/>
+      <c r="I96" s="9"/>
     </row>
     <row r="97" spans="2:9">
       <c r="B97" s="2">
@@ -3940,11 +3934,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G97" s="4"/>
-      <c r="H97" s="7" t="e">
+      <c r="H97" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I97" s="7"/>
+      <c r="I97" s="9"/>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="2">
@@ -3962,11 +3956,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G98" s="4"/>
-      <c r="H98" s="7" t="e">
+      <c r="H98" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I98" s="7"/>
+      <c r="I98" s="9"/>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="2">
@@ -3984,11 +3978,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G99" s="4"/>
-      <c r="H99" s="7" t="e">
+      <c r="H99" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I99" s="7"/>
+      <c r="I99" s="9"/>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="2">
@@ -4006,11 +4000,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G100" s="4"/>
-      <c r="H100" s="7" t="e">
+      <c r="H100" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I100" s="7"/>
+      <c r="I100" s="9"/>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="2">
@@ -4028,11 +4022,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G101" s="4"/>
-      <c r="H101" s="7" t="e">
+      <c r="H101" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I101" s="7"/>
+      <c r="I101" s="9"/>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="2">
@@ -4050,61 +4044,96 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G102" s="4"/>
-      <c r="H102" s="7" t="e">
+      <c r="H102" s="9" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I102" s="7"/>
+      <c r="I102" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="153">
-    <mergeCell ref="L49:M49"/>
-    <mergeCell ref="L50:M50"/>
-    <mergeCell ref="L51:M51"/>
-    <mergeCell ref="L52:M52"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="L44:M44"/>
-    <mergeCell ref="L45:M45"/>
-    <mergeCell ref="L46:M46"/>
-    <mergeCell ref="L47:M47"/>
-    <mergeCell ref="L48:M48"/>
-    <mergeCell ref="L37:M37"/>
-    <mergeCell ref="L38:M38"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="L40:M40"/>
-    <mergeCell ref="L41:M41"/>
-    <mergeCell ref="L42:M42"/>
-    <mergeCell ref="L31:M31"/>
-    <mergeCell ref="L32:M32"/>
-    <mergeCell ref="L33:M33"/>
-    <mergeCell ref="L34:M34"/>
-    <mergeCell ref="L35:M35"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="L25:M25"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="L27:M27"/>
-    <mergeCell ref="L28:M28"/>
-    <mergeCell ref="L29:M29"/>
-    <mergeCell ref="L30:M30"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="L20:M20"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="L22:M22"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="L24:M24"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="L14:M14"/>
-    <mergeCell ref="L15:M15"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="L17:M17"/>
-    <mergeCell ref="L18:M18"/>
-    <mergeCell ref="L7:M7"/>
-    <mergeCell ref="L8:M8"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="L10:M10"/>
-    <mergeCell ref="L11:M11"/>
-    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H12:I12"/>
+    <mergeCell ref="H13:I13"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="H4:I4"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H20:I20"/>
+    <mergeCell ref="H21:I21"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H24:I24"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H16:I16"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H32:I32"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="H45:I45"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H48:I48"/>
+    <mergeCell ref="H49:I49"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H40:I40"/>
+    <mergeCell ref="H41:I41"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="H57:I57"/>
+    <mergeCell ref="H58:I58"/>
+    <mergeCell ref="H59:I59"/>
+    <mergeCell ref="H60:I60"/>
+    <mergeCell ref="H61:I61"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H52:I52"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="H55:I55"/>
+    <mergeCell ref="H68:I68"/>
+    <mergeCell ref="H69:I69"/>
+    <mergeCell ref="H70:I70"/>
+    <mergeCell ref="H71:I71"/>
+    <mergeCell ref="H72:I72"/>
+    <mergeCell ref="H73:I73"/>
+    <mergeCell ref="H62:I62"/>
+    <mergeCell ref="H63:I63"/>
+    <mergeCell ref="H64:I64"/>
+    <mergeCell ref="H65:I65"/>
+    <mergeCell ref="H66:I66"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="H82:I82"/>
+    <mergeCell ref="H83:I83"/>
+    <mergeCell ref="H84:I84"/>
+    <mergeCell ref="H85:I85"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="H75:I75"/>
+    <mergeCell ref="H76:I76"/>
+    <mergeCell ref="H77:I77"/>
+    <mergeCell ref="H78:I78"/>
+    <mergeCell ref="H79:I79"/>
     <mergeCell ref="H98:I98"/>
     <mergeCell ref="H99:I99"/>
     <mergeCell ref="H100:I100"/>
@@ -4129,88 +4158,53 @@
     <mergeCell ref="H91:I91"/>
     <mergeCell ref="H80:I80"/>
     <mergeCell ref="H81:I81"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="H75:I75"/>
-    <mergeCell ref="H76:I76"/>
-    <mergeCell ref="H77:I77"/>
-    <mergeCell ref="H78:I78"/>
-    <mergeCell ref="H79:I79"/>
-    <mergeCell ref="H68:I68"/>
-    <mergeCell ref="H69:I69"/>
-    <mergeCell ref="H70:I70"/>
-    <mergeCell ref="H71:I71"/>
-    <mergeCell ref="H72:I72"/>
-    <mergeCell ref="H73:I73"/>
-    <mergeCell ref="H62:I62"/>
-    <mergeCell ref="H63:I63"/>
-    <mergeCell ref="H64:I64"/>
-    <mergeCell ref="H65:I65"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="H67:I67"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="H57:I57"/>
-    <mergeCell ref="H58:I58"/>
-    <mergeCell ref="H59:I59"/>
-    <mergeCell ref="H60:I60"/>
-    <mergeCell ref="H61:I61"/>
-    <mergeCell ref="H50:I50"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H52:I52"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="H55:I55"/>
-    <mergeCell ref="H44:I44"/>
-    <mergeCell ref="H45:I45"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H48:I48"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H40:I40"/>
-    <mergeCell ref="H41:I41"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H32:I32"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="H37:I37"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H28:I28"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H20:I20"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H16:I16"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H12:I12"/>
-    <mergeCell ref="H13:I13"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="L14:M14"/>
+    <mergeCell ref="L15:M15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="L17:M17"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="L7:M7"/>
+    <mergeCell ref="L8:M8"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="L10:M10"/>
+    <mergeCell ref="L11:M11"/>
+    <mergeCell ref="L12:M12"/>
+    <mergeCell ref="L25:M25"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="L27:M27"/>
+    <mergeCell ref="L28:M28"/>
+    <mergeCell ref="L29:M29"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="L19:M19"/>
+    <mergeCell ref="L20:M20"/>
+    <mergeCell ref="L21:M21"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="L23:M23"/>
+    <mergeCell ref="L24:M24"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="L38:M38"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="L40:M40"/>
+    <mergeCell ref="L41:M41"/>
+    <mergeCell ref="L42:M42"/>
+    <mergeCell ref="L31:M31"/>
+    <mergeCell ref="L32:M32"/>
+    <mergeCell ref="L33:M33"/>
+    <mergeCell ref="L34:M34"/>
+    <mergeCell ref="L35:M35"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="L49:M49"/>
+    <mergeCell ref="L50:M50"/>
+    <mergeCell ref="L51:M51"/>
+    <mergeCell ref="L52:M52"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L43:M43"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="L45:M45"/>
+    <mergeCell ref="L46:M46"/>
+    <mergeCell ref="L47:M47"/>
+    <mergeCell ref="L48:M48"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
+++ b/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D.tuy\Documents\GitHub\school\one down\普物實驗\6 密立根油滴實驗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F5D72BC-28A4-463B-A585-D37A22C4DDC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFF1654-F2CB-45E0-A200-313FC651A46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
   <si>
     <t>次數</t>
   </si>
@@ -75,6 +75,19 @@
   <si>
     <t>大於5.0E-19</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>V1(m/s)</t>
+  </si>
+  <si>
+    <t>次數</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>估計n值</t>
+  </si>
+  <si>
+    <t>誤差(%)</t>
   </si>
 </sst>
 </file>
@@ -119,17 +132,17 @@
       <charset val="136"/>
     </font>
     <font>
-      <sz val="11"/>
-      <name val="標楷體"/>
-      <family val="4"/>
-      <charset val="136"/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="標楷體"/>
-      <family val="4"/>
-      <charset val="136"/>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -146,7 +159,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -169,13 +182,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -191,12 +230,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="11" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -205,6 +238,30 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1250,7 +1307,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3419739-BEEB-4B53-8EC5-6DC56A0166CA}">
-  <dimension ref="B2:N102"/>
+  <dimension ref="B2:AF102"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="2" max="2" width="11.77734375" customWidth="1"/>
@@ -1263,7 +1320,7 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" s="2" t="s">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>1</v>
@@ -1280,14 +1337,14 @@
       <c r="G2" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H2" s="9" t="s">
+      <c r="H2" s="8" t="s">
         <v>4</v>
       </c>
       <c r="I2" s="9"/>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="8"/>
+      <c r="M2" s="6"/>
       <c r="N2" s="1" t="s">
         <v>6</v>
       </c>
@@ -1303,24 +1360,24 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E3" s="4">
-        <v>22.8</v>
+        <v>19.71</v>
       </c>
       <c r="F3" s="2">
         <f>D3/E3</f>
-        <v>1.6754385964912282E-5</v>
-      </c>
-      <c r="G3" s="5">
-        <v>72.3</v>
-      </c>
-      <c r="H3" s="9">
+        <v>1.9381024860476914E-5</v>
+      </c>
+      <c r="G3" s="4">
+        <v>102.5</v>
+      </c>
+      <c r="H3" s="8">
         <f>1.945*10^-10*F3^1.5/G3</f>
-        <v>1.8449053158903017E-19</v>
+        <v>1.6190521892403686E-19</v>
       </c>
       <c r="I3" s="9"/>
-      <c r="L3" s="7">
+      <c r="L3" s="5">
         <v>9.9999999999999995E-21</v>
       </c>
-      <c r="M3" s="7"/>
+      <c r="M3" s="5"/>
       <c r="N3" s="1">
         <f t="array" ref="N3:N52">FREQUENCY(H3:I52,L3:M52)</f>
         <v>0</v>
@@ -1337,24 +1394,24 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E4" s="4">
-        <v>7.32</v>
+        <v>10.130000000000001</v>
       </c>
       <c r="F4" s="2">
         <f t="shared" ref="F4:F67" si="0">D4/E4</f>
-        <v>5.2185792349726774E-5</v>
-      </c>
-      <c r="G4" s="5">
-        <v>168.6</v>
-      </c>
-      <c r="H4" s="9">
+        <v>3.7709772951628824E-5</v>
+      </c>
+      <c r="G4" s="4">
+        <v>93.4</v>
+      </c>
+      <c r="H4" s="8">
         <f t="shared" ref="H4:H67" si="1">1.945*10^-10*F4^1.5/G4</f>
-        <v>4.3490105195356502E-19</v>
+        <v>4.8222931266951704E-19</v>
       </c>
       <c r="I4" s="9"/>
-      <c r="L4" s="7">
+      <c r="L4" s="5">
         <v>1.9999999999999999E-20</v>
       </c>
-      <c r="M4" s="7"/>
+      <c r="M4" s="5"/>
       <c r="N4" s="1">
         <v>0</v>
       </c>
@@ -1370,24 +1427,24 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E5" s="4">
-        <v>14.47</v>
+        <v>25.52</v>
       </c>
       <c r="F5" s="2">
         <f t="shared" si="0"/>
-        <v>2.6399447131997236E-5</v>
-      </c>
-      <c r="G5" s="5">
-        <v>62.6</v>
-      </c>
-      <c r="H5" s="9">
-        <f t="shared" si="1"/>
-        <v>4.2144171456566916E-19</v>
+        <v>1.4968652037617556E-5</v>
+      </c>
+      <c r="G5" s="4">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="H5" s="8">
+        <f t="shared" si="1"/>
+        <v>1.5409064320443441E-19</v>
       </c>
       <c r="I5" s="9"/>
-      <c r="L5" s="7">
+      <c r="L5" s="5">
         <v>3.0000000000000003E-20</v>
       </c>
-      <c r="M5" s="7"/>
+      <c r="M5" s="5"/>
       <c r="N5" s="1">
         <v>0</v>
       </c>
@@ -1403,26 +1460,26 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E6" s="4">
-        <v>14.98</v>
+        <v>17.53</v>
       </c>
       <c r="F6" s="2">
         <f t="shared" si="0"/>
-        <v>2.5500667556742323E-5</v>
-      </c>
-      <c r="G6" s="5">
-        <v>68.599999999999994</v>
-      </c>
-      <c r="H6" s="9">
-        <f t="shared" si="1"/>
-        <v>3.6510923183134183E-19</v>
+        <v>2.1791215059897318E-5</v>
+      </c>
+      <c r="G6" s="4">
+        <v>115.8</v>
+      </c>
+      <c r="H6" s="8">
+        <f t="shared" si="1"/>
+        <v>1.708571730945013E-19</v>
       </c>
       <c r="I6" s="9"/>
-      <c r="L6" s="7">
+      <c r="L6" s="5">
         <v>3.9999999999999998E-20</v>
       </c>
-      <c r="M6" s="7"/>
+      <c r="M6" s="5"/>
       <c r="N6" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="2:14">
@@ -1436,26 +1493,26 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E7" s="4">
-        <v>3.72</v>
+        <v>23.62</v>
       </c>
       <c r="F7" s="2">
         <f t="shared" si="0"/>
-        <v>1.0268817204301075E-4</v>
-      </c>
-      <c r="G7" s="5">
-        <v>284.2</v>
-      </c>
-      <c r="H7" s="9">
-        <f t="shared" si="1"/>
-        <v>7.1215768734266231E-19</v>
+        <v>1.6172734970364097E-5</v>
+      </c>
+      <c r="G7" s="4">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="H7" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6135363266837157E-19</v>
       </c>
       <c r="I7" s="9"/>
-      <c r="L7" s="7">
+      <c r="L7" s="5">
         <v>4.9999999999999999E-20</v>
       </c>
-      <c r="M7" s="7"/>
+      <c r="M7" s="5"/>
       <c r="N7" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="2:14">
@@ -1469,24 +1526,24 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E8" s="4">
-        <v>4.05</v>
+        <v>21.06</v>
       </c>
       <c r="F8" s="2">
         <f t="shared" si="0"/>
-        <v>9.432098765432099E-5</v>
-      </c>
-      <c r="G8" s="5">
-        <v>351.7</v>
-      </c>
-      <c r="H8" s="9">
-        <f t="shared" si="1"/>
-        <v>5.0659365601111741E-19</v>
+        <v>1.8138651471984806E-5</v>
+      </c>
+      <c r="G8" s="4">
+        <v>47.3</v>
+      </c>
+      <c r="H8" s="8">
+        <f t="shared" si="1"/>
+        <v>3.1766250698411249E-19</v>
       </c>
       <c r="I8" s="9"/>
-      <c r="L8" s="7">
+      <c r="L8" s="5">
         <v>6.0000000000000006E-20</v>
       </c>
-      <c r="M8" s="7"/>
+      <c r="M8" s="5"/>
       <c r="N8" s="1">
         <v>0</v>
       </c>
@@ -1502,26 +1559,26 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E9" s="4">
-        <v>10.6</v>
+        <v>7.22</v>
       </c>
       <c r="F9" s="2">
         <f t="shared" si="0"/>
-        <v>3.6037735849056609E-5</v>
-      </c>
-      <c r="G9" s="5">
-        <v>126</v>
-      </c>
-      <c r="H9" s="9">
-        <f t="shared" si="1"/>
-        <v>3.339529675490588E-19</v>
+        <v>5.2908587257617734E-5</v>
+      </c>
+      <c r="G9" s="4">
+        <v>118.2</v>
+      </c>
+      <c r="H9" s="8">
+        <f t="shared" si="1"/>
+        <v>6.3327359074808118E-19</v>
       </c>
       <c r="I9" s="9"/>
-      <c r="L9" s="7">
+      <c r="L9" s="5">
         <v>7.0000000000000001E-20</v>
       </c>
-      <c r="M9" s="7"/>
+      <c r="M9" s="5"/>
       <c r="N9" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:14">
@@ -1535,26 +1592,26 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E10" s="4">
-        <v>9.75</v>
+        <v>18.28</v>
       </c>
       <c r="F10" s="2">
         <f t="shared" si="0"/>
-        <v>3.917948717948718E-5</v>
-      </c>
-      <c r="G10" s="5">
-        <v>120.1</v>
-      </c>
-      <c r="H10" s="9">
-        <f t="shared" si="1"/>
-        <v>3.971592840015501E-19</v>
+        <v>2.0897155361050329E-5</v>
+      </c>
+      <c r="G10" s="4">
+        <v>42.1</v>
+      </c>
+      <c r="H10" s="8">
+        <f t="shared" si="1"/>
+        <v>4.4133489495533817E-19</v>
       </c>
       <c r="I10" s="9"/>
-      <c r="L10" s="7">
+      <c r="L10" s="5">
         <v>7.9999999999999996E-20</v>
       </c>
-      <c r="M10" s="7"/>
+      <c r="M10" s="5"/>
       <c r="N10" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:14">
@@ -1568,26 +1625,26 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E11" s="4">
-        <v>8.11</v>
+        <v>10.24</v>
       </c>
       <c r="F11" s="2">
         <f t="shared" si="0"/>
-        <v>4.710234278668311E-5</v>
-      </c>
-      <c r="G11" s="5">
-        <v>170.8</v>
-      </c>
-      <c r="H11" s="9">
-        <f t="shared" si="1"/>
-        <v>3.6812516124506652E-19</v>
+        <v>3.7304687499999998E-5</v>
+      </c>
+      <c r="G11" s="4">
+        <v>141.5</v>
+      </c>
+      <c r="H11" s="8">
+        <f t="shared" si="1"/>
+        <v>3.1319028009888046E-19</v>
       </c>
       <c r="I11" s="9"/>
-      <c r="L11" s="7">
+      <c r="L11" s="5">
         <v>9.0000000000000003E-20</v>
       </c>
-      <c r="M11" s="7"/>
+      <c r="M11" s="5"/>
       <c r="N11" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="2:14">
@@ -1601,26 +1658,26 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E12" s="4">
-        <v>22.15</v>
+        <v>10.35</v>
       </c>
       <c r="F12" s="2">
         <f t="shared" si="0"/>
-        <v>1.7246049661399549E-5</v>
-      </c>
-      <c r="G12" s="5">
-        <v>88.4</v>
-      </c>
-      <c r="H12" s="9">
-        <f t="shared" si="1"/>
-        <v>1.5758025146171712E-19</v>
+        <v>3.6908212560386474E-5</v>
+      </c>
+      <c r="G12" s="4">
+        <v>268.39999999999998</v>
+      </c>
+      <c r="H12" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6248811998355345E-19</v>
       </c>
       <c r="I12" s="9"/>
-      <c r="L12" s="7">
+      <c r="L12" s="5">
         <v>9.9999999999999998E-20</v>
       </c>
-      <c r="M12" s="7"/>
+      <c r="M12" s="5"/>
       <c r="N12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:14">
@@ -1634,26 +1691,26 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E13" s="4">
-        <v>8.76</v>
+        <v>19.62</v>
       </c>
       <c r="F13" s="2">
         <f t="shared" si="0"/>
-        <v>4.3607305936073063E-5</v>
-      </c>
-      <c r="G13" s="5">
-        <v>126.6</v>
-      </c>
-      <c r="H13" s="9">
-        <f t="shared" si="1"/>
-        <v>4.4240984732649361E-19</v>
+        <v>1.9469928644240569E-5</v>
+      </c>
+      <c r="G13" s="4">
+        <v>54.2</v>
+      </c>
+      <c r="H13" s="8">
+        <f t="shared" si="1"/>
+        <v>3.0829526807059106E-19</v>
       </c>
       <c r="I13" s="9"/>
-      <c r="L13" s="7">
+      <c r="L13" s="5">
         <v>1.0999999999999999E-19</v>
       </c>
-      <c r="M13" s="7"/>
+      <c r="M13" s="5"/>
       <c r="N13" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:14">
@@ -1667,24 +1724,24 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E14" s="4">
-        <v>9.11</v>
+        <v>9.82</v>
       </c>
       <c r="F14" s="2">
         <f t="shared" si="0"/>
-        <v>4.1931942919868279E-5</v>
-      </c>
-      <c r="G14" s="5">
-        <v>128.4</v>
-      </c>
-      <c r="H14" s="9">
-        <f t="shared" si="1"/>
-        <v>4.1131264461271426E-19</v>
+        <v>3.8900203665987778E-5</v>
+      </c>
+      <c r="G14" s="4">
+        <v>148.6</v>
+      </c>
+      <c r="H14" s="8">
+        <f t="shared" si="1"/>
+        <v>3.1756205883650899E-19</v>
       </c>
       <c r="I14" s="9"/>
-      <c r="L14" s="7">
+      <c r="L14" s="5">
         <v>1.2000000000000001E-19</v>
       </c>
-      <c r="M14" s="7"/>
+      <c r="M14" s="5"/>
       <c r="N14" s="1">
         <v>0</v>
       </c>
@@ -1700,24 +1757,24 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E15" s="4">
-        <v>23.48</v>
+        <v>21.77</v>
       </c>
       <c r="F15" s="2">
         <f t="shared" si="0"/>
-        <v>1.6269165247018739E-5</v>
-      </c>
-      <c r="G15" s="5">
-        <v>41.9</v>
-      </c>
-      <c r="H15" s="9">
-        <f t="shared" si="1"/>
-        <v>3.0461654514538201E-19</v>
+        <v>1.754708314193845E-5</v>
+      </c>
+      <c r="G15" s="4">
+        <v>93.6</v>
+      </c>
+      <c r="H15" s="8">
+        <f t="shared" si="1"/>
+        <v>1.5273942724973247E-19</v>
       </c>
       <c r="I15" s="9"/>
-      <c r="L15" s="7">
+      <c r="L15" s="5">
         <v>1.3000000000000001E-19</v>
       </c>
-      <c r="M15" s="7"/>
+      <c r="M15" s="5"/>
       <c r="N15" s="1">
         <v>0</v>
       </c>
@@ -1733,29 +1790,29 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E16" s="4">
-        <v>12.36</v>
+        <v>10.27</v>
       </c>
       <c r="F16" s="2">
         <f t="shared" si="0"/>
-        <v>3.0906148867313921E-5</v>
-      </c>
-      <c r="G16" s="5">
-        <v>83.9</v>
-      </c>
-      <c r="H16" s="9">
-        <f t="shared" si="1"/>
-        <v>3.9831346048250973E-19</v>
+        <v>3.7195715676728335E-5</v>
+      </c>
+      <c r="G16" s="4">
+        <v>272.5</v>
+      </c>
+      <c r="H16" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6191701096095374E-19</v>
       </c>
       <c r="I16" s="9"/>
-      <c r="L16" s="7">
+      <c r="L16" s="5">
         <v>1.4E-19</v>
       </c>
-      <c r="M16" s="7"/>
+      <c r="M16" s="5"/>
       <c r="N16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="2:14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="2:32">
       <c r="B17" s="2">
         <v>15</v>
       </c>
@@ -1766,29 +1823,29 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E17" s="4">
-        <v>13.6</v>
+        <v>11.16</v>
       </c>
       <c r="F17" s="2">
         <f t="shared" si="0"/>
-        <v>2.8088235294117648E-5</v>
-      </c>
-      <c r="G17" s="5">
-        <v>173.6</v>
-      </c>
-      <c r="H17" s="9">
-        <f t="shared" si="1"/>
-        <v>1.6678483768588152E-19</v>
+        <v>3.4229390681003587E-5</v>
+      </c>
+      <c r="G17" s="4">
+        <v>224.8</v>
+      </c>
+      <c r="H17" s="8">
+        <f t="shared" si="1"/>
+        <v>1.7326947169993828E-19</v>
       </c>
       <c r="I17" s="9"/>
-      <c r="L17" s="7">
+      <c r="L17" s="5">
         <v>1.5E-19</v>
       </c>
-      <c r="M17" s="7"/>
+      <c r="M17" s="5"/>
       <c r="N17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="2:14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:32">
       <c r="B18" s="2">
         <v>16</v>
       </c>
@@ -1799,29 +1856,29 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E18" s="4">
-        <v>9.5299999999999994</v>
+        <v>11.09</v>
       </c>
       <c r="F18" s="2">
         <f t="shared" si="0"/>
-        <v>4.008394543546695E-5</v>
-      </c>
-      <c r="G18" s="5">
-        <v>232.8</v>
-      </c>
-      <c r="H18" s="9">
-        <f t="shared" si="1"/>
-        <v>2.120275636869835E-19</v>
+        <v>3.4445446348061322E-5</v>
+      </c>
+      <c r="G18" s="4">
+        <v>125.1</v>
+      </c>
+      <c r="H18" s="8">
+        <f t="shared" si="1"/>
+        <v>3.1431131897925522E-19</v>
       </c>
       <c r="I18" s="9"/>
-      <c r="L18" s="7">
+      <c r="L18" s="5">
         <v>1.5999999999999999E-19</v>
       </c>
-      <c r="M18" s="7"/>
+      <c r="M18" s="5"/>
       <c r="N18" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="2:14">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="19" spans="2:32">
       <c r="B19" s="2">
         <v>17</v>
       </c>
@@ -1832,29 +1889,29 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E19" s="4">
-        <v>17.25</v>
+        <v>11.04</v>
       </c>
       <c r="F19" s="2">
         <f t="shared" si="0"/>
-        <v>2.2144927536231886E-5</v>
-      </c>
-      <c r="G19" s="5">
-        <v>115.9</v>
-      </c>
-      <c r="H19" s="9">
-        <f t="shared" si="1"/>
-        <v>1.7488298802142485E-19</v>
+        <v>3.4601449275362325E-5</v>
+      </c>
+      <c r="G19" s="4">
+        <v>76.5</v>
+      </c>
+      <c r="H19" s="8">
+        <f t="shared" si="1"/>
+        <v>5.1748719137262963E-19</v>
       </c>
       <c r="I19" s="9"/>
-      <c r="L19" s="7">
+      <c r="L19" s="5">
         <v>1.7000000000000001E-19</v>
       </c>
-      <c r="M19" s="7"/>
+      <c r="M19" s="5"/>
       <c r="N19" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" spans="2:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="20" spans="2:32">
       <c r="B20" s="2">
         <v>18</v>
       </c>
@@ -1865,29 +1922,29 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E20" s="4">
-        <v>19.329999999999998</v>
+        <v>14.19</v>
       </c>
       <c r="F20" s="2">
         <f t="shared" si="0"/>
-        <v>1.9762027935851012E-5</v>
-      </c>
-      <c r="G20" s="5">
-        <v>69.599999999999994</v>
-      </c>
-      <c r="H20" s="9">
-        <f t="shared" si="1"/>
-        <v>2.455034668682092E-19</v>
+        <v>2.6920366455250178E-5</v>
+      </c>
+      <c r="G20" s="4">
+        <v>158.4</v>
+      </c>
+      <c r="H20" s="8">
+        <f t="shared" si="1"/>
+        <v>1.7150859120311481E-19</v>
       </c>
       <c r="I20" s="9"/>
-      <c r="L20" s="7">
+      <c r="L20" s="5">
         <v>1.8000000000000001E-19</v>
       </c>
-      <c r="M20" s="7"/>
+      <c r="M20" s="5"/>
       <c r="N20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="2:14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="2:32">
       <c r="B21" s="2">
         <v>19</v>
       </c>
@@ -1898,29 +1955,36 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E21" s="4">
-        <v>12.57</v>
+        <v>16.72</v>
       </c>
       <c r="F21" s="2">
         <f t="shared" si="0"/>
-        <v>3.0389817024661894E-5</v>
-      </c>
-      <c r="G21" s="5">
-        <v>211.8</v>
-      </c>
-      <c r="H21" s="9">
-        <f t="shared" si="1"/>
-        <v>1.5384584720296341E-19</v>
+        <v>2.2846889952153114E-5</v>
+      </c>
+      <c r="G21" s="4">
+        <v>143.1</v>
+      </c>
+      <c r="H21" s="8">
+        <f t="shared" si="1"/>
+        <v>1.4842963060041101E-19</v>
       </c>
       <c r="I21" s="9"/>
-      <c r="L21" s="7">
+      <c r="L21" s="5">
         <v>1.9E-19</v>
       </c>
-      <c r="M21" s="7"/>
+      <c r="M21" s="5"/>
       <c r="N21" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="11"/>
+      <c r="AA21" s="11"/>
+      <c r="AB21" s="11"/>
+      <c r="AC21" s="11"/>
+      <c r="AD21" s="11"/>
+      <c r="AE21" s="11"/>
+      <c r="AF21" s="11"/>
+    </row>
+    <row r="22" spans="2:32">
       <c r="B22" s="2">
         <v>20</v>
       </c>
@@ -1931,29 +1995,36 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E22" s="4">
-        <v>4.07</v>
+        <v>7.52</v>
       </c>
       <c r="F22" s="2">
         <f t="shared" si="0"/>
-        <v>9.385749385749386E-5</v>
-      </c>
-      <c r="G22" s="5">
-        <v>225.3</v>
-      </c>
-      <c r="H22" s="9">
-        <f t="shared" si="1"/>
-        <v>7.8498587920631624E-19</v>
+        <v>5.0797872340425537E-5</v>
+      </c>
+      <c r="G22" s="4">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="H22" s="8">
+        <f t="shared" si="1"/>
+        <v>5.1102091067173877E-19</v>
       </c>
       <c r="I22" s="9"/>
-      <c r="L22" s="7">
+      <c r="L22" s="5">
         <v>2E-19</v>
       </c>
-      <c r="M22" s="7"/>
+      <c r="M22" s="5"/>
       <c r="N22" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="2:14">
+      <c r="Z22" s="12"/>
+      <c r="AA22" s="12"/>
+      <c r="AB22" s="12"/>
+      <c r="AC22" s="12"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="12"/>
+      <c r="AF22" s="13"/>
+    </row>
+    <row r="23" spans="2:32">
       <c r="B23" s="2">
         <v>21</v>
       </c>
@@ -1964,29 +2035,36 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E23" s="4">
-        <v>8.24</v>
+        <v>14.71</v>
       </c>
       <c r="F23" s="2">
         <f t="shared" si="0"/>
-        <v>4.6359223300970875E-5</v>
-      </c>
-      <c r="G23" s="5">
-        <v>42.2</v>
-      </c>
-      <c r="H23" s="9">
-        <f t="shared" si="1"/>
-        <v>1.4548270972574926E-18</v>
+        <v>2.5968728755948334E-5</v>
+      </c>
+      <c r="G23" s="4">
+        <v>167.4</v>
+      </c>
+      <c r="H23" s="8">
+        <f t="shared" si="1"/>
+        <v>1.5375887306187692E-19</v>
       </c>
       <c r="I23" s="9"/>
-      <c r="L23" s="7">
+      <c r="L23" s="5">
         <v>2.0999999999999999E-19</v>
       </c>
-      <c r="M23" s="7"/>
+      <c r="M23" s="5"/>
       <c r="N23" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="12"/>
+      <c r="AA23" s="12"/>
+      <c r="AB23" s="12"/>
+      <c r="AC23" s="12"/>
+      <c r="AD23" s="13"/>
+      <c r="AE23" s="12"/>
+      <c r="AF23" s="13"/>
+    </row>
+    <row r="24" spans="2:32">
       <c r="B24" s="2">
         <v>22</v>
       </c>
@@ -1997,29 +2075,36 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E24" s="4">
-        <v>20.83</v>
+        <v>24.8</v>
       </c>
       <c r="F24" s="2">
         <f t="shared" si="0"/>
-        <v>1.8338934229476717E-5</v>
-      </c>
-      <c r="G24" s="5">
-        <v>92.9</v>
-      </c>
-      <c r="H24" s="9">
-        <f t="shared" si="1"/>
-        <v>1.6442393256488777E-19</v>
+        <v>1.5403225806451613E-5</v>
+      </c>
+      <c r="G24" s="4">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="H24" s="8">
+        <f t="shared" si="1"/>
+        <v>1.5910824683035385E-19</v>
       </c>
       <c r="I24" s="9"/>
-      <c r="L24" s="7">
+      <c r="L24" s="5">
         <v>2.1999999999999998E-19</v>
       </c>
-      <c r="M24" s="7"/>
+      <c r="M24" s="5"/>
       <c r="N24" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="12"/>
+      <c r="AA24" s="12"/>
+      <c r="AB24" s="12"/>
+      <c r="AC24" s="12"/>
+      <c r="AD24" s="13"/>
+      <c r="AE24" s="12"/>
+      <c r="AF24" s="13"/>
+    </row>
+    <row r="25" spans="2:32">
       <c r="B25" s="2">
         <v>23</v>
       </c>
@@ -2030,29 +2115,36 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E25" s="4">
-        <v>24.08</v>
+        <v>19.739999999999998</v>
       </c>
       <c r="F25" s="2">
         <f t="shared" si="0"/>
-        <v>1.5863787375415285E-5</v>
-      </c>
-      <c r="G25" s="5">
-        <v>72.900000000000006</v>
-      </c>
-      <c r="H25" s="9">
-        <f t="shared" si="1"/>
-        <v>1.6857858253870438E-19</v>
+        <v>1.9351570415400205E-5</v>
+      </c>
+      <c r="G25" s="4">
+        <v>102.4</v>
+      </c>
+      <c r="H25" s="8">
+        <f t="shared" si="1"/>
+        <v>1.616940246117234E-19</v>
       </c>
       <c r="I25" s="9"/>
-      <c r="L25" s="7">
+      <c r="L25" s="5">
         <v>2.2999999999999998E-19</v>
       </c>
-      <c r="M25" s="7"/>
+      <c r="M25" s="5"/>
       <c r="N25" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="12"/>
+      <c r="AA25" s="12"/>
+      <c r="AB25" s="12"/>
+      <c r="AC25" s="12"/>
+      <c r="AD25" s="13"/>
+      <c r="AE25" s="12"/>
+      <c r="AF25" s="13"/>
+    </row>
+    <row r="26" spans="2:32">
       <c r="B26" s="2">
         <v>24</v>
       </c>
@@ -2063,29 +2155,36 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E26" s="4">
-        <v>21.72</v>
+        <v>11.06</v>
       </c>
       <c r="F26" s="2">
         <f t="shared" si="0"/>
-        <v>1.7587476979742175E-5</v>
-      </c>
-      <c r="G26" s="5">
-        <v>288.10000000000002</v>
-      </c>
-      <c r="H26" s="9">
-        <f t="shared" si="1"/>
-        <v>4.9794532621128721E-20</v>
+        <v>3.4538878842676313E-5</v>
+      </c>
+      <c r="G26" s="4">
+        <v>124.4</v>
+      </c>
+      <c r="H26" s="8">
+        <f t="shared" si="1"/>
+        <v>3.1736686308447008E-19</v>
       </c>
       <c r="I26" s="9"/>
-      <c r="L26" s="7">
+      <c r="L26" s="5">
         <v>2.4000000000000002E-19</v>
       </c>
-      <c r="M26" s="7"/>
+      <c r="M26" s="5"/>
       <c r="N26" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="12"/>
+      <c r="AA26" s="12"/>
+      <c r="AB26" s="12"/>
+      <c r="AC26" s="12"/>
+      <c r="AD26" s="13"/>
+      <c r="AE26" s="12"/>
+      <c r="AF26" s="13"/>
+    </row>
+    <row r="27" spans="2:32">
       <c r="B27" s="2">
         <v>25</v>
       </c>
@@ -2096,29 +2195,39 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E27" s="4">
-        <v>15.03</v>
+        <v>17.2</v>
       </c>
       <c r="F27" s="2">
         <f t="shared" si="0"/>
-        <v>2.5415834996673323E-5</v>
-      </c>
-      <c r="G27" s="5">
-        <v>227.7</v>
-      </c>
-      <c r="H27" s="9">
-        <f t="shared" si="1"/>
-        <v>1.0944934037775462E-19</v>
+        <v>2.2209302325581396E-5</v>
+      </c>
+      <c r="G27" s="4">
+        <v>125.6</v>
+      </c>
+      <c r="H27" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6208108686427493E-19</v>
       </c>
       <c r="I27" s="9"/>
-      <c r="L27" s="7">
+      <c r="L27" s="5">
         <v>2.5000000000000002E-19</v>
       </c>
-      <c r="M27" s="7"/>
+      <c r="M27" s="5"/>
       <c r="N27" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="V27" s="11"/>
+      <c r="W27" s="11"/>
+      <c r="X27" s="11"/>
+      <c r="Y27" s="11"/>
+      <c r="AA27" s="11"/>
+      <c r="AB27" s="11"/>
+      <c r="AC27" s="11"/>
+      <c r="AD27" s="13"/>
+      <c r="AE27" s="11"/>
+      <c r="AF27" s="13"/>
+    </row>
+    <row r="28" spans="2:32">
       <c r="B28" s="2">
         <v>26</v>
       </c>
@@ -2129,29 +2238,40 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E28" s="4">
-        <v>21.33</v>
+        <v>5.45</v>
       </c>
       <c r="F28" s="2">
         <f t="shared" si="0"/>
-        <v>1.7909048288795127E-5</v>
-      </c>
-      <c r="G28" s="5">
-        <v>236.3</v>
-      </c>
-      <c r="H28" s="9">
-        <f t="shared" si="1"/>
-        <v>6.2382768602547688E-20</v>
+        <v>7.009174311926605E-5</v>
+      </c>
+      <c r="G28" s="4">
+        <v>141.19999999999999</v>
+      </c>
+      <c r="H28" s="8">
+        <f t="shared" si="1"/>
+        <v>8.0832349047428564E-19</v>
       </c>
       <c r="I28" s="9"/>
-      <c r="L28" s="7">
+      <c r="L28" s="5">
         <v>2.6000000000000001E-19</v>
       </c>
-      <c r="M28" s="7"/>
+      <c r="M28" s="5"/>
       <c r="N28" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="2:14">
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="12"/>
+      <c r="Z28" s="12"/>
+      <c r="AA28" s="12"/>
+      <c r="AB28" s="12"/>
+      <c r="AC28" s="12"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="12"/>
+      <c r="AF28" s="13"/>
+    </row>
+    <row r="29" spans="2:32">
       <c r="B29" s="2">
         <v>27</v>
       </c>
@@ -2162,29 +2282,40 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E29" s="4">
-        <v>18.649999999999999</v>
+        <v>24.13</v>
       </c>
       <c r="F29" s="2">
         <f t="shared" si="0"/>
-        <v>2.0482573726541557E-5</v>
-      </c>
-      <c r="G29" s="5">
-        <v>138.4</v>
-      </c>
-      <c r="H29" s="9">
-        <f t="shared" si="1"/>
-        <v>1.3027476717986452E-19</v>
+        <v>1.5830915872358062E-5</v>
+      </c>
+      <c r="G29" s="4">
+        <v>41.1</v>
+      </c>
+      <c r="H29" s="8">
+        <f t="shared" si="1"/>
+        <v>2.9808275074187584E-19</v>
       </c>
       <c r="I29" s="9"/>
-      <c r="L29" s="7">
+      <c r="L29" s="5">
         <v>2.7000000000000001E-19</v>
       </c>
-      <c r="M29" s="7"/>
+      <c r="M29" s="5"/>
       <c r="N29" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="2:14">
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="12"/>
+      <c r="Z29" s="12"/>
+      <c r="AA29" s="12"/>
+      <c r="AB29" s="12"/>
+      <c r="AC29" s="12"/>
+      <c r="AD29" s="13"/>
+      <c r="AE29" s="12"/>
+      <c r="AF29" s="13"/>
+    </row>
+    <row r="30" spans="2:32">
       <c r="B30" s="2">
         <v>28</v>
       </c>
@@ -2195,29 +2326,40 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E30" s="4">
-        <v>5.22</v>
+        <v>16.18</v>
       </c>
       <c r="F30" s="2">
         <f t="shared" si="0"/>
-        <v>7.3180076628352495E-5</v>
-      </c>
-      <c r="G30" s="5">
-        <v>134.5</v>
-      </c>
-      <c r="H30" s="9">
-        <f t="shared" si="1"/>
-        <v>9.05287682212827E-19</v>
+        <v>2.3609394313967864E-5</v>
+      </c>
+      <c r="G30" s="4">
+        <v>131.80000000000001</v>
+      </c>
+      <c r="H30" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6929006192718707E-19</v>
       </c>
       <c r="I30" s="9"/>
-      <c r="L30" s="7">
+      <c r="L30" s="5">
         <v>2.8E-19</v>
       </c>
-      <c r="M30" s="7"/>
+      <c r="M30" s="5"/>
       <c r="N30" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12"/>
+      <c r="AA30" s="12"/>
+      <c r="AB30" s="12"/>
+      <c r="AC30" s="12"/>
+      <c r="AD30" s="13"/>
+      <c r="AE30" s="12"/>
+      <c r="AF30" s="13"/>
+    </row>
+    <row r="31" spans="2:32">
       <c r="B31" s="2">
         <v>29</v>
       </c>
@@ -2228,29 +2370,40 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E31" s="4">
-        <v>17.170000000000002</v>
+        <v>22.61</v>
       </c>
       <c r="F31" s="2">
         <f t="shared" si="0"/>
-        <v>2.224810716365754E-5</v>
-      </c>
-      <c r="G31" s="5">
-        <v>111.2</v>
-      </c>
-      <c r="H31" s="9">
-        <f t="shared" si="1"/>
-        <v>1.835500131871435E-19</v>
+        <v>1.6895179124281292E-5</v>
+      </c>
+      <c r="G31" s="4">
+        <v>86.8</v>
+      </c>
+      <c r="H31" s="8">
+        <f t="shared" si="1"/>
+        <v>1.5561235717258572E-19</v>
       </c>
       <c r="I31" s="9"/>
-      <c r="L31" s="7">
+      <c r="L31" s="5">
         <v>2.9E-19</v>
       </c>
-      <c r="M31" s="7"/>
+      <c r="M31" s="5"/>
       <c r="N31" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="12"/>
+      <c r="Z31" s="12"/>
+      <c r="AA31" s="12"/>
+      <c r="AB31" s="12"/>
+      <c r="AC31" s="12"/>
+      <c r="AD31" s="13"/>
+      <c r="AE31" s="12"/>
+      <c r="AF31" s="13"/>
+    </row>
+    <row r="32" spans="2:32">
       <c r="B32" s="2">
         <v>30</v>
       </c>
@@ -2261,29 +2414,40 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E32" s="4">
-        <v>9.24</v>
+        <v>17.649999999999999</v>
       </c>
       <c r="F32" s="2">
         <f t="shared" si="0"/>
-        <v>4.1341991341991342E-5</v>
-      </c>
-      <c r="G32" s="5">
-        <v>247.1</v>
-      </c>
-      <c r="H32" s="9">
-        <f t="shared" si="1"/>
-        <v>2.0923481425821882E-19</v>
+        <v>2.1643059490084987E-5</v>
+      </c>
+      <c r="G32" s="4">
+        <v>61.4</v>
+      </c>
+      <c r="H32" s="8">
+        <f t="shared" si="1"/>
+        <v>3.1895485287977782E-19</v>
       </c>
       <c r="I32" s="9"/>
-      <c r="L32" s="7">
+      <c r="L32" s="5">
         <v>2.9999999999999999E-19</v>
       </c>
-      <c r="M32" s="7"/>
+      <c r="M32" s="5"/>
       <c r="N32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:14">
+        <v>1</v>
+      </c>
+      <c r="V32" s="12"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="13"/>
+      <c r="Y32" s="12"/>
+      <c r="Z32" s="12"/>
+      <c r="AA32" s="12"/>
+      <c r="AB32" s="12"/>
+      <c r="AC32" s="12"/>
+      <c r="AD32" s="13"/>
+      <c r="AE32" s="12"/>
+      <c r="AF32" s="13"/>
+    </row>
+    <row r="33" spans="2:32">
       <c r="B33" s="2">
         <v>31</v>
       </c>
@@ -2294,29 +2458,40 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E33" s="4">
-        <v>7.18</v>
+        <v>14.73</v>
       </c>
       <c r="F33" s="2">
         <f t="shared" si="0"/>
-        <v>5.3203342618384407E-5</v>
-      </c>
-      <c r="G33" s="5">
-        <v>169</v>
-      </c>
-      <c r="H33" s="9">
-        <f t="shared" si="1"/>
-        <v>4.4662320015468356E-19</v>
+        <v>2.5933469110658519E-5</v>
+      </c>
+      <c r="G33" s="4">
+        <v>156.4</v>
+      </c>
+      <c r="H33" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6423805038992107E-19</v>
       </c>
       <c r="I33" s="9"/>
-      <c r="L33" s="7">
+      <c r="L33" s="5">
         <v>3.0999999999999999E-19</v>
       </c>
-      <c r="M33" s="7"/>
+      <c r="M33" s="5"/>
       <c r="N33" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="34" spans="2:14">
+      <c r="V33" s="12"/>
+      <c r="W33" s="12"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="12"/>
+      <c r="Z33" s="12"/>
+      <c r="AA33" s="12"/>
+      <c r="AB33" s="12"/>
+      <c r="AC33" s="12"/>
+      <c r="AD33" s="13"/>
+      <c r="AE33" s="12"/>
+      <c r="AF33" s="13"/>
+    </row>
+    <row r="34" spans="2:32">
       <c r="B34" s="2">
         <v>32</v>
       </c>
@@ -2327,29 +2502,40 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E34" s="4">
-        <v>24.77</v>
+        <v>21.79</v>
       </c>
       <c r="F34" s="2">
         <f t="shared" si="0"/>
-        <v>1.5421881308033913E-5</v>
-      </c>
-      <c r="G34" s="5">
-        <v>272.8</v>
-      </c>
-      <c r="H34" s="9">
-        <f t="shared" si="1"/>
-        <v>4.3179864400352903E-20</v>
+        <v>1.753097751262047E-5</v>
+      </c>
+      <c r="G34" s="4">
+        <v>89.2</v>
+      </c>
+      <c r="H34" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6005304842643498E-19</v>
       </c>
       <c r="I34" s="9"/>
-      <c r="L34" s="7">
+      <c r="L34" s="5">
         <v>3.1999999999999998E-19</v>
       </c>
-      <c r="M34" s="7"/>
+      <c r="M34" s="5"/>
       <c r="N34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:14">
+        <v>8</v>
+      </c>
+      <c r="V34" s="12"/>
+      <c r="W34" s="12"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="12"/>
+      <c r="Z34" s="12"/>
+      <c r="AA34" s="12"/>
+      <c r="AB34" s="12"/>
+      <c r="AC34" s="12"/>
+      <c r="AD34" s="13"/>
+      <c r="AE34" s="12"/>
+      <c r="AF34" s="13"/>
+    </row>
+    <row r="35" spans="2:32">
       <c r="B35" s="2">
         <v>33</v>
       </c>
@@ -2360,29 +2546,40 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E35" s="4">
-        <v>21.62</v>
+        <v>16.899999999999999</v>
       </c>
       <c r="F35" s="2">
         <f t="shared" si="0"/>
-        <v>1.766882516188714E-5</v>
-      </c>
-      <c r="G35" s="5">
-        <v>50.9</v>
-      </c>
-      <c r="H35" s="9">
-        <f t="shared" si="1"/>
-        <v>2.8380061566768923E-19</v>
+        <v>2.2603550295857992E-5</v>
+      </c>
+      <c r="G35" s="4">
+        <v>138.80000000000001</v>
+      </c>
+      <c r="H35" s="8">
+        <f t="shared" si="1"/>
+        <v>1.5058965106882606E-19</v>
       </c>
       <c r="I35" s="9"/>
-      <c r="L35" s="7">
+      <c r="L35" s="5">
         <v>3.2999999999999998E-19</v>
       </c>
-      <c r="M35" s="7"/>
+      <c r="M35" s="5"/>
       <c r="N35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:14">
+        <v>2</v>
+      </c>
+      <c r="V35" s="12"/>
+      <c r="W35" s="12"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="12"/>
+      <c r="Z35" s="12"/>
+      <c r="AA35" s="12"/>
+      <c r="AB35" s="12"/>
+      <c r="AC35" s="12"/>
+      <c r="AD35" s="13"/>
+      <c r="AE35" s="12"/>
+      <c r="AF35" s="13"/>
+    </row>
+    <row r="36" spans="2:32">
       <c r="B36" s="2">
         <v>34</v>
       </c>
@@ -2393,29 +2590,40 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E36" s="4">
-        <v>8.11</v>
+        <v>12.78</v>
       </c>
       <c r="F36" s="2">
         <f t="shared" si="0"/>
-        <v>4.710234278668311E-5</v>
-      </c>
-      <c r="G36" s="5">
-        <v>170.8</v>
-      </c>
-      <c r="H36" s="9">
-        <f t="shared" si="1"/>
-        <v>3.6812516124506652E-19</v>
+        <v>2.9890453834115809E-5</v>
+      </c>
+      <c r="G36" s="4">
+        <v>64.8</v>
+      </c>
+      <c r="H36" s="8">
+        <f t="shared" si="1"/>
+        <v>4.905049149232246E-19</v>
       </c>
       <c r="I36" s="9"/>
-      <c r="L36" s="7">
+      <c r="L36" s="5">
         <v>3.4000000000000002E-19</v>
       </c>
-      <c r="M36" s="7"/>
+      <c r="M36" s="5"/>
       <c r="N36" s="1">
         <v>1</v>
       </c>
-    </row>
-    <row r="37" spans="2:14">
+      <c r="V36" s="12"/>
+      <c r="W36" s="12"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="12"/>
+      <c r="Z36" s="12"/>
+      <c r="AA36" s="12"/>
+      <c r="AB36" s="12"/>
+      <c r="AC36" s="12"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="12"/>
+      <c r="AF36" s="13"/>
+    </row>
+    <row r="37" spans="2:32" ht="30">
       <c r="B37" s="2">
         <v>35</v>
       </c>
@@ -2426,29 +2634,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E37" s="4">
-        <v>22.34</v>
+        <v>10.06</v>
       </c>
       <c r="F37" s="2">
         <f t="shared" si="0"/>
-        <v>1.70993733213966E-5</v>
-      </c>
-      <c r="G37" s="5">
-        <v>174.5</v>
-      </c>
-      <c r="H37" s="9">
-        <f t="shared" si="1"/>
-        <v>7.8812384156677962E-20</v>
+        <v>3.7972166998011931E-5</v>
+      </c>
+      <c r="G37" s="4">
+        <v>276.39999999999998</v>
+      </c>
+      <c r="H37" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6465678837048874E-19</v>
       </c>
       <c r="I37" s="9"/>
-      <c r="L37" s="7">
+      <c r="L37" s="5">
         <v>3.5000000000000002E-19</v>
       </c>
-      <c r="M37" s="7"/>
+      <c r="M37" s="5"/>
       <c r="N37" s="1">
+        <v>2</v>
+      </c>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="13" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" spans="2:14">
+      <c r="Y37" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="AA37" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AB37" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AC37" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD37" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE37" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF37" s="13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="38" spans="2:32">
       <c r="B38" s="2">
         <v>36</v>
       </c>
@@ -2459,29 +2696,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E38" s="4">
-        <v>23.16</v>
+        <v>10.27</v>
       </c>
       <c r="F38" s="2">
         <f t="shared" si="0"/>
-        <v>1.6493955094991366E-5</v>
-      </c>
-      <c r="G38" s="5">
-        <v>123.9</v>
-      </c>
-      <c r="H38" s="9">
-        <f t="shared" si="1"/>
-        <v>1.0515635189613713E-19</v>
+        <v>3.7195715676728335E-5</v>
+      </c>
+      <c r="G38" s="4">
+        <v>55.2</v>
+      </c>
+      <c r="H38" s="8">
+        <f t="shared" si="1"/>
+        <v>7.9931857766050533E-19</v>
       </c>
       <c r="I38" s="9"/>
-      <c r="L38" s="7">
+      <c r="L38" s="5">
         <v>3.6000000000000001E-19</v>
       </c>
-      <c r="M38" s="7"/>
+      <c r="M38" s="5"/>
       <c r="N38" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="39" spans="2:14">
+      <c r="V38" s="12"/>
+      <c r="W38" s="12"/>
+      <c r="X38" s="13">
+        <v>1</v>
+      </c>
+      <c r="Y38" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA38" s="12">
+        <v>19.71</v>
+      </c>
+      <c r="AB38" s="13">
+        <v>1.9381E-5</v>
+      </c>
+      <c r="AC38" s="12">
+        <v>102.5</v>
+      </c>
+      <c r="AD38" s="13">
+        <v>1.6375E-19</v>
+      </c>
+      <c r="AE38" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="13">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="39" spans="2:32">
       <c r="B39" s="2">
         <v>37</v>
       </c>
@@ -2492,29 +2758,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E39" s="4">
-        <v>15.57</v>
+        <v>6.63</v>
       </c>
       <c r="F39" s="2">
         <f t="shared" si="0"/>
-        <v>2.4534360950545924E-5</v>
-      </c>
-      <c r="G39" s="5">
-        <v>345.3</v>
-      </c>
-      <c r="H39" s="9">
-        <f t="shared" si="1"/>
-        <v>6.8451844141021412E-20</v>
+        <v>5.7616892911010564E-5</v>
+      </c>
+      <c r="G39" s="4">
+        <v>256.10000000000002</v>
+      </c>
+      <c r="H39" s="8">
+        <f t="shared" si="1"/>
+        <v>3.3215039936244537E-19</v>
       </c>
       <c r="I39" s="9"/>
-      <c r="L39" s="7">
+      <c r="L39" s="5">
         <v>3.7000000000000001E-19</v>
       </c>
-      <c r="M39" s="7"/>
+      <c r="M39" s="5"/>
       <c r="N39" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="V39" s="12"/>
+      <c r="W39" s="12"/>
+      <c r="X39" s="13">
+        <v>2</v>
+      </c>
+      <c r="Y39" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA39" s="12">
+        <v>10.130000000000001</v>
+      </c>
+      <c r="AB39" s="13">
+        <v>3.7709800000000003E-5</v>
+      </c>
+      <c r="AC39" s="12">
+        <v>93.4</v>
+      </c>
+      <c r="AD39" s="13">
+        <v>4.9646E-19</v>
+      </c>
+      <c r="AE39" s="12">
+        <v>3</v>
+      </c>
+      <c r="AF39" s="13">
+        <v>3.29</v>
+      </c>
+    </row>
+    <row r="40" spans="2:32">
       <c r="B40" s="2">
         <v>38</v>
       </c>
@@ -2525,29 +2820,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E40" s="4">
-        <v>12.09</v>
+        <v>9.93</v>
       </c>
       <c r="F40" s="2">
         <f t="shared" si="0"/>
-        <v>3.1596360628618697E-5</v>
-      </c>
-      <c r="G40" s="5">
-        <v>213.2</v>
-      </c>
-      <c r="H40" s="9">
-        <f t="shared" si="1"/>
-        <v>1.6202722663136051E-19</v>
+        <v>3.8469284994964755E-5</v>
+      </c>
+      <c r="G40" s="4">
+        <v>270.2</v>
+      </c>
+      <c r="H40" s="8">
+        <f t="shared" si="1"/>
+        <v>1.7175343542151431E-19</v>
       </c>
       <c r="I40" s="9"/>
-      <c r="L40" s="7">
+      <c r="L40" s="5">
         <v>3.8E-19</v>
       </c>
-      <c r="M40" s="7"/>
+      <c r="M40" s="5"/>
       <c r="N40" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="41" spans="2:14">
+      <c r="V40" s="12"/>
+      <c r="W40" s="12"/>
+      <c r="X40" s="13">
+        <v>3</v>
+      </c>
+      <c r="Y40" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA40" s="12">
+        <v>25.52</v>
+      </c>
+      <c r="AB40" s="13">
+        <v>1.49687E-5</v>
+      </c>
+      <c r="AC40" s="12">
+        <v>73.099999999999994</v>
+      </c>
+      <c r="AD40" s="13">
+        <v>1.5435E-19</v>
+      </c>
+      <c r="AE40" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="13">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="41" spans="2:32">
       <c r="B41" s="2">
         <v>39</v>
       </c>
@@ -2558,29 +2882,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E41" s="4">
-        <v>5.45</v>
+        <v>18.13</v>
       </c>
       <c r="F41" s="2">
         <f t="shared" si="0"/>
-        <v>7.009174311926605E-5</v>
-      </c>
-      <c r="G41" s="5">
-        <v>253.3</v>
-      </c>
-      <c r="H41" s="9">
-        <f t="shared" si="1"/>
-        <v>4.5059327617437475E-19</v>
+        <v>2.1070049641478214E-5</v>
+      </c>
+      <c r="G41" s="4">
+        <v>58.7</v>
+      </c>
+      <c r="H41" s="8">
+        <f t="shared" si="1"/>
+        <v>3.2046443789041549E-19</v>
       </c>
       <c r="I41" s="9"/>
-      <c r="L41" s="7">
+      <c r="L41" s="5">
         <v>3.9E-19</v>
       </c>
-      <c r="M41" s="7"/>
+      <c r="M41" s="5"/>
       <c r="N41" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="42" spans="2:14">
+      <c r="V41" s="12"/>
+      <c r="W41" s="12"/>
+      <c r="X41" s="13">
+        <v>4</v>
+      </c>
+      <c r="Y41" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA41" s="12">
+        <v>17.53</v>
+      </c>
+      <c r="AB41" s="13">
+        <v>2.1791199999999999E-5</v>
+      </c>
+      <c r="AC41" s="12">
+        <v>115.8</v>
+      </c>
+      <c r="AD41" s="13">
+        <v>1.6853E-19</v>
+      </c>
+      <c r="AE41" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="13">
+        <v>5.2</v>
+      </c>
+    </row>
+    <row r="42" spans="2:32">
       <c r="B42" s="2">
         <v>40</v>
       </c>
@@ -2591,29 +2944,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E42" s="4">
-        <v>20.53</v>
+        <v>23.57</v>
       </c>
       <c r="F42" s="2">
         <f t="shared" si="0"/>
-        <v>1.8606916707257671E-5</v>
-      </c>
-      <c r="G42" s="5">
-        <v>169.8</v>
-      </c>
-      <c r="H42" s="9">
-        <f t="shared" si="1"/>
-        <v>9.193767993870622E-20</v>
+        <v>1.6207042851081884E-5</v>
+      </c>
+      <c r="G42" s="4">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="H42" s="8">
+        <f t="shared" si="1"/>
+        <v>1.5744911883144483E-19</v>
       </c>
       <c r="I42" s="9"/>
-      <c r="L42" s="7">
+      <c r="L42" s="5">
         <v>3.9999999999999999E-19</v>
       </c>
-      <c r="M42" s="7"/>
+      <c r="M42" s="5"/>
       <c r="N42" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="V42" s="12"/>
+      <c r="W42" s="12"/>
+      <c r="X42" s="13">
+        <v>5</v>
+      </c>
+      <c r="Y42" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA42" s="12">
+        <v>23.62</v>
+      </c>
+      <c r="AB42" s="13">
+        <v>1.6172699999999998E-5</v>
+      </c>
+      <c r="AC42" s="12">
+        <v>78.400000000000006</v>
+      </c>
+      <c r="AD42" s="13">
+        <v>1.5644999999999999E-19</v>
+      </c>
+      <c r="AE42" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="13">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="43" spans="2:32">
       <c r="B43" s="2">
         <v>41</v>
       </c>
@@ -2624,29 +3006,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E43" s="4">
-        <v>24.92</v>
+        <v>14.91</v>
       </c>
       <c r="F43" s="2">
         <f t="shared" si="0"/>
-        <v>1.5329052969502406E-5</v>
-      </c>
-      <c r="G43" s="5">
-        <v>332.7</v>
-      </c>
-      <c r="H43" s="9">
-        <f t="shared" si="1"/>
-        <v>3.5086479332700357E-20</v>
+        <v>2.562038900067069E-5</v>
+      </c>
+      <c r="G43" s="4">
+        <v>81.3</v>
+      </c>
+      <c r="H43" s="8">
+        <f t="shared" si="1"/>
+        <v>3.1024703469583505E-19</v>
       </c>
       <c r="I43" s="9"/>
-      <c r="L43" s="7">
+      <c r="L43" s="5">
         <v>4.0999999999999999E-19</v>
       </c>
-      <c r="M43" s="7"/>
+      <c r="M43" s="5"/>
       <c r="N43" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14">
+      <c r="V43" s="12"/>
+      <c r="W43" s="12"/>
+      <c r="X43" s="13">
+        <v>6</v>
+      </c>
+      <c r="Y43" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA43" s="12">
+        <v>21.06</v>
+      </c>
+      <c r="AB43" s="13">
+        <v>1.81387E-5</v>
+      </c>
+      <c r="AC43" s="12">
+        <v>47.3</v>
+      </c>
+      <c r="AD43" s="13">
+        <v>3.1256000000000001E-19</v>
+      </c>
+      <c r="AE43" s="12">
+        <v>2</v>
+      </c>
+      <c r="AF43" s="13">
+        <v>2.4500000000000002</v>
+      </c>
+    </row>
+    <row r="44" spans="2:32">
       <c r="B44" s="2">
         <v>42</v>
       </c>
@@ -2657,29 +3068,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E44" s="4">
-        <v>3.75</v>
+        <v>7.26</v>
       </c>
       <c r="F44" s="2">
         <f t="shared" si="0"/>
-        <v>1.0186666666666667E-4</v>
-      </c>
-      <c r="G44" s="5">
-        <v>222.6</v>
-      </c>
-      <c r="H44" s="9">
-        <f t="shared" si="1"/>
-        <v>8.98343828154446E-19</v>
+        <v>5.2617079889807166E-5</v>
+      </c>
+      <c r="G44" s="4">
+        <v>230.7</v>
+      </c>
+      <c r="H44" s="8">
+        <f t="shared" si="1"/>
+        <v>3.2178227991935692E-19</v>
       </c>
       <c r="I44" s="9"/>
-      <c r="L44" s="7">
+      <c r="L44" s="5">
         <v>4.1999999999999998E-19</v>
       </c>
-      <c r="M44" s="7"/>
+      <c r="M44" s="5"/>
       <c r="N44" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="45" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="V44" s="12"/>
+      <c r="W44" s="12"/>
+      <c r="X44" s="13">
+        <v>7</v>
+      </c>
+      <c r="Y44" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA44" s="12">
+        <v>7.22</v>
+      </c>
+      <c r="AB44" s="13">
+        <v>5.2908599999999997E-5</v>
+      </c>
+      <c r="AC44" s="12">
+        <v>118.2</v>
+      </c>
+      <c r="AD44" s="13">
+        <v>6.7450999999999998E-19</v>
+      </c>
+      <c r="AE44" s="12">
+        <v>4</v>
+      </c>
+      <c r="AF44" s="13">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="45" spans="2:32">
       <c r="B45" s="2">
         <v>43</v>
       </c>
@@ -2690,29 +3130,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E45" s="4">
-        <v>9.24</v>
+        <v>15.32</v>
       </c>
       <c r="F45" s="2">
         <f t="shared" si="0"/>
-        <v>4.1341991341991342E-5</v>
-      </c>
-      <c r="G45" s="5">
-        <v>187.8</v>
-      </c>
-      <c r="H45" s="9">
-        <f t="shared" si="1"/>
-        <v>2.7530310225349235E-19</v>
+        <v>2.4934725848563968E-5</v>
+      </c>
+      <c r="G45" s="4">
+        <v>75.8</v>
+      </c>
+      <c r="H45" s="8">
+        <f t="shared" si="1"/>
+        <v>3.1949001994516714E-19</v>
       </c>
       <c r="I45" s="9"/>
-      <c r="L45" s="7">
+      <c r="L45" s="5">
         <v>4.3000000000000002E-19</v>
       </c>
-      <c r="M45" s="7"/>
+      <c r="M45" s="5"/>
       <c r="N45" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="V45" s="12"/>
+      <c r="W45" s="12"/>
+      <c r="X45" s="13">
+        <v>8</v>
+      </c>
+      <c r="Y45" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA45" s="12">
+        <v>18.28</v>
+      </c>
+      <c r="AB45" s="13">
+        <v>2.08972E-5</v>
+      </c>
+      <c r="AC45" s="12">
+        <v>42.1</v>
+      </c>
+      <c r="AD45" s="13">
+        <v>4.6542E-19</v>
+      </c>
+      <c r="AE45" s="12">
+        <v>3</v>
+      </c>
+      <c r="AF45" s="13">
+        <v>3.16</v>
+      </c>
+    </row>
+    <row r="46" spans="2:32">
       <c r="B46" s="2">
         <v>44</v>
       </c>
@@ -2723,29 +3192,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E46" s="4">
-        <v>13.26</v>
+        <v>10.75</v>
       </c>
       <c r="F46" s="2">
         <f t="shared" si="0"/>
-        <v>2.8808446455505282E-5</v>
-      </c>
-      <c r="G46" s="5">
-        <v>129.6</v>
-      </c>
-      <c r="H46" s="9">
-        <f t="shared" si="1"/>
-        <v>2.3205683379361788E-19</v>
+        <v>3.5534883720930237E-5</v>
+      </c>
+      <c r="G46" s="4">
+        <v>49.5</v>
+      </c>
+      <c r="H46" s="8">
+        <f t="shared" si="1"/>
+        <v>8.3233231199566174E-19</v>
       </c>
       <c r="I46" s="9"/>
-      <c r="L46" s="7">
+      <c r="L46" s="5">
         <v>4.3999999999999997E-19</v>
       </c>
-      <c r="M46" s="7"/>
+      <c r="M46" s="5"/>
       <c r="N46" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="47" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="V46" s="12"/>
+      <c r="W46" s="12"/>
+      <c r="X46" s="13">
+        <v>9</v>
+      </c>
+      <c r="Y46" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA46" s="12">
+        <v>10.24</v>
+      </c>
+      <c r="AB46" s="13">
+        <v>3.7304700000000002E-5</v>
+      </c>
+      <c r="AC46" s="12">
+        <v>141.5</v>
+      </c>
+      <c r="AD46" s="13">
+        <v>3.1189000000000002E-19</v>
+      </c>
+      <c r="AE46" s="12">
+        <v>2</v>
+      </c>
+      <c r="AF46" s="13">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="47" spans="2:32">
       <c r="B47" s="2">
         <v>45</v>
       </c>
@@ -2756,29 +3254,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E47" s="4">
-        <v>14.26</v>
+        <v>16.170000000000002</v>
       </c>
       <c r="F47" s="2">
         <f t="shared" si="0"/>
-        <v>2.6788218793828895E-5</v>
-      </c>
-      <c r="G47" s="5">
-        <v>336</v>
-      </c>
-      <c r="H47" s="9">
-        <f t="shared" si="1"/>
-        <v>8.0259432458438495E-20</v>
+        <v>2.3623995052566481E-5</v>
+      </c>
+      <c r="G47" s="4">
+        <v>137.9</v>
+      </c>
+      <c r="H47" s="8">
+        <f t="shared" si="1"/>
+        <v>1.6195164139881523E-19</v>
       </c>
       <c r="I47" s="9"/>
-      <c r="L47" s="7">
+      <c r="L47" s="5">
         <v>4.5000000000000001E-19</v>
       </c>
-      <c r="M47" s="7"/>
+      <c r="M47" s="5"/>
       <c r="N47" s="1">
         <v>2</v>
       </c>
-    </row>
-    <row r="48" spans="2:14">
+      <c r="V47" s="12"/>
+      <c r="W47" s="12"/>
+      <c r="X47" s="13">
+        <v>10</v>
+      </c>
+      <c r="Y47" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA47" s="12">
+        <v>10.35</v>
+      </c>
+      <c r="AB47" s="13">
+        <v>3.69082E-5</v>
+      </c>
+      <c r="AC47" s="12">
+        <v>268.39999999999998</v>
+      </c>
+      <c r="AD47" s="13">
+        <v>1.6432E-19</v>
+      </c>
+      <c r="AE47" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF47" s="13">
+        <v>2.57</v>
+      </c>
+    </row>
+    <row r="48" spans="2:32">
       <c r="B48" s="2">
         <v>46</v>
       </c>
@@ -2789,29 +3316,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E48" s="4">
-        <v>9.92</v>
+        <v>6.35</v>
       </c>
       <c r="F48" s="2">
         <f t="shared" si="0"/>
-        <v>3.8508064516129036E-5</v>
-      </c>
-      <c r="G48" s="5">
-        <v>92</v>
-      </c>
-      <c r="H48" s="9">
-        <f t="shared" si="1"/>
-        <v>5.0519531504841948E-19</v>
+        <v>6.0157480314960636E-5</v>
+      </c>
+      <c r="G48" s="4">
+        <v>262.39999999999998</v>
+      </c>
+      <c r="H48" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4585195215408273E-19</v>
       </c>
       <c r="I48" s="9"/>
-      <c r="L48" s="7">
+      <c r="L48" s="5">
         <v>4.5999999999999996E-19</v>
       </c>
-      <c r="M48" s="7"/>
+      <c r="M48" s="5"/>
       <c r="N48" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="49" spans="2:14">
+        <v>0</v>
+      </c>
+      <c r="V48" s="12"/>
+      <c r="W48" s="12"/>
+      <c r="X48" s="13">
+        <v>11</v>
+      </c>
+      <c r="Y48" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z48" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA48" s="12">
+        <v>19.62</v>
+      </c>
+      <c r="AB48" s="13">
+        <v>1.9469900000000001E-5</v>
+      </c>
+      <c r="AC48" s="12">
+        <v>54.2</v>
+      </c>
+      <c r="AD48" s="13">
+        <v>3.119E-19</v>
+      </c>
+      <c r="AE48" s="12">
+        <v>2</v>
+      </c>
+      <c r="AF48" s="13">
+        <v>2.65</v>
+      </c>
+    </row>
+    <row r="49" spans="2:32">
       <c r="B49" s="2">
         <v>47</v>
       </c>
@@ -2822,29 +3378,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E49" s="4">
-        <v>19.89</v>
+        <v>11.1</v>
       </c>
       <c r="F49" s="2">
         <f t="shared" si="0"/>
-        <v>1.9205630970336851E-5</v>
-      </c>
-      <c r="G49" s="5">
-        <v>220.3</v>
-      </c>
-      <c r="H49" s="9">
-        <f t="shared" si="1"/>
-        <v>7.4310122663013932E-20</v>
+        <v>3.4414414414414419E-5</v>
+      </c>
+      <c r="G49" s="4">
+        <v>63.3</v>
+      </c>
+      <c r="H49" s="8">
+        <f t="shared" si="1"/>
+        <v>6.2033526652246278E-19</v>
       </c>
       <c r="I49" s="9"/>
-      <c r="L49" s="7">
+      <c r="L49" s="5">
         <v>4.7E-19</v>
       </c>
-      <c r="M49" s="7"/>
+      <c r="M49" s="5"/>
       <c r="N49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" spans="2:14">
+      <c r="V49" s="12"/>
+      <c r="W49" s="12"/>
+      <c r="X49" s="13">
+        <v>12</v>
+      </c>
+      <c r="Y49" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z49" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA49" s="12">
+        <v>9.82</v>
+      </c>
+      <c r="AB49" s="13">
+        <v>3.8900199999999997E-5</v>
+      </c>
+      <c r="AC49" s="12">
+        <v>148.6</v>
+      </c>
+      <c r="AD49" s="13">
+        <v>3.3289E-19</v>
+      </c>
+      <c r="AE49" s="12">
+        <v>2</v>
+      </c>
+      <c r="AF49" s="13">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="50" spans="2:32">
       <c r="B50" s="2">
         <v>48</v>
       </c>
@@ -2855,29 +3440,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E50" s="4">
-        <v>8.11</v>
+        <v>17.78</v>
       </c>
       <c r="F50" s="2">
         <f t="shared" si="0"/>
-        <v>4.710234278668311E-5</v>
-      </c>
-      <c r="G50" s="6">
-        <v>170.8</v>
-      </c>
-      <c r="H50" s="9">
-        <f t="shared" si="1"/>
-        <v>3.6812516124506652E-19</v>
+        <v>2.1484814398200224E-5</v>
+      </c>
+      <c r="G50" s="4">
+        <v>43.5</v>
+      </c>
+      <c r="H50" s="8">
+        <f t="shared" si="1"/>
+        <v>4.4527443179394587E-19</v>
       </c>
       <c r="I50" s="9"/>
-      <c r="L50" s="7">
+      <c r="L50" s="5">
         <v>4.8000000000000005E-19</v>
       </c>
-      <c r="M50" s="7"/>
+      <c r="M50" s="5"/>
       <c r="N50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="2:14">
+      <c r="V50" s="12"/>
+      <c r="W50" s="12"/>
+      <c r="X50" s="13">
+        <v>13</v>
+      </c>
+      <c r="Y50" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z50" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA50" s="12">
+        <v>21.77</v>
+      </c>
+      <c r="AB50" s="13">
+        <v>1.75471E-5</v>
+      </c>
+      <c r="AC50" s="12">
+        <v>93.6</v>
+      </c>
+      <c r="AD50" s="13">
+        <v>1.5456000000000001E-19</v>
+      </c>
+      <c r="AE50" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF50" s="13">
+        <v>3.52</v>
+      </c>
+    </row>
+    <row r="51" spans="2:32">
       <c r="B51" s="2">
         <v>49</v>
       </c>
@@ -2888,29 +3502,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E51" s="4">
-        <v>22.39</v>
+        <v>11.82</v>
       </c>
       <c r="F51" s="2">
         <f t="shared" si="0"/>
-        <v>1.7061188030370701E-5</v>
-      </c>
-      <c r="G51" s="5">
-        <v>59.7</v>
-      </c>
-      <c r="H51" s="9">
-        <f t="shared" si="1"/>
-        <v>2.2959328319809843E-19</v>
+        <v>3.2318104906937397E-5</v>
+      </c>
+      <c r="G51" s="4">
+        <v>43.1</v>
+      </c>
+      <c r="H51" s="8">
+        <f t="shared" si="1"/>
+        <v>8.2910811342124125E-19</v>
       </c>
       <c r="I51" s="9"/>
-      <c r="L51" s="7">
+      <c r="L51" s="5">
         <v>4.8999999999999999E-19</v>
       </c>
-      <c r="M51" s="7"/>
+      <c r="M51" s="5"/>
       <c r="N51" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:14">
+        <v>1</v>
+      </c>
+      <c r="V51" s="12"/>
+      <c r="W51" s="12"/>
+      <c r="X51" s="13">
+        <v>14</v>
+      </c>
+      <c r="Y51" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA51" s="12">
+        <v>10.27</v>
+      </c>
+      <c r="AB51" s="13">
+        <v>3.71957E-5</v>
+      </c>
+      <c r="AC51" s="12">
+        <v>272.5</v>
+      </c>
+      <c r="AD51" s="13">
+        <v>1.6579999999999999E-19</v>
+      </c>
+      <c r="AE51" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF51" s="13">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="52" spans="2:32">
       <c r="B52" s="2">
         <v>50</v>
       </c>
@@ -2921,29 +3564,58 @@
         <v>3.8200000000000002E-4</v>
       </c>
       <c r="E52" s="4">
-        <v>22.38</v>
+        <v>18.440000000000001</v>
       </c>
       <c r="F52" s="2">
         <f t="shared" si="0"/>
-        <v>1.706881143878463E-5</v>
-      </c>
-      <c r="G52" s="5">
-        <v>205.2</v>
-      </c>
-      <c r="H52" s="9">
-        <f t="shared" si="1"/>
-        <v>6.6841651277123587E-20</v>
+        <v>2.0715835140997831E-5</v>
+      </c>
+      <c r="G52" s="4">
+        <v>53</v>
+      </c>
+      <c r="H52" s="8">
+        <f t="shared" si="1"/>
+        <v>3.4601697523378286E-19</v>
       </c>
       <c r="I52" s="9"/>
-      <c r="L52" s="7">
+      <c r="L52" s="5">
         <v>5.0000000000000004E-19</v>
       </c>
-      <c r="M52" s="7"/>
+      <c r="M52" s="5"/>
       <c r="N52" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:14">
+        <v>1</v>
+      </c>
+      <c r="V52" s="12"/>
+      <c r="W52" s="12"/>
+      <c r="X52" s="13">
+        <v>15</v>
+      </c>
+      <c r="Y52" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z52" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA52" s="12">
+        <v>11.16</v>
+      </c>
+      <c r="AB52" s="13">
+        <v>3.4229400000000001E-5</v>
+      </c>
+      <c r="AC52" s="12">
+        <v>224.8</v>
+      </c>
+      <c r="AD52" s="13">
+        <v>1.7051000000000001E-19</v>
+      </c>
+      <c r="AE52" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF52" s="13">
+        <v>6.43</v>
+      </c>
+    </row>
+    <row r="53" spans="2:32">
       <c r="B53" s="2">
         <v>51</v>
       </c>
@@ -2959,20 +3631,49 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G53" s="4"/>
-      <c r="H53" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I53" s="9"/>
-      <c r="L53" s="8" t="s">
+      <c r="H53" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I53" s="7"/>
+      <c r="L53" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="M53" s="8"/>
+      <c r="M53" s="6"/>
       <c r="N53" s="1">
         <v>7</v>
       </c>
-    </row>
-    <row r="54" spans="2:14">
+      <c r="V53" s="12"/>
+      <c r="W53" s="12"/>
+      <c r="X53" s="13">
+        <v>16</v>
+      </c>
+      <c r="Y53" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z53" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA53" s="12">
+        <v>11.09</v>
+      </c>
+      <c r="AB53" s="13">
+        <v>3.4445400000000001E-5</v>
+      </c>
+      <c r="AC53" s="12">
+        <v>125.1</v>
+      </c>
+      <c r="AD53" s="13">
+        <v>3.1294000000000001E-19</v>
+      </c>
+      <c r="AE53" s="12">
+        <v>2</v>
+      </c>
+      <c r="AF53" s="13">
+        <v>2.33</v>
+      </c>
+    </row>
+    <row r="54" spans="2:32">
       <c r="B54" s="2">
         <v>52</v>
       </c>
@@ -2988,13 +3689,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G54" s="4"/>
-      <c r="H54" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I54" s="9"/>
-    </row>
-    <row r="55" spans="2:14">
+      <c r="H54" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I54" s="7"/>
+      <c r="V54" s="12"/>
+      <c r="W54" s="12"/>
+      <c r="X54" s="13">
+        <v>17</v>
+      </c>
+      <c r="Y54" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z54" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA54" s="12">
+        <v>11.04</v>
+      </c>
+      <c r="AB54" s="13">
+        <v>3.4601399999999997E-5</v>
+      </c>
+      <c r="AC54" s="12">
+        <v>76.5</v>
+      </c>
+      <c r="AD54" s="13">
+        <v>5.0563999999999995E-19</v>
+      </c>
+      <c r="AE54" s="12">
+        <v>3</v>
+      </c>
+      <c r="AF54" s="13">
+        <v>5.21</v>
+      </c>
+    </row>
+    <row r="55" spans="2:32">
       <c r="B55" s="2">
         <v>53</v>
       </c>
@@ -3010,13 +3740,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G55" s="4"/>
-      <c r="H55" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I55" s="9"/>
-    </row>
-    <row r="56" spans="2:14">
+      <c r="H55" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I55" s="7"/>
+      <c r="V55" s="12"/>
+      <c r="W55" s="12"/>
+      <c r="X55" s="13">
+        <v>18</v>
+      </c>
+      <c r="Y55" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z55" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA55" s="12">
+        <v>14.19</v>
+      </c>
+      <c r="AB55" s="13">
+        <v>2.6920400000000001E-5</v>
+      </c>
+      <c r="AC55" s="12">
+        <v>158.4</v>
+      </c>
+      <c r="AD55" s="13">
+        <v>1.7084000000000001E-19</v>
+      </c>
+      <c r="AE55" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="13">
+        <v>6.64</v>
+      </c>
+    </row>
+    <row r="56" spans="2:32">
       <c r="B56" s="2">
         <v>54</v>
       </c>
@@ -3032,13 +3791,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G56" s="4"/>
-      <c r="H56" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I56" s="9"/>
-    </row>
-    <row r="57" spans="2:14">
+      <c r="H56" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I56" s="7"/>
+      <c r="V56" s="12"/>
+      <c r="W56" s="12"/>
+      <c r="X56" s="13">
+        <v>19</v>
+      </c>
+      <c r="Y56" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z56" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA56" s="12">
+        <v>16.72</v>
+      </c>
+      <c r="AB56" s="13">
+        <v>2.28469E-5</v>
+      </c>
+      <c r="AC56" s="12">
+        <v>143.1</v>
+      </c>
+      <c r="AD56" s="13">
+        <v>1.5615000000000001E-19</v>
+      </c>
+      <c r="AE56" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="13">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="57" spans="2:32">
       <c r="B57" s="2">
         <v>55</v>
       </c>
@@ -3054,13 +3842,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G57" s="4"/>
-      <c r="H57" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I57" s="9"/>
-    </row>
-    <row r="58" spans="2:14">
+      <c r="H57" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I57" s="7"/>
+      <c r="V57" s="12"/>
+      <c r="W57" s="12"/>
+      <c r="X57" s="13">
+        <v>20</v>
+      </c>
+      <c r="Y57" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z57" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA57" s="12">
+        <v>7.52</v>
+      </c>
+      <c r="AB57" s="13">
+        <v>5.0797899999999997E-5</v>
+      </c>
+      <c r="AC57" s="12">
+        <v>137.80000000000001</v>
+      </c>
+      <c r="AD57" s="13">
+        <v>5.1246000000000004E-19</v>
+      </c>
+      <c r="AE57" s="12">
+        <v>3</v>
+      </c>
+      <c r="AF57" s="13">
+        <v>6.63</v>
+      </c>
+    </row>
+    <row r="58" spans="2:32">
       <c r="B58" s="2">
         <v>56</v>
       </c>
@@ -3076,13 +3893,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G58" s="4"/>
-      <c r="H58" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I58" s="9"/>
-    </row>
-    <row r="59" spans="2:14">
+      <c r="H58" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I58" s="7"/>
+      <c r="V58" s="12"/>
+      <c r="W58" s="12"/>
+      <c r="X58" s="13">
+        <v>21</v>
+      </c>
+      <c r="Y58" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z58" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA58" s="12">
+        <v>14.71</v>
+      </c>
+      <c r="AB58" s="13">
+        <v>2.5968700000000001E-5</v>
+      </c>
+      <c r="AC58" s="11">
+        <v>167.4</v>
+      </c>
+      <c r="AD58" s="13">
+        <v>1.5428000000000001E-19</v>
+      </c>
+      <c r="AE58" s="11">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="13">
+        <v>3.69</v>
+      </c>
+    </row>
+    <row r="59" spans="2:32">
       <c r="B59" s="2">
         <v>57</v>
       </c>
@@ -3098,13 +3944,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G59" s="4"/>
-      <c r="H59" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I59" s="9"/>
-    </row>
-    <row r="60" spans="2:14">
+      <c r="H59" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I59" s="7"/>
+      <c r="V59" s="12"/>
+      <c r="W59" s="12"/>
+      <c r="X59" s="13">
+        <v>22</v>
+      </c>
+      <c r="Y59" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z59" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA59" s="12">
+        <v>24.8</v>
+      </c>
+      <c r="AB59" s="13">
+        <v>1.5403199999999998E-5</v>
+      </c>
+      <c r="AC59" s="12">
+        <v>73.900000000000006</v>
+      </c>
+      <c r="AD59" s="13">
+        <v>1.5583000000000001E-19</v>
+      </c>
+      <c r="AE59" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF59" s="13">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="60" spans="2:32">
       <c r="B60" s="2">
         <v>58</v>
       </c>
@@ -3120,13 +3995,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G60" s="4"/>
-      <c r="H60" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I60" s="9"/>
-    </row>
-    <row r="61" spans="2:14">
+      <c r="H60" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I60" s="7"/>
+      <c r="V60" s="12"/>
+      <c r="W60" s="12"/>
+      <c r="X60" s="13">
+        <v>23</v>
+      </c>
+      <c r="Y60" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA60" s="12">
+        <v>19.739999999999998</v>
+      </c>
+      <c r="AB60" s="13">
+        <v>1.93516E-5</v>
+      </c>
+      <c r="AC60" s="12">
+        <v>102.4</v>
+      </c>
+      <c r="AD60" s="13">
+        <v>1.6375E-19</v>
+      </c>
+      <c r="AE60" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF60" s="13">
+        <v>2.21</v>
+      </c>
+    </row>
+    <row r="61" spans="2:32">
       <c r="B61" s="2">
         <v>59</v>
       </c>
@@ -3142,13 +4046,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G61" s="4"/>
-      <c r="H61" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I61" s="9"/>
-    </row>
-    <row r="62" spans="2:14">
+      <c r="H61" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I61" s="7"/>
+      <c r="V61" s="12"/>
+      <c r="W61" s="12"/>
+      <c r="X61" s="13">
+        <v>24</v>
+      </c>
+      <c r="Y61" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z61" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA61" s="12">
+        <v>11.06</v>
+      </c>
+      <c r="AB61" s="13">
+        <v>3.4538900000000002E-5</v>
+      </c>
+      <c r="AC61" s="12">
+        <v>124.4</v>
+      </c>
+      <c r="AD61" s="13">
+        <v>3.1350999999999999E-19</v>
+      </c>
+      <c r="AE61" s="12">
+        <v>2</v>
+      </c>
+      <c r="AF61" s="13">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="62" spans="2:32">
       <c r="B62" s="2">
         <v>60</v>
       </c>
@@ -3164,13 +4097,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G62" s="4"/>
-      <c r="H62" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I62" s="9"/>
-    </row>
-    <row r="63" spans="2:14">
+      <c r="H62" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I62" s="7"/>
+      <c r="V62" s="12"/>
+      <c r="W62" s="12"/>
+      <c r="X62" s="13">
+        <v>25</v>
+      </c>
+      <c r="Y62" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z62" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA62" s="12">
+        <v>17.2</v>
+      </c>
+      <c r="AB62" s="13">
+        <v>2.2209300000000001E-5</v>
+      </c>
+      <c r="AC62" s="11">
+        <v>125.6</v>
+      </c>
+      <c r="AD62" s="13">
+        <v>1.6420999999999999E-19</v>
+      </c>
+      <c r="AE62" s="11">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="13">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="63" spans="2:32">
       <c r="B63" s="2">
         <v>61</v>
       </c>
@@ -3186,13 +4148,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G63" s="4"/>
-      <c r="H63" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I63" s="9"/>
-    </row>
-    <row r="64" spans="2:14">
+      <c r="H63" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I63" s="7"/>
+      <c r="V63" s="12"/>
+      <c r="W63" s="12"/>
+      <c r="X63" s="13">
+        <v>26</v>
+      </c>
+      <c r="Y63" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z63" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA63" s="12">
+        <v>5.45</v>
+      </c>
+      <c r="AB63" s="13">
+        <v>7.0091699999999998E-5</v>
+      </c>
+      <c r="AC63" s="12">
+        <v>141.19999999999999</v>
+      </c>
+      <c r="AD63" s="13">
+        <v>8.5275999999999998E-19</v>
+      </c>
+      <c r="AE63" s="12">
+        <v>5</v>
+      </c>
+      <c r="AF63" s="13">
+        <v>6.46</v>
+      </c>
+    </row>
+    <row r="64" spans="2:32">
       <c r="B64" s="2">
         <v>62</v>
       </c>
@@ -3208,13 +4199,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G64" s="4"/>
-      <c r="H64" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I64" s="9"/>
-    </row>
-    <row r="65" spans="2:9">
+      <c r="H64" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I64" s="7"/>
+      <c r="V64" s="12"/>
+      <c r="W64" s="12"/>
+      <c r="X64" s="13">
+        <v>27</v>
+      </c>
+      <c r="Y64" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA64" s="12">
+        <v>24.13</v>
+      </c>
+      <c r="AB64" s="13">
+        <v>1.5830900000000001E-5</v>
+      </c>
+      <c r="AC64" s="12">
+        <v>41.1</v>
+      </c>
+      <c r="AD64" s="13">
+        <v>3.018E-19</v>
+      </c>
+      <c r="AE64" s="12">
+        <v>2</v>
+      </c>
+      <c r="AF64" s="13">
+        <v>5.8</v>
+      </c>
+    </row>
+    <row r="65" spans="2:32">
       <c r="B65" s="2">
         <v>63</v>
       </c>
@@ -3230,13 +4250,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G65" s="4"/>
-      <c r="H65" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I65" s="9"/>
-    </row>
-    <row r="66" spans="2:9">
+      <c r="H65" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I65" s="7"/>
+      <c r="V65" s="12"/>
+      <c r="W65" s="12"/>
+      <c r="X65" s="13">
+        <v>28</v>
+      </c>
+      <c r="Y65" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA65" s="12">
+        <v>16.18</v>
+      </c>
+      <c r="AB65" s="13">
+        <v>2.3609400000000001E-5</v>
+      </c>
+      <c r="AC65" s="12">
+        <v>131.80000000000001</v>
+      </c>
+      <c r="AD65" s="13">
+        <v>1.6845000000000001E-19</v>
+      </c>
+      <c r="AE65" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF65" s="13">
+        <v>5.14</v>
+      </c>
+    </row>
+    <row r="66" spans="2:32">
       <c r="B66" s="2">
         <v>64</v>
       </c>
@@ -3252,13 +4301,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G66" s="4"/>
-      <c r="H66" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I66" s="9"/>
-    </row>
-    <row r="67" spans="2:9">
+      <c r="H66" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I66" s="7"/>
+      <c r="V66" s="12"/>
+      <c r="W66" s="12"/>
+      <c r="X66" s="13">
+        <v>29</v>
+      </c>
+      <c r="Y66" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z66" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA66" s="12">
+        <v>22.61</v>
+      </c>
+      <c r="AB66" s="13">
+        <v>1.68952E-5</v>
+      </c>
+      <c r="AC66" s="11">
+        <v>86.8</v>
+      </c>
+      <c r="AD66" s="13">
+        <v>1.5543E-19</v>
+      </c>
+      <c r="AE66" s="11">
+        <v>1</v>
+      </c>
+      <c r="AF66" s="13">
+        <v>2.97</v>
+      </c>
+    </row>
+    <row r="67" spans="2:32">
       <c r="B67" s="2">
         <v>65</v>
       </c>
@@ -3274,13 +4352,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G67" s="4"/>
-      <c r="H67" s="9" t="e">
-        <f t="shared" si="1"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="I67" s="9"/>
-    </row>
-    <row r="68" spans="2:9">
+      <c r="H67" s="7" t="e">
+        <f t="shared" si="1"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="I67" s="7"/>
+      <c r="V67" s="12"/>
+      <c r="W67" s="12"/>
+      <c r="X67" s="13">
+        <v>30</v>
+      </c>
+      <c r="Y67" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z67" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA67" s="12">
+        <v>17.649999999999999</v>
+      </c>
+      <c r="AB67" s="13">
+        <v>2.16431E-5</v>
+      </c>
+      <c r="AC67" s="12">
+        <v>61.4</v>
+      </c>
+      <c r="AD67" s="13">
+        <v>3.0999999999999999E-19</v>
+      </c>
+      <c r="AE67" s="12">
+        <v>2</v>
+      </c>
+      <c r="AF67" s="13">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="68" spans="2:32">
       <c r="B68" s="2">
         <v>66</v>
       </c>
@@ -3296,13 +4403,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G68" s="4"/>
-      <c r="H68" s="9" t="e">
+      <c r="H68" s="7" t="e">
         <f t="shared" ref="H68:H102" si="3">1.945*10^-10*F68^1.5/G68</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="I68" s="9"/>
-    </row>
-    <row r="69" spans="2:9">
+      <c r="I68" s="7"/>
+      <c r="V68" s="12"/>
+      <c r="W68" s="12"/>
+      <c r="X68" s="13">
+        <v>31</v>
+      </c>
+      <c r="Y68" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z68" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA68" s="12">
+        <v>14.73</v>
+      </c>
+      <c r="AB68" s="13">
+        <v>2.5933500000000002E-5</v>
+      </c>
+      <c r="AC68" s="12">
+        <v>156.4</v>
+      </c>
+      <c r="AD68" s="13">
+        <v>1.6483E-19</v>
+      </c>
+      <c r="AE68" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF68" s="13">
+        <v>2.88</v>
+      </c>
+    </row>
+    <row r="69" spans="2:32">
       <c r="B69" s="2">
         <v>67</v>
       </c>
@@ -3318,13 +4454,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G69" s="4"/>
-      <c r="H69" s="9" t="e">
+      <c r="H69" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I69" s="9"/>
-    </row>
-    <row r="70" spans="2:9">
+      <c r="I69" s="7"/>
+      <c r="V69" s="12"/>
+      <c r="W69" s="12"/>
+      <c r="X69" s="13">
+        <v>32</v>
+      </c>
+      <c r="Y69" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z69" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA69" s="12">
+        <v>21.79</v>
+      </c>
+      <c r="AB69" s="13">
+        <v>1.7530999999999999E-5</v>
+      </c>
+      <c r="AC69" s="12">
+        <v>89.2</v>
+      </c>
+      <c r="AD69" s="13">
+        <v>1.5363000000000001E-19</v>
+      </c>
+      <c r="AE69" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF69" s="13">
+        <v>4.0999999999999996</v>
+      </c>
+    </row>
+    <row r="70" spans="2:32">
       <c r="B70" s="2">
         <v>68</v>
       </c>
@@ -3340,13 +4505,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G70" s="4"/>
-      <c r="H70" s="9" t="e">
+      <c r="H70" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I70" s="9"/>
-    </row>
-    <row r="71" spans="2:9">
+      <c r="I70" s="7"/>
+      <c r="V70" s="12"/>
+      <c r="W70" s="12"/>
+      <c r="X70" s="13">
+        <v>33</v>
+      </c>
+      <c r="Y70" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z70" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA70" s="12">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="AB70" s="13">
+        <v>2.2603600000000002E-5</v>
+      </c>
+      <c r="AC70" s="12">
+        <v>138.80000000000001</v>
+      </c>
+      <c r="AD70" s="13">
+        <v>1.5539E-19</v>
+      </c>
+      <c r="AE70" s="12">
+        <v>1</v>
+      </c>
+      <c r="AF70" s="13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="71" spans="2:32">
       <c r="B71" s="2">
         <v>69</v>
       </c>
@@ -3362,13 +4556,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G71" s="4"/>
-      <c r="H71" s="9" t="e">
+      <c r="H71" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I71" s="9"/>
-    </row>
-    <row r="72" spans="2:9">
+      <c r="I71" s="7"/>
+      <c r="V71" s="12"/>
+      <c r="W71" s="12"/>
+      <c r="X71" s="13">
+        <v>34</v>
+      </c>
+      <c r="Y71" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z71" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA71" s="12">
+        <v>12.78</v>
+      </c>
+      <c r="AB71" s="13">
+        <v>2.9890500000000001E-5</v>
+      </c>
+      <c r="AC71" s="12">
+        <v>64.8</v>
+      </c>
+      <c r="AD71" s="13">
+        <v>4.9080000000000002E-19</v>
+      </c>
+      <c r="AE71" s="12">
+        <v>3</v>
+      </c>
+      <c r="AF71" s="13">
+        <v>2.12</v>
+      </c>
+    </row>
+    <row r="72" spans="2:32">
       <c r="B72" s="2">
         <v>70</v>
       </c>
@@ -3384,13 +4607,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G72" s="4"/>
-      <c r="H72" s="9" t="e">
+      <c r="H72" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I72" s="9"/>
-    </row>
-    <row r="73" spans="2:9">
+      <c r="I72" s="7"/>
+      <c r="V72" s="12"/>
+      <c r="W72" s="12"/>
+      <c r="X72" s="13">
+        <v>35</v>
+      </c>
+      <c r="Y72" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z72" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA72" s="12">
+        <v>10.06</v>
+      </c>
+      <c r="AB72" s="13">
+        <v>3.7972200000000002E-5</v>
+      </c>
+      <c r="AC72" s="14">
+        <v>276.39999999999998</v>
+      </c>
+      <c r="AD72" s="15">
+        <v>1.6625000000000001E-19</v>
+      </c>
+      <c r="AE72" s="14">
+        <v>1</v>
+      </c>
+      <c r="AF72" s="15">
+        <v>3.77</v>
+      </c>
+    </row>
+    <row r="73" spans="2:32">
       <c r="B73" s="2">
         <v>71</v>
       </c>
@@ -3406,13 +4658,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G73" s="4"/>
-      <c r="H73" s="9" t="e">
+      <c r="H73" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I73" s="9"/>
-    </row>
-    <row r="74" spans="2:9">
+      <c r="I73" s="7"/>
+      <c r="V73" s="12"/>
+      <c r="W73" s="12"/>
+      <c r="X73" s="13">
+        <v>36</v>
+      </c>
+      <c r="Y73" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z73" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA73" s="12">
+        <v>10.27</v>
+      </c>
+      <c r="AB73" s="13">
+        <v>3.71957E-5</v>
+      </c>
+      <c r="AC73" s="14">
+        <v>55.2</v>
+      </c>
+      <c r="AD73" s="15">
+        <v>8.2434999999999997E-19</v>
+      </c>
+      <c r="AE73" s="14">
+        <v>5</v>
+      </c>
+      <c r="AF73" s="15">
+        <v>2.91</v>
+      </c>
+    </row>
+    <row r="74" spans="2:32">
       <c r="B74" s="2">
         <v>72</v>
       </c>
@@ -3428,13 +4709,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G74" s="4"/>
-      <c r="H74" s="9" t="e">
+      <c r="H74" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I74" s="9"/>
-    </row>
-    <row r="75" spans="2:9">
+      <c r="I74" s="7"/>
+      <c r="V74" s="12"/>
+      <c r="W74" s="12"/>
+      <c r="X74" s="13">
+        <v>37</v>
+      </c>
+      <c r="Y74" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z74" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA74" s="12">
+        <v>6.63</v>
+      </c>
+      <c r="AB74" s="13">
+        <v>5.7616900000000001E-5</v>
+      </c>
+      <c r="AC74" s="14">
+        <v>256.10000000000002</v>
+      </c>
+      <c r="AD74" s="15">
+        <v>3.3280000000000002E-19</v>
+      </c>
+      <c r="AE74" s="14">
+        <v>2</v>
+      </c>
+      <c r="AF74" s="15">
+        <v>3.87</v>
+      </c>
+    </row>
+    <row r="75" spans="2:32">
       <c r="B75" s="2">
         <v>73</v>
       </c>
@@ -3450,13 +4760,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G75" s="4"/>
-      <c r="H75" s="9" t="e">
+      <c r="H75" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I75" s="9"/>
-    </row>
-    <row r="76" spans="2:9">
+      <c r="I75" s="7"/>
+      <c r="V75" s="12"/>
+      <c r="W75" s="12"/>
+      <c r="X75" s="13">
+        <v>38</v>
+      </c>
+      <c r="Y75" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z75" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA75" s="12">
+        <v>9.93</v>
+      </c>
+      <c r="AB75" s="13">
+        <v>3.8469300000000001E-5</v>
+      </c>
+      <c r="AC75" s="14">
+        <v>270.2</v>
+      </c>
+      <c r="AD75" s="15">
+        <v>1.6853E-19</v>
+      </c>
+      <c r="AE75" s="14">
+        <v>1</v>
+      </c>
+      <c r="AF75" s="15">
+        <v>5.19</v>
+      </c>
+    </row>
+    <row r="76" spans="2:32">
       <c r="B76" s="2">
         <v>74</v>
       </c>
@@ -3472,13 +4811,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G76" s="4"/>
-      <c r="H76" s="9" t="e">
+      <c r="H76" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I76" s="9"/>
-    </row>
-    <row r="77" spans="2:9">
+      <c r="I76" s="7"/>
+      <c r="V76" s="12"/>
+      <c r="W76" s="12"/>
+      <c r="X76" s="13">
+        <v>39</v>
+      </c>
+      <c r="Y76" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z76" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA76" s="12">
+        <v>18.13</v>
+      </c>
+      <c r="AB76" s="13">
+        <v>2.107E-5</v>
+      </c>
+      <c r="AC76" s="14">
+        <v>58.7</v>
+      </c>
+      <c r="AD76" s="15">
+        <v>3.1245000000000002E-19</v>
+      </c>
+      <c r="AE76" s="14">
+        <v>2</v>
+      </c>
+      <c r="AF76" s="15">
+        <v>2.46</v>
+      </c>
+    </row>
+    <row r="77" spans="2:32">
       <c r="B77" s="2">
         <v>75</v>
       </c>
@@ -3494,13 +4862,42 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G77" s="4"/>
-      <c r="H77" s="9" t="e">
+      <c r="H77" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I77" s="9"/>
-    </row>
-    <row r="78" spans="2:9">
+      <c r="I77" s="7"/>
+      <c r="V77" s="12"/>
+      <c r="W77" s="12"/>
+      <c r="X77" s="13">
+        <v>40</v>
+      </c>
+      <c r="Y77" s="12">
+        <v>1</v>
+      </c>
+      <c r="Z77" s="12">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA77" s="12">
+        <v>23.57</v>
+      </c>
+      <c r="AB77" s="13">
+        <v>1.6206999999999999E-5</v>
+      </c>
+      <c r="AC77" s="14">
+        <v>80.599999999999994</v>
+      </c>
+      <c r="AD77" s="15">
+        <v>1.5583000000000001E-19</v>
+      </c>
+      <c r="AE77" s="14">
+        <v>1</v>
+      </c>
+      <c r="AF77" s="14">
+        <v>2.72</v>
+      </c>
+    </row>
+    <row r="78" spans="2:32">
       <c r="B78" s="2">
         <v>76</v>
       </c>
@@ -3516,13 +4913,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G78" s="4"/>
-      <c r="H78" s="9" t="e">
+      <c r="H78" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I78" s="9"/>
-    </row>
-    <row r="79" spans="2:9">
+      <c r="I78" s="7"/>
+      <c r="X78">
+        <v>41</v>
+      </c>
+      <c r="Y78">
+        <v>1</v>
+      </c>
+      <c r="Z78">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA78">
+        <v>14.91</v>
+      </c>
+      <c r="AB78" s="10">
+        <v>2.56204E-5</v>
+      </c>
+      <c r="AC78">
+        <v>81.3</v>
+      </c>
+      <c r="AD78" s="10">
+        <v>3.1053999999999998E-19</v>
+      </c>
+      <c r="AE78">
+        <v>2</v>
+      </c>
+      <c r="AF78">
+        <v>3.08</v>
+      </c>
+    </row>
+    <row r="79" spans="2:32">
       <c r="B79" s="2">
         <v>77</v>
       </c>
@@ -3538,13 +4962,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G79" s="4"/>
-      <c r="H79" s="9" t="e">
+      <c r="H79" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I79" s="9"/>
-    </row>
-    <row r="80" spans="2:9">
+      <c r="I79" s="7"/>
+      <c r="X79">
+        <v>42</v>
+      </c>
+      <c r="Y79">
+        <v>1</v>
+      </c>
+      <c r="Z79">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA79">
+        <v>7.26</v>
+      </c>
+      <c r="AB79" s="10">
+        <v>5.2617100000000001E-5</v>
+      </c>
+      <c r="AC79">
+        <v>230.7</v>
+      </c>
+      <c r="AD79" s="10">
+        <v>3.278E-19</v>
+      </c>
+      <c r="AE79">
+        <v>2</v>
+      </c>
+      <c r="AF79">
+        <v>2.31</v>
+      </c>
+    </row>
+    <row r="80" spans="2:32">
       <c r="B80" s="2">
         <v>78</v>
       </c>
@@ -3560,13 +5011,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G80" s="4"/>
-      <c r="H80" s="9" t="e">
+      <c r="H80" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I80" s="9"/>
-    </row>
-    <row r="81" spans="2:9">
+      <c r="I80" s="7"/>
+      <c r="X80">
+        <v>43</v>
+      </c>
+      <c r="Y80">
+        <v>1</v>
+      </c>
+      <c r="Z80">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA80">
+        <v>15.32</v>
+      </c>
+      <c r="AB80" s="10">
+        <v>2.49347E-5</v>
+      </c>
+      <c r="AC80">
+        <v>75.8</v>
+      </c>
+      <c r="AD80" s="10">
+        <v>3.1090000000000002E-19</v>
+      </c>
+      <c r="AE80">
+        <v>2</v>
+      </c>
+      <c r="AF80">
+        <v>2.93</v>
+      </c>
+    </row>
+    <row r="81" spans="2:32">
       <c r="B81" s="2">
         <v>79</v>
       </c>
@@ -3582,13 +5060,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G81" s="4"/>
-      <c r="H81" s="9" t="e">
+      <c r="H81" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I81" s="9"/>
-    </row>
-    <row r="82" spans="2:9">
+      <c r="I81" s="7"/>
+      <c r="X81">
+        <v>44</v>
+      </c>
+      <c r="Y81">
+        <v>1</v>
+      </c>
+      <c r="Z81">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA81">
+        <v>10.75</v>
+      </c>
+      <c r="AB81" s="10">
+        <v>3.5534899999999998E-5</v>
+      </c>
+      <c r="AC81">
+        <v>49.5</v>
+      </c>
+      <c r="AD81" s="10">
+        <v>8.3390000000000005E-19</v>
+      </c>
+      <c r="AE81">
+        <v>5</v>
+      </c>
+      <c r="AF81">
+        <v>4.12</v>
+      </c>
+    </row>
+    <row r="82" spans="2:32">
       <c r="B82" s="2">
         <v>80</v>
       </c>
@@ -3604,13 +5109,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G82" s="4"/>
-      <c r="H82" s="9" t="e">
+      <c r="H82" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I82" s="9"/>
-    </row>
-    <row r="83" spans="2:9">
+      <c r="I82" s="7"/>
+      <c r="X82">
+        <v>45</v>
+      </c>
+      <c r="Y82">
+        <v>1</v>
+      </c>
+      <c r="Z82">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA82">
+        <v>16.170000000000002</v>
+      </c>
+      <c r="AB82" s="10">
+        <v>2.3623999999999999E-5</v>
+      </c>
+      <c r="AC82">
+        <v>137.9</v>
+      </c>
+      <c r="AD82" s="10">
+        <v>1.6425000000000001E-19</v>
+      </c>
+      <c r="AE82">
+        <v>1</v>
+      </c>
+      <c r="AF82">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="83" spans="2:32">
       <c r="B83" s="2">
         <v>81</v>
       </c>
@@ -3626,13 +5158,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G83" s="4"/>
-      <c r="H83" s="9" t="e">
+      <c r="H83" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I83" s="9"/>
-    </row>
-    <row r="84" spans="2:9">
+      <c r="I83" s="7"/>
+      <c r="X83">
+        <v>46</v>
+      </c>
+      <c r="Y83">
+        <v>1</v>
+      </c>
+      <c r="Z83">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA83">
+        <v>6.35</v>
+      </c>
+      <c r="AB83" s="10">
+        <v>6.0157500000000001E-5</v>
+      </c>
+      <c r="AC83">
+        <v>262.39999999999998</v>
+      </c>
+      <c r="AD83" s="10">
+        <v>3.321E-19</v>
+      </c>
+      <c r="AE83">
+        <v>2</v>
+      </c>
+      <c r="AF83">
+        <v>3.65</v>
+      </c>
+    </row>
+    <row r="84" spans="2:32">
       <c r="B84" s="2">
         <v>82</v>
       </c>
@@ -3648,13 +5207,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G84" s="4"/>
-      <c r="H84" s="9" t="e">
+      <c r="H84" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I84" s="9"/>
-    </row>
-    <row r="85" spans="2:9">
+      <c r="I84" s="7"/>
+      <c r="X84">
+        <v>47</v>
+      </c>
+      <c r="Y84">
+        <v>1</v>
+      </c>
+      <c r="Z84">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA84">
+        <v>11.1</v>
+      </c>
+      <c r="AB84" s="10">
+        <v>3.44144E-5</v>
+      </c>
+      <c r="AC84">
+        <v>63.3</v>
+      </c>
+      <c r="AD84" s="10">
+        <v>6.1550000000000002E-19</v>
+      </c>
+      <c r="AE84">
+        <v>4</v>
+      </c>
+      <c r="AF84">
+        <v>3.94</v>
+      </c>
+    </row>
+    <row r="85" spans="2:32">
       <c r="B85" s="2">
         <v>83</v>
       </c>
@@ -3670,13 +5256,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G85" s="4"/>
-      <c r="H85" s="9" t="e">
+      <c r="H85" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I85" s="9"/>
-    </row>
-    <row r="86" spans="2:9">
+      <c r="I85" s="7"/>
+      <c r="X85">
+        <v>48</v>
+      </c>
+      <c r="Y85">
+        <v>1</v>
+      </c>
+      <c r="Z85">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA85">
+        <v>17.78</v>
+      </c>
+      <c r="AB85" s="10">
+        <v>2.1484800000000001E-5</v>
+      </c>
+      <c r="AC85">
+        <v>43.5</v>
+      </c>
+      <c r="AD85" s="10">
+        <v>4.4980000000000001E-19</v>
+      </c>
+      <c r="AE85">
+        <v>3</v>
+      </c>
+      <c r="AF85">
+        <v>6.41</v>
+      </c>
+    </row>
+    <row r="86" spans="2:32">
       <c r="B86" s="2">
         <v>84</v>
       </c>
@@ -3692,13 +5305,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G86" s="4"/>
-      <c r="H86" s="9" t="e">
+      <c r="H86" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I86" s="9"/>
-    </row>
-    <row r="87" spans="2:9">
+      <c r="I86" s="7"/>
+      <c r="X86">
+        <v>49</v>
+      </c>
+      <c r="Y86">
+        <v>1</v>
+      </c>
+      <c r="Z86">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA86">
+        <v>11.82</v>
+      </c>
+      <c r="AB86" s="10">
+        <v>3.2318099999999998E-5</v>
+      </c>
+      <c r="AC86">
+        <v>43.1</v>
+      </c>
+      <c r="AD86" s="10">
+        <v>8.3580000000000001E-19</v>
+      </c>
+      <c r="AE86">
+        <v>5</v>
+      </c>
+      <c r="AF86">
+        <v>4.34</v>
+      </c>
+    </row>
+    <row r="87" spans="2:32">
       <c r="B87" s="2">
         <v>85</v>
       </c>
@@ -3714,13 +5354,40 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G87" s="4"/>
-      <c r="H87" s="9" t="e">
+      <c r="H87" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I87" s="9"/>
-    </row>
-    <row r="88" spans="2:9">
+      <c r="I87" s="7"/>
+      <c r="X87">
+        <v>50</v>
+      </c>
+      <c r="Y87">
+        <v>1</v>
+      </c>
+      <c r="Z87">
+        <v>3.8200000000000002E-4</v>
+      </c>
+      <c r="AA87">
+        <v>18.440000000000001</v>
+      </c>
+      <c r="AB87" s="10">
+        <v>2.0715799999999999E-5</v>
+      </c>
+      <c r="AC87">
+        <v>53</v>
+      </c>
+      <c r="AD87" s="10">
+        <v>3.3449999999999998E-19</v>
+      </c>
+      <c r="AE87">
+        <v>2</v>
+      </c>
+      <c r="AF87">
+        <v>4.4000000000000004</v>
+      </c>
+    </row>
+    <row r="88" spans="2:32">
       <c r="B88" s="2">
         <v>86</v>
       </c>
@@ -3736,13 +5403,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G88" s="4"/>
-      <c r="H88" s="9" t="e">
+      <c r="H88" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I88" s="9"/>
-    </row>
-    <row r="89" spans="2:9">
+      <c r="I88" s="7"/>
+    </row>
+    <row r="89" spans="2:32">
       <c r="B89" s="2">
         <v>87</v>
       </c>
@@ -3758,13 +5425,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G89" s="4"/>
-      <c r="H89" s="9" t="e">
+      <c r="H89" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I89" s="9"/>
-    </row>
-    <row r="90" spans="2:9">
+      <c r="I89" s="7"/>
+    </row>
+    <row r="90" spans="2:32">
       <c r="B90" s="2">
         <v>88</v>
       </c>
@@ -3780,13 +5447,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G90" s="4"/>
-      <c r="H90" s="9" t="e">
+      <c r="H90" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I90" s="9"/>
-    </row>
-    <row r="91" spans="2:9">
+      <c r="I90" s="7"/>
+    </row>
+    <row r="91" spans="2:32">
       <c r="B91" s="2">
         <v>89</v>
       </c>
@@ -3802,13 +5469,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G91" s="4"/>
-      <c r="H91" s="9" t="e">
+      <c r="H91" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I91" s="9"/>
-    </row>
-    <row r="92" spans="2:9">
+      <c r="I91" s="7"/>
+    </row>
+    <row r="92" spans="2:32">
       <c r="B92" s="2">
         <v>90</v>
       </c>
@@ -3824,13 +5491,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G92" s="4"/>
-      <c r="H92" s="9" t="e">
+      <c r="H92" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I92" s="9"/>
-    </row>
-    <row r="93" spans="2:9">
+      <c r="I92" s="7"/>
+    </row>
+    <row r="93" spans="2:32">
       <c r="B93" s="2">
         <v>91</v>
       </c>
@@ -3846,13 +5513,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G93" s="4"/>
-      <c r="H93" s="9" t="e">
+      <c r="H93" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I93" s="9"/>
-    </row>
-    <row r="94" spans="2:9">
+      <c r="I93" s="7"/>
+    </row>
+    <row r="94" spans="2:32">
       <c r="B94" s="2">
         <v>92</v>
       </c>
@@ -3868,13 +5535,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G94" s="4"/>
-      <c r="H94" s="9" t="e">
+      <c r="H94" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I94" s="9"/>
-    </row>
-    <row r="95" spans="2:9">
+      <c r="I94" s="7"/>
+    </row>
+    <row r="95" spans="2:32">
       <c r="B95" s="2">
         <v>93</v>
       </c>
@@ -3890,13 +5557,13 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G95" s="4"/>
-      <c r="H95" s="9" t="e">
+      <c r="H95" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I95" s="9"/>
-    </row>
-    <row r="96" spans="2:9">
+      <c r="I95" s="7"/>
+    </row>
+    <row r="96" spans="2:32">
       <c r="B96" s="2">
         <v>94</v>
       </c>
@@ -3912,11 +5579,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G96" s="4"/>
-      <c r="H96" s="9" t="e">
+      <c r="H96" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I96" s="9"/>
+      <c r="I96" s="7"/>
     </row>
     <row r="97" spans="2:9">
       <c r="B97" s="2">
@@ -3934,11 +5601,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G97" s="4"/>
-      <c r="H97" s="9" t="e">
+      <c r="H97" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I97" s="9"/>
+      <c r="I97" s="7"/>
     </row>
     <row r="98" spans="2:9">
       <c r="B98" s="2">
@@ -3956,11 +5623,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G98" s="4"/>
-      <c r="H98" s="9" t="e">
+      <c r="H98" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I98" s="9"/>
+      <c r="I98" s="7"/>
     </row>
     <row r="99" spans="2:9">
       <c r="B99" s="2">
@@ -3978,11 +5645,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G99" s="4"/>
-      <c r="H99" s="9" t="e">
+      <c r="H99" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I99" s="9"/>
+      <c r="I99" s="7"/>
     </row>
     <row r="100" spans="2:9">
       <c r="B100" s="2">
@@ -4000,11 +5667,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G100" s="4"/>
-      <c r="H100" s="9" t="e">
+      <c r="H100" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I100" s="9"/>
+      <c r="I100" s="7"/>
     </row>
     <row r="101" spans="2:9">
       <c r="B101" s="2">
@@ -4022,11 +5689,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G101" s="4"/>
-      <c r="H101" s="9" t="e">
+      <c r="H101" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I101" s="9"/>
+      <c r="I101" s="7"/>
     </row>
     <row r="102" spans="2:9">
       <c r="B102" s="2">
@@ -4044,11 +5711,11 @@
         <v>#DIV/0!</v>
       </c>
       <c r="G102" s="4"/>
-      <c r="H102" s="9" t="e">
+      <c r="H102" s="7" t="e">
         <f t="shared" si="3"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I102" s="9"/>
+      <c r="I102" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="153">

--- a/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
+++ b/one down/普物實驗/6 密立根油滴實驗/E24146107_王翊權_預報6_表格.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\D.tuy\Documents\GitHub\school\one down\普物實驗\6 密立根油滴實驗\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAFF1654-F2CB-45E0-A200-313FC651A46F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F754429-B30D-4202-BD04-3ADB79F7BBDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="41496" windowHeight="16776" xr2:uid="{DB1FF5BB-3E16-44F6-8EBE-091011F52E70}"/>
   </bookViews>
@@ -44,10 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="14">
-  <si>
-    <t>次數</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>X(格數)</t>
   </si>
@@ -77,17 +74,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>V1(m/s)</t>
-  </si>
-  <si>
     <t>次數</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>估計n值</t>
-  </si>
-  <si>
-    <t>誤差(%)</t>
   </si>
 </sst>
 </file>
@@ -1320,33 +1308,33 @@
   <sheetData>
     <row r="2" spans="2:14">
       <c r="B2" s="2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>3</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>4</v>
       </c>
       <c r="I2" s="9"/>
       <c r="L2" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M2" s="6"/>
       <c r="N2" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="2:14">
@@ -2623,7 +2611,7 @@
       <c r="AE36" s="12"/>
       <c r="AF36" s="13"/>
     </row>
-    <row r="37" spans="2:32" ht="30">
+    <row r="37" spans="2:32">
       <c r="B37" s="2">
         <v>35</v>
       </c>
@@ -2657,33 +2645,15 @@
       </c>
       <c r="V37" s="12"/>
       <c r="W37" s="12"/>
-      <c r="X37" s="13" t="s">
-        <v>0</v>
-      </c>
-      <c r="Y37" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="AA37" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="AB37" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="AC37" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD37" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE37" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF37" s="13" t="s">
-        <v>13</v>
-      </c>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="12"/>
+      <c r="Z37" s="12"/>
+      <c r="AA37" s="12"/>
+      <c r="AB37" s="12"/>
+      <c r="AC37" s="12"/>
+      <c r="AD37" s="13"/>
+      <c r="AE37" s="12"/>
+      <c r="AF37" s="13"/>
     </row>
     <row r="38" spans="2:32">
       <c r="B38" s="2">
@@ -2719,33 +2689,15 @@
       </c>
       <c r="V38" s="12"/>
       <c r="W38" s="12"/>
-      <c r="X38" s="13">
-        <v>1</v>
-      </c>
-      <c r="Y38" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z38" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA38" s="12">
-        <v>19.71</v>
-      </c>
-      <c r="AB38" s="13">
-        <v>1.9381E-5</v>
-      </c>
-      <c r="AC38" s="12">
-        <v>102.5</v>
-      </c>
-      <c r="AD38" s="13">
-        <v>1.6375E-19</v>
-      </c>
-      <c r="AE38" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF38" s="13">
-        <v>2.21</v>
-      </c>
+      <c r="X38" s="13"/>
+      <c r="Y38" s="12"/>
+      <c r="Z38" s="12"/>
+      <c r="AA38" s="12"/>
+      <c r="AB38" s="13"/>
+      <c r="AC38" s="12"/>
+      <c r="AD38" s="13"/>
+      <c r="AE38" s="12"/>
+      <c r="AF38" s="13"/>
     </row>
     <row r="39" spans="2:32">
       <c r="B39" s="2">
@@ -2781,33 +2733,15 @@
       </c>
       <c r="V39" s="12"/>
       <c r="W39" s="12"/>
-      <c r="X39" s="13">
-        <v>2</v>
-      </c>
-      <c r="Y39" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z39" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA39" s="12">
-        <v>10.130000000000001</v>
-      </c>
-      <c r="AB39" s="13">
-        <v>3.7709800000000003E-5</v>
-      </c>
-      <c r="AC39" s="12">
-        <v>93.4</v>
-      </c>
-      <c r="AD39" s="13">
-        <v>4.9646E-19</v>
-      </c>
-      <c r="AE39" s="12">
-        <v>3</v>
-      </c>
-      <c r="AF39" s="13">
-        <v>3.29</v>
-      </c>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="12"/>
+      <c r="Z39" s="12"/>
+      <c r="AA39" s="12"/>
+      <c r="AB39" s="13"/>
+      <c r="AC39" s="12"/>
+      <c r="AD39" s="13"/>
+      <c r="AE39" s="12"/>
+      <c r="AF39" s="13"/>
     </row>
     <row r="40" spans="2:32">
       <c r="B40" s="2">
@@ -2843,33 +2777,15 @@
       </c>
       <c r="V40" s="12"/>
       <c r="W40" s="12"/>
-      <c r="X40" s="13">
-        <v>3</v>
-      </c>
-      <c r="Y40" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z40" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA40" s="12">
-        <v>25.52</v>
-      </c>
-      <c r="AB40" s="13">
-        <v>1.49687E-5</v>
-      </c>
-      <c r="AC40" s="12">
-        <v>73.099999999999994</v>
-      </c>
-      <c r="AD40" s="13">
-        <v>1.5435E-19</v>
-      </c>
-      <c r="AE40" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF40" s="13">
-        <v>3.65</v>
-      </c>
+      <c r="X40" s="13"/>
+      <c r="Y40" s="12"/>
+      <c r="Z40" s="12"/>
+      <c r="AA40" s="12"/>
+      <c r="AB40" s="13"/>
+      <c r="AC40" s="12"/>
+      <c r="AD40" s="13"/>
+      <c r="AE40" s="12"/>
+      <c r="AF40" s="13"/>
     </row>
     <row r="41" spans="2:32">
       <c r="B41" s="2">
@@ -2905,33 +2821,15 @@
       </c>
       <c r="V41" s="12"/>
       <c r="W41" s="12"/>
-      <c r="X41" s="13">
-        <v>4</v>
-      </c>
-      <c r="Y41" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA41" s="12">
-        <v>17.53</v>
-      </c>
-      <c r="AB41" s="13">
-        <v>2.1791199999999999E-5</v>
-      </c>
-      <c r="AC41" s="12">
-        <v>115.8</v>
-      </c>
-      <c r="AD41" s="13">
-        <v>1.6853E-19</v>
-      </c>
-      <c r="AE41" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF41" s="13">
-        <v>5.2</v>
-      </c>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="12"/>
+      <c r="Z41" s="12"/>
+      <c r="AA41" s="12"/>
+      <c r="AB41" s="13"/>
+      <c r="AC41" s="12"/>
+      <c r="AD41" s="13"/>
+      <c r="AE41" s="12"/>
+      <c r="AF41" s="13"/>
     </row>
     <row r="42" spans="2:32">
       <c r="B42" s="2">
@@ -2967,33 +2865,15 @@
       </c>
       <c r="V42" s="12"/>
       <c r="W42" s="12"/>
-      <c r="X42" s="13">
-        <v>5</v>
-      </c>
-      <c r="Y42" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z42" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA42" s="12">
-        <v>23.62</v>
-      </c>
-      <c r="AB42" s="13">
-        <v>1.6172699999999998E-5</v>
-      </c>
-      <c r="AC42" s="12">
-        <v>78.400000000000006</v>
-      </c>
-      <c r="AD42" s="13">
-        <v>1.5644999999999999E-19</v>
-      </c>
-      <c r="AE42" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF42" s="13">
-        <v>2.34</v>
-      </c>
+      <c r="X42" s="13"/>
+      <c r="Y42" s="12"/>
+      <c r="Z42" s="12"/>
+      <c r="AA42" s="12"/>
+      <c r="AB42" s="13"/>
+      <c r="AC42" s="12"/>
+      <c r="AD42" s="13"/>
+      <c r="AE42" s="12"/>
+      <c r="AF42" s="13"/>
     </row>
     <row r="43" spans="2:32">
       <c r="B43" s="2">
@@ -3029,33 +2909,15 @@
       </c>
       <c r="V43" s="12"/>
       <c r="W43" s="12"/>
-      <c r="X43" s="13">
-        <v>6</v>
-      </c>
-      <c r="Y43" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z43" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA43" s="12">
-        <v>21.06</v>
-      </c>
-      <c r="AB43" s="13">
-        <v>1.81387E-5</v>
-      </c>
-      <c r="AC43" s="12">
-        <v>47.3</v>
-      </c>
-      <c r="AD43" s="13">
-        <v>3.1256000000000001E-19</v>
-      </c>
-      <c r="AE43" s="12">
-        <v>2</v>
-      </c>
-      <c r="AF43" s="13">
-        <v>2.4500000000000002</v>
-      </c>
+      <c r="X43" s="13"/>
+      <c r="Y43" s="12"/>
+      <c r="Z43" s="12"/>
+      <c r="AA43" s="12"/>
+      <c r="AB43" s="13"/>
+      <c r="AC43" s="12"/>
+      <c r="AD43" s="13"/>
+      <c r="AE43" s="12"/>
+      <c r="AF43" s="13"/>
     </row>
     <row r="44" spans="2:32">
       <c r="B44" s="2">
@@ -3091,33 +2953,15 @@
       </c>
       <c r="V44" s="12"/>
       <c r="W44" s="12"/>
-      <c r="X44" s="13">
-        <v>7</v>
-      </c>
-      <c r="Y44" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA44" s="12">
-        <v>7.22</v>
-      </c>
-      <c r="AB44" s="13">
-        <v>5.2908599999999997E-5</v>
-      </c>
-      <c r="AC44" s="12">
-        <v>118.2</v>
-      </c>
-      <c r="AD44" s="13">
-        <v>6.7450999999999998E-19</v>
-      </c>
-      <c r="AE44" s="12">
-        <v>4</v>
-      </c>
-      <c r="AF44" s="13">
-        <v>5.25</v>
-      </c>
+      <c r="X44" s="13"/>
+      <c r="Y44" s="12"/>
+      <c r="Z44" s="12"/>
+      <c r="AA44" s="12"/>
+      <c r="AB44" s="13"/>
+      <c r="AC44" s="12"/>
+      <c r="AD44" s="13"/>
+      <c r="AE44" s="12"/>
+      <c r="AF44" s="13"/>
     </row>
     <row r="45" spans="2:32">
       <c r="B45" s="2">
@@ -3153,33 +2997,15 @@
       </c>
       <c r="V45" s="12"/>
       <c r="W45" s="12"/>
-      <c r="X45" s="13">
-        <v>8</v>
-      </c>
-      <c r="Y45" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z45" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA45" s="12">
-        <v>18.28</v>
-      </c>
-      <c r="AB45" s="13">
-        <v>2.08972E-5</v>
-      </c>
-      <c r="AC45" s="12">
-        <v>42.1</v>
-      </c>
-      <c r="AD45" s="13">
-        <v>4.6542E-19</v>
-      </c>
-      <c r="AE45" s="12">
-        <v>3</v>
-      </c>
-      <c r="AF45" s="13">
-        <v>3.16</v>
-      </c>
+      <c r="X45" s="13"/>
+      <c r="Y45" s="12"/>
+      <c r="Z45" s="12"/>
+      <c r="AA45" s="12"/>
+      <c r="AB45" s="13"/>
+      <c r="AC45" s="12"/>
+      <c r="AD45" s="13"/>
+      <c r="AE45" s="12"/>
+      <c r="AF45" s="13"/>
     </row>
     <row r="46" spans="2:32">
       <c r="B46" s="2">
@@ -3215,33 +3041,15 @@
       </c>
       <c r="V46" s="12"/>
       <c r="W46" s="12"/>
-      <c r="X46" s="13">
-        <v>9</v>
-      </c>
-      <c r="Y46" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z46" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA46" s="12">
-        <v>10.24</v>
-      </c>
-      <c r="AB46" s="13">
-        <v>3.7304700000000002E-5</v>
-      </c>
-      <c r="AC46" s="12">
-        <v>141.5</v>
-      </c>
-      <c r="AD46" s="13">
-        <v>3.1189000000000002E-19</v>
-      </c>
-      <c r="AE46" s="12">
-        <v>2</v>
-      </c>
-      <c r="AF46" s="13">
-        <v>2.65</v>
-      </c>
+      <c r="X46" s="13"/>
+      <c r="Y46" s="12"/>
+      <c r="Z46" s="12"/>
+      <c r="AA46" s="12"/>
+      <c r="AB46" s="13"/>
+      <c r="AC46" s="12"/>
+      <c r="AD46" s="13"/>
+      <c r="AE46" s="12"/>
+      <c r="AF46" s="13"/>
     </row>
     <row r="47" spans="2:32">
       <c r="B47" s="2">
@@ -3277,33 +3085,15 @@
       </c>
       <c r="V47" s="12"/>
       <c r="W47" s="12"/>
-      <c r="X47" s="13">
-        <v>10</v>
-      </c>
-      <c r="Y47" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z47" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA47" s="12">
-        <v>10.35</v>
-      </c>
-      <c r="AB47" s="13">
-        <v>3.69082E-5</v>
-      </c>
-      <c r="AC47" s="12">
-        <v>268.39999999999998</v>
-      </c>
-      <c r="AD47" s="13">
-        <v>1.6432E-19</v>
-      </c>
-      <c r="AE47" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF47" s="13">
-        <v>2.57</v>
-      </c>
+      <c r="X47" s="13"/>
+      <c r="Y47" s="12"/>
+      <c r="Z47" s="12"/>
+      <c r="AA47" s="12"/>
+      <c r="AB47" s="13"/>
+      <c r="AC47" s="12"/>
+      <c r="AD47" s="13"/>
+      <c r="AE47" s="12"/>
+      <c r="AF47" s="13"/>
     </row>
     <row r="48" spans="2:32">
       <c r="B48" s="2">
@@ -3339,33 +3129,15 @@
       </c>
       <c r="V48" s="12"/>
       <c r="W48" s="12"/>
-      <c r="X48" s="13">
-        <v>11</v>
-      </c>
-      <c r="Y48" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z48" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA48" s="12">
-        <v>19.62</v>
-      </c>
-      <c r="AB48" s="13">
-        <v>1.9469900000000001E-5</v>
-      </c>
-      <c r="AC48" s="12">
-        <v>54.2</v>
-      </c>
-      <c r="AD48" s="13">
-        <v>3.119E-19</v>
-      </c>
-      <c r="AE48" s="12">
-        <v>2</v>
-      </c>
-      <c r="AF48" s="13">
-        <v>2.65</v>
-      </c>
+      <c r="X48" s="13"/>
+      <c r="Y48" s="12"/>
+      <c r="Z48" s="12"/>
+      <c r="AA48" s="12"/>
+      <c r="AB48" s="13"/>
+      <c r="AC48" s="12"/>
+      <c r="AD48" s="13"/>
+      <c r="AE48" s="12"/>
+      <c r="AF48" s="13"/>
     </row>
     <row r="49" spans="2:32">
       <c r="B49" s="2">
@@ -3401,33 +3173,15 @@
       </c>
       <c r="V49" s="12"/>
       <c r="W49" s="12"/>
-      <c r="X49" s="13">
-        <v>12</v>
-      </c>
-      <c r="Y49" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z49" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA49" s="12">
-        <v>9.82</v>
-      </c>
-      <c r="AB49" s="13">
-        <v>3.8900199999999997E-5</v>
-      </c>
-      <c r="AC49" s="12">
-        <v>148.6</v>
-      </c>
-      <c r="AD49" s="13">
-        <v>3.3289E-19</v>
-      </c>
-      <c r="AE49" s="12">
-        <v>2</v>
-      </c>
-      <c r="AF49" s="13">
-        <v>3.9</v>
-      </c>
+      <c r="X49" s="13"/>
+      <c r="Y49" s="12"/>
+      <c r="Z49" s="12"/>
+      <c r="AA49" s="12"/>
+      <c r="AB49" s="13"/>
+      <c r="AC49" s="12"/>
+      <c r="AD49" s="13"/>
+      <c r="AE49" s="12"/>
+      <c r="AF49" s="13"/>
     </row>
     <row r="50" spans="2:32">
       <c r="B50" s="2">
@@ -3463,33 +3217,15 @@
       </c>
       <c r="V50" s="12"/>
       <c r="W50" s="12"/>
-      <c r="X50" s="13">
-        <v>13</v>
-      </c>
-      <c r="Y50" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z50" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA50" s="12">
-        <v>21.77</v>
-      </c>
-      <c r="AB50" s="13">
-        <v>1.75471E-5</v>
-      </c>
-      <c r="AC50" s="12">
-        <v>93.6</v>
-      </c>
-      <c r="AD50" s="13">
-        <v>1.5456000000000001E-19</v>
-      </c>
-      <c r="AE50" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF50" s="13">
-        <v>3.52</v>
-      </c>
+      <c r="X50" s="13"/>
+      <c r="Y50" s="12"/>
+      <c r="Z50" s="12"/>
+      <c r="AA50" s="12"/>
+      <c r="AB50" s="13"/>
+      <c r="AC50" s="12"/>
+      <c r="AD50" s="13"/>
+      <c r="AE50" s="12"/>
+      <c r="AF50" s="13"/>
     </row>
     <row r="51" spans="2:32">
       <c r="B51" s="2">
@@ -3525,33 +3261,15 @@
       </c>
       <c r="V51" s="12"/>
       <c r="W51" s="12"/>
-      <c r="X51" s="13">
-        <v>14</v>
-      </c>
-      <c r="Y51" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z51" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA51" s="12">
-        <v>10.27</v>
-      </c>
-      <c r="AB51" s="13">
-        <v>3.71957E-5</v>
-      </c>
-      <c r="AC51" s="12">
-        <v>272.5</v>
-      </c>
-      <c r="AD51" s="13">
-        <v>1.6579999999999999E-19</v>
-      </c>
-      <c r="AE51" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF51" s="13">
-        <v>3.49</v>
-      </c>
+      <c r="X51" s="13"/>
+      <c r="Y51" s="12"/>
+      <c r="Z51" s="12"/>
+      <c r="AA51" s="12"/>
+      <c r="AB51" s="13"/>
+      <c r="AC51" s="12"/>
+      <c r="AD51" s="13"/>
+      <c r="AE51" s="12"/>
+      <c r="AF51" s="13"/>
     </row>
     <row r="52" spans="2:32">
       <c r="B52" s="2">
@@ -3587,33 +3305,15 @@
       </c>
       <c r="V52" s="12"/>
       <c r="W52" s="12"/>
-      <c r="X52" s="13">
-        <v>15</v>
-      </c>
-      <c r="Y52" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z52" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA52" s="12">
-        <v>11.16</v>
-      </c>
-      <c r="AB52" s="13">
-        <v>3.4229400000000001E-5</v>
-      </c>
-      <c r="AC52" s="12">
-        <v>224.8</v>
-      </c>
-      <c r="AD52" s="13">
-        <v>1.7051000000000001E-19</v>
-      </c>
-      <c r="AE52" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF52" s="13">
-        <v>6.43</v>
-      </c>
+      <c r="X52" s="13"/>
+      <c r="Y52" s="12"/>
+      <c r="Z52" s="12"/>
+      <c r="AA52" s="12"/>
+      <c r="AB52" s="13"/>
+      <c r="AC52" s="12"/>
+      <c r="AD52" s="13"/>
+      <c r="AE52" s="12"/>
+      <c r="AF52" s="13"/>
     </row>
     <row r="53" spans="2:32">
       <c r="B53" s="2">
@@ -3637,41 +3337,23 @@
       </c>
       <c r="I53" s="7"/>
       <c r="L53" s="6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M53" s="6"/>
       <c r="N53" s="1">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V53" s="12"/>
       <c r="W53" s="12"/>
-      <c r="X53" s="13">
-        <v>16</v>
-      </c>
-      <c r="Y53" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z53" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA53" s="12">
-        <v>11.09</v>
-      </c>
-      <c r="AB53" s="13">
-        <v>3.4445400000000001E-5</v>
-      </c>
-      <c r="AC53" s="12">
-        <v>125.1</v>
-      </c>
-      <c r="AD53" s="13">
-        <v>3.1294000000000001E-19</v>
-      </c>
-      <c r="AE53" s="12">
-        <v>2</v>
-      </c>
-      <c r="AF53" s="13">
-        <v>2.33</v>
-      </c>
+      <c r="X53" s="13"/>
+      <c r="Y53" s="12"/>
+      <c r="Z53" s="12"/>
+      <c r="AA53" s="12"/>
+      <c r="AB53" s="13"/>
+      <c r="AC53" s="12"/>
+      <c r="AD53" s="13"/>
+      <c r="AE53" s="12"/>
+      <c r="AF53" s="13"/>
     </row>
     <row r="54" spans="2:32">
       <c r="B54" s="2">
@@ -3696,33 +3378,15 @@
       <c r="I54" s="7"/>
       <c r="V54" s="12"/>
       <c r="W54" s="12"/>
-      <c r="X54" s="13">
-        <v>17</v>
-      </c>
-      <c r="Y54" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z54" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA54" s="12">
-        <v>11.04</v>
-      </c>
-      <c r="AB54" s="13">
-        <v>3.4601399999999997E-5</v>
-      </c>
-      <c r="AC54" s="12">
-        <v>76.5</v>
-      </c>
-      <c r="AD54" s="13">
-        <v>5.0563999999999995E-19</v>
-      </c>
-      <c r="AE54" s="12">
-        <v>3</v>
-      </c>
-      <c r="AF54" s="13">
-        <v>5.21</v>
-      </c>
+      <c r="X54" s="13"/>
+      <c r="Y54" s="12"/>
+      <c r="Z54" s="12"/>
+      <c r="AA54" s="12"/>
+      <c r="AB54" s="13"/>
+      <c r="AC54" s="12"/>
+      <c r="AD54" s="13"/>
+      <c r="AE54" s="12"/>
+      <c r="AF54" s="13"/>
     </row>
     <row r="55" spans="2:32">
       <c r="B55" s="2">
@@ -3747,33 +3411,15 @@
       <c r="I55" s="7"/>
       <c r="V55" s="12"/>
       <c r="W55" s="12"/>
-      <c r="X55" s="13">
-        <v>18</v>
-      </c>
-      <c r="Y55" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z55" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA55" s="12">
-        <v>14.19</v>
-      </c>
-      <c r="AB55" s="13">
-        <v>2.6920400000000001E-5</v>
-      </c>
-      <c r="AC55" s="12">
-        <v>158.4</v>
-      </c>
-      <c r="AD55" s="13">
-        <v>1.7084000000000001E-19</v>
-      </c>
-      <c r="AE55" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF55" s="13">
-        <v>6.64</v>
-      </c>
+      <c r="X55" s="13"/>
+      <c r="Y55" s="12"/>
+      <c r="Z55" s="12"/>
+      <c r="AA55" s="12"/>
+      <c r="AB55" s="13"/>
+      <c r="AC55" s="12"/>
+      <c r="AD55" s="13"/>
+      <c r="AE55" s="12"/>
+      <c r="AF55" s="13"/>
     </row>
     <row r="56" spans="2:32">
       <c r="B56" s="2">
@@ -3798,33 +3444,15 @@
       <c r="I56" s="7"/>
       <c r="V56" s="12"/>
       <c r="W56" s="12"/>
-      <c r="X56" s="13">
-        <v>19</v>
-      </c>
-      <c r="Y56" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z56" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA56" s="12">
-        <v>16.72</v>
-      </c>
-      <c r="AB56" s="13">
-        <v>2.28469E-5</v>
-      </c>
-      <c r="AC56" s="12">
-        <v>143.1</v>
-      </c>
-      <c r="AD56" s="13">
-        <v>1.5615000000000001E-19</v>
-      </c>
-      <c r="AE56" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF56" s="13">
-        <v>2.52</v>
-      </c>
+      <c r="X56" s="13"/>
+      <c r="Y56" s="12"/>
+      <c r="Z56" s="12"/>
+      <c r="AA56" s="12"/>
+      <c r="AB56" s="13"/>
+      <c r="AC56" s="12"/>
+      <c r="AD56" s="13"/>
+      <c r="AE56" s="12"/>
+      <c r="AF56" s="13"/>
     </row>
     <row r="57" spans="2:32">
       <c r="B57" s="2">
@@ -3849,33 +3477,15 @@
       <c r="I57" s="7"/>
       <c r="V57" s="12"/>
       <c r="W57" s="12"/>
-      <c r="X57" s="13">
-        <v>20</v>
-      </c>
-      <c r="Y57" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z57" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA57" s="12">
-        <v>7.52</v>
-      </c>
-      <c r="AB57" s="13">
-        <v>5.0797899999999997E-5</v>
-      </c>
-      <c r="AC57" s="12">
-        <v>137.80000000000001</v>
-      </c>
-      <c r="AD57" s="13">
-        <v>5.1246000000000004E-19</v>
-      </c>
-      <c r="AE57" s="12">
-        <v>3</v>
-      </c>
-      <c r="AF57" s="13">
-        <v>6.63</v>
-      </c>
+      <c r="X57" s="13"/>
+      <c r="Y57" s="12"/>
+      <c r="Z57" s="12"/>
+      <c r="AA57" s="12"/>
+      <c r="AB57" s="13"/>
+      <c r="AC57" s="12"/>
+      <c r="AD57" s="13"/>
+      <c r="AE57" s="12"/>
+      <c r="AF57" s="13"/>
     </row>
     <row r="58" spans="2:32">
       <c r="B58" s="2">
@@ -3900,33 +3510,15 @@
       <c r="I58" s="7"/>
       <c r="V58" s="12"/>
       <c r="W58" s="12"/>
-      <c r="X58" s="13">
-        <v>21</v>
-      </c>
-      <c r="Y58" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z58" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA58" s="12">
-        <v>14.71</v>
-      </c>
-      <c r="AB58" s="13">
-        <v>2.5968700000000001E-5</v>
-      </c>
-      <c r="AC58" s="11">
-        <v>167.4</v>
-      </c>
-      <c r="AD58" s="13">
-        <v>1.5428000000000001E-19</v>
-      </c>
-      <c r="AE58" s="11">
-        <v>1</v>
-      </c>
-      <c r="AF58" s="13">
-        <v>3.69</v>
-      </c>
+      <c r="X58" s="13"/>
+      <c r="Y58" s="12"/>
+      <c r="Z58" s="12"/>
+      <c r="AA58" s="12"/>
+      <c r="AB58" s="13"/>
+      <c r="AC58" s="11"/>
+      <c r="AD58" s="13"/>
+      <c r="AE58" s="11"/>
+      <c r="AF58" s="13"/>
     </row>
     <row r="59" spans="2:32">
       <c r="B59" s="2">
@@ -3951,33 +3543,15 @@
       <c r="I59" s="7"/>
       <c r="V59" s="12"/>
       <c r="W59" s="12"/>
-      <c r="X59" s="13">
-        <v>22</v>
-      </c>
-      <c r="Y59" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z59" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA59" s="12">
-        <v>24.8</v>
-      </c>
-      <c r="AB59" s="13">
-        <v>1.5403199999999998E-5</v>
-      </c>
-      <c r="AC59" s="12">
-        <v>73.900000000000006</v>
-      </c>
-      <c r="AD59" s="13">
-        <v>1.5583000000000001E-19</v>
-      </c>
-      <c r="AE59" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF59" s="13">
-        <v>2.72</v>
-      </c>
+      <c r="X59" s="13"/>
+      <c r="Y59" s="12"/>
+      <c r="Z59" s="12"/>
+      <c r="AA59" s="12"/>
+      <c r="AB59" s="13"/>
+      <c r="AC59" s="12"/>
+      <c r="AD59" s="13"/>
+      <c r="AE59" s="12"/>
+      <c r="AF59" s="13"/>
     </row>
     <row r="60" spans="2:32">
       <c r="B60" s="2">
@@ -4002,33 +3576,15 @@
       <c r="I60" s="7"/>
       <c r="V60" s="12"/>
       <c r="W60" s="12"/>
-      <c r="X60" s="13">
-        <v>23</v>
-      </c>
-      <c r="Y60" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z60" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA60" s="12">
-        <v>19.739999999999998</v>
-      </c>
-      <c r="AB60" s="13">
-        <v>1.93516E-5</v>
-      </c>
-      <c r="AC60" s="12">
-        <v>102.4</v>
-      </c>
-      <c r="AD60" s="13">
-        <v>1.6375E-19</v>
-      </c>
-      <c r="AE60" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF60" s="13">
-        <v>2.21</v>
-      </c>
+      <c r="X60" s="13"/>
+      <c r="Y60" s="12"/>
+      <c r="Z60" s="12"/>
+      <c r="AA60" s="12"/>
+      <c r="AB60" s="13"/>
+      <c r="AC60" s="12"/>
+      <c r="AD60" s="13"/>
+      <c r="AE60" s="12"/>
+      <c r="AF60" s="13"/>
     </row>
     <row r="61" spans="2:32">
       <c r="B61" s="2">
@@ -4053,33 +3609,15 @@
       <c r="I61" s="7"/>
       <c r="V61" s="12"/>
       <c r="W61" s="12"/>
-      <c r="X61" s="13">
-        <v>24</v>
-      </c>
-      <c r="Y61" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z61" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA61" s="12">
-        <v>11.06</v>
-      </c>
-      <c r="AB61" s="13">
-        <v>3.4538900000000002E-5</v>
-      </c>
-      <c r="AC61" s="12">
-        <v>124.4</v>
-      </c>
-      <c r="AD61" s="13">
-        <v>3.1350999999999999E-19</v>
-      </c>
-      <c r="AE61" s="12">
-        <v>2</v>
-      </c>
-      <c r="AF61" s="13">
-        <v>2.15</v>
-      </c>
+      <c r="X61" s="13"/>
+      <c r="Y61" s="12"/>
+      <c r="Z61" s="12"/>
+      <c r="AA61" s="12"/>
+      <c r="AB61" s="13"/>
+      <c r="AC61" s="12"/>
+      <c r="AD61" s="13"/>
+      <c r="AE61" s="12"/>
+      <c r="AF61" s="13"/>
     </row>
     <row r="62" spans="2:32">
       <c r="B62" s="2">
@@ -4104,33 +3642,15 @@
       <c r="I62" s="7"/>
       <c r="V62" s="12"/>
       <c r="W62" s="12"/>
-      <c r="X62" s="13">
-        <v>25</v>
-      </c>
-      <c r="Y62" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z62" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA62" s="12">
-        <v>17.2</v>
-      </c>
-      <c r="AB62" s="13">
-        <v>2.2209300000000001E-5</v>
-      </c>
-      <c r="AC62" s="11">
-        <v>125.6</v>
-      </c>
-      <c r="AD62" s="13">
-        <v>1.6420999999999999E-19</v>
-      </c>
-      <c r="AE62" s="11">
-        <v>1</v>
-      </c>
-      <c r="AF62" s="13">
-        <v>2.5</v>
-      </c>
+      <c r="X62" s="13"/>
+      <c r="Y62" s="12"/>
+      <c r="Z62" s="12"/>
+      <c r="AA62" s="12"/>
+      <c r="AB62" s="13"/>
+      <c r="AC62" s="11"/>
+      <c r="AD62" s="13"/>
+      <c r="AE62" s="11"/>
+      <c r="AF62" s="13"/>
     </row>
     <row r="63" spans="2:32">
       <c r="B63" s="2">
@@ -4155,33 +3675,15 @@
       <c r="I63" s="7"/>
       <c r="V63" s="12"/>
       <c r="W63" s="12"/>
-      <c r="X63" s="13">
-        <v>26</v>
-      </c>
-      <c r="Y63" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z63" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA63" s="12">
-        <v>5.45</v>
-      </c>
-      <c r="AB63" s="13">
-        <v>7.0091699999999998E-5</v>
-      </c>
-      <c r="AC63" s="12">
-        <v>141.19999999999999</v>
-      </c>
-      <c r="AD63" s="13">
-        <v>8.5275999999999998E-19</v>
-      </c>
-      <c r="AE63" s="12">
-        <v>5</v>
-      </c>
-      <c r="AF63" s="13">
-        <v>6.46</v>
-      </c>
+      <c r="X63" s="13"/>
+      <c r="Y63" s="12"/>
+      <c r="Z63" s="12"/>
+      <c r="AA63" s="12"/>
+      <c r="AB63" s="13"/>
+      <c r="AC63" s="12"/>
+      <c r="AD63" s="13"/>
+      <c r="AE63" s="12"/>
+      <c r="AF63" s="13"/>
     </row>
     <row r="64" spans="2:32">
       <c r="B64" s="2">
@@ -4206,33 +3708,15 @@
       <c r="I64" s="7"/>
       <c r="V64" s="12"/>
       <c r="W64" s="12"/>
-      <c r="X64" s="13">
-        <v>27</v>
-      </c>
-      <c r="Y64" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z64" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA64" s="12">
-        <v>24.13</v>
-      </c>
-      <c r="AB64" s="13">
-        <v>1.5830900000000001E-5</v>
-      </c>
-      <c r="AC64" s="12">
-        <v>41.1</v>
-      </c>
-      <c r="AD64" s="13">
-        <v>3.018E-19</v>
-      </c>
-      <c r="AE64" s="12">
-        <v>2</v>
-      </c>
-      <c r="AF64" s="13">
-        <v>5.8</v>
-      </c>
+      <c r="X64" s="13"/>
+      <c r="Y64" s="12"/>
+      <c r="Z64" s="12"/>
+      <c r="AA64" s="12"/>
+      <c r="AB64" s="13"/>
+      <c r="AC64" s="12"/>
+      <c r="AD64" s="13"/>
+      <c r="AE64" s="12"/>
+      <c r="AF64" s="13"/>
     </row>
     <row r="65" spans="2:32">
       <c r="B65" s="2">
@@ -4257,33 +3741,15 @@
       <c r="I65" s="7"/>
       <c r="V65" s="12"/>
       <c r="W65" s="12"/>
-      <c r="X65" s="13">
-        <v>28</v>
-      </c>
-      <c r="Y65" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z65" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA65" s="12">
-        <v>16.18</v>
-      </c>
-      <c r="AB65" s="13">
-        <v>2.3609400000000001E-5</v>
-      </c>
-      <c r="AC65" s="12">
-        <v>131.80000000000001</v>
-      </c>
-      <c r="AD65" s="13">
-        <v>1.6845000000000001E-19</v>
-      </c>
-      <c r="AE65" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF65" s="13">
-        <v>5.14</v>
-      </c>
+      <c r="X65" s="13"/>
+      <c r="Y65" s="12"/>
+      <c r="Z65" s="12"/>
+      <c r="AA65" s="12"/>
+      <c r="AB65" s="13"/>
+      <c r="AC65" s="12"/>
+      <c r="AD65" s="13"/>
+      <c r="AE65" s="12"/>
+      <c r="AF65" s="13"/>
     </row>
     <row r="66" spans="2:32">
       <c r="B66" s="2">
@@ -4308,33 +3774,15 @@
       <c r="I66" s="7"/>
       <c r="V66" s="12"/>
       <c r="W66" s="12"/>
-      <c r="X66" s="13">
-        <v>29</v>
-      </c>
-      <c r="Y66" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z66" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA66" s="12">
-        <v>22.61</v>
-      </c>
-      <c r="AB66" s="13">
-        <v>1.68952E-5</v>
-      </c>
-      <c r="AC66" s="11">
-        <v>86.8</v>
-      </c>
-      <c r="AD66" s="13">
-        <v>1.5543E-19</v>
-      </c>
-      <c r="AE66" s="11">
-        <v>1</v>
-      </c>
-      <c r="AF66" s="13">
-        <v>2.97</v>
-      </c>
+      <c r="X66" s="13"/>
+      <c r="Y66" s="12"/>
+      <c r="Z66" s="12"/>
+      <c r="AA66" s="12"/>
+      <c r="AB66" s="13"/>
+      <c r="AC66" s="11"/>
+      <c r="AD66" s="13"/>
+      <c r="AE66" s="11"/>
+      <c r="AF66" s="13"/>
     </row>
     <row r="67" spans="2:32">
       <c r="B67" s="2">
@@ -4359,33 +3807,15 @@
       <c r="I67" s="7"/>
       <c r="V67" s="12"/>
       <c r="W67" s="12"/>
-      <c r="X67" s="13">
-        <v>30</v>
-      </c>
-      <c r="Y67" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z67" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA67" s="12">
-        <v>17.649999999999999</v>
-      </c>
-      <c r="AB67" s="13">
-        <v>2.16431E-5</v>
-      </c>
-      <c r="AC67" s="12">
-        <v>61.4</v>
-      </c>
-      <c r="AD67" s="13">
-        <v>3.0999999999999999E-19</v>
-      </c>
-      <c r="AE67" s="12">
-        <v>2</v>
-      </c>
-      <c r="AF67" s="13">
-        <v>3.25</v>
-      </c>
+      <c r="X67" s="13"/>
+      <c r="Y67" s="12"/>
+      <c r="Z67" s="12"/>
+      <c r="AA67" s="12"/>
+      <c r="AB67" s="13"/>
+      <c r="AC67" s="12"/>
+      <c r="AD67" s="13"/>
+      <c r="AE67" s="12"/>
+      <c r="AF67" s="13"/>
     </row>
     <row r="68" spans="2:32">
       <c r="B68" s="2">
@@ -4410,33 +3840,15 @@
       <c r="I68" s="7"/>
       <c r="V68" s="12"/>
       <c r="W68" s="12"/>
-      <c r="X68" s="13">
-        <v>31</v>
-      </c>
-      <c r="Y68" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z68" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA68" s="12">
-        <v>14.73</v>
-      </c>
-      <c r="AB68" s="13">
-        <v>2.5933500000000002E-5</v>
-      </c>
-      <c r="AC68" s="12">
-        <v>156.4</v>
-      </c>
-      <c r="AD68" s="13">
-        <v>1.6483E-19</v>
-      </c>
-      <c r="AE68" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF68" s="13">
-        <v>2.88</v>
-      </c>
+      <c r="X68" s="13"/>
+      <c r="Y68" s="12"/>
+      <c r="Z68" s="12"/>
+      <c r="AA68" s="12"/>
+      <c r="AB68" s="13"/>
+      <c r="AC68" s="12"/>
+      <c r="AD68" s="13"/>
+      <c r="AE68" s="12"/>
+      <c r="AF68" s="13"/>
     </row>
     <row r="69" spans="2:32">
       <c r="B69" s="2">
@@ -4461,33 +3873,15 @@
       <c r="I69" s="7"/>
       <c r="V69" s="12"/>
       <c r="W69" s="12"/>
-      <c r="X69" s="13">
-        <v>32</v>
-      </c>
-      <c r="Y69" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z69" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA69" s="12">
-        <v>21.79</v>
-      </c>
-      <c r="AB69" s="13">
-        <v>1.7530999999999999E-5</v>
-      </c>
-      <c r="AC69" s="12">
-        <v>89.2</v>
-      </c>
-      <c r="AD69" s="13">
-        <v>1.5363000000000001E-19</v>
-      </c>
-      <c r="AE69" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF69" s="13">
-        <v>4.0999999999999996</v>
-      </c>
+      <c r="X69" s="13"/>
+      <c r="Y69" s="12"/>
+      <c r="Z69" s="12"/>
+      <c r="AA69" s="12"/>
+      <c r="AB69" s="13"/>
+      <c r="AC69" s="12"/>
+      <c r="AD69" s="13"/>
+      <c r="AE69" s="12"/>
+      <c r="AF69" s="13"/>
     </row>
     <row r="70" spans="2:32">
       <c r="B70" s="2">
@@ -4512,33 +3906,15 @@
       <c r="I70" s="7"/>
       <c r="V70" s="12"/>
       <c r="W70" s="12"/>
-      <c r="X70" s="13">
-        <v>33</v>
-      </c>
-      <c r="Y70" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z70" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA70" s="12">
-        <v>16.899999999999999</v>
-      </c>
-      <c r="AB70" s="13">
-        <v>2.2603600000000002E-5</v>
-      </c>
-      <c r="AC70" s="12">
-        <v>138.80000000000001</v>
-      </c>
-      <c r="AD70" s="13">
-        <v>1.5539E-19</v>
-      </c>
-      <c r="AE70" s="12">
-        <v>1</v>
-      </c>
-      <c r="AF70" s="13">
-        <v>3</v>
-      </c>
+      <c r="X70" s="13"/>
+      <c r="Y70" s="12"/>
+      <c r="Z70" s="12"/>
+      <c r="AA70" s="12"/>
+      <c r="AB70" s="13"/>
+      <c r="AC70" s="12"/>
+      <c r="AD70" s="13"/>
+      <c r="AE70" s="12"/>
+      <c r="AF70" s="13"/>
     </row>
     <row r="71" spans="2:32">
       <c r="B71" s="2">
@@ -4563,33 +3939,15 @@
       <c r="I71" s="7"/>
       <c r="V71" s="12"/>
       <c r="W71" s="12"/>
-      <c r="X71" s="13">
-        <v>34</v>
-      </c>
-      <c r="Y71" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z71" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA71" s="12">
-        <v>12.78</v>
-      </c>
-      <c r="AB71" s="13">
-        <v>2.9890500000000001E-5</v>
-      </c>
-      <c r="AC71" s="12">
-        <v>64.8</v>
-      </c>
-      <c r="AD71" s="13">
-        <v>4.9080000000000002E-19</v>
-      </c>
-      <c r="AE71" s="12">
-        <v>3</v>
-      </c>
-      <c r="AF71" s="13">
-        <v>2.12</v>
-      </c>
+      <c r="X71" s="13"/>
+      <c r="Y71" s="12"/>
+      <c r="Z71" s="12"/>
+      <c r="AA71" s="12"/>
+      <c r="AB71" s="13"/>
+      <c r="AC71" s="12"/>
+      <c r="AD71" s="13"/>
+      <c r="AE71" s="12"/>
+      <c r="AF71" s="13"/>
     </row>
     <row r="72" spans="2:32">
       <c r="B72" s="2">
@@ -4614,33 +3972,15 @@
       <c r="I72" s="7"/>
       <c r="V72" s="12"/>
       <c r="W72" s="12"/>
-      <c r="X72" s="13">
-        <v>35</v>
-      </c>
-      <c r="Y72" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z72" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA72" s="12">
-        <v>10.06</v>
-      </c>
-      <c r="AB72" s="13">
-        <v>3.7972200000000002E-5</v>
-      </c>
-      <c r="AC72" s="14">
-        <v>276.39999999999998</v>
-      </c>
-      <c r="AD72" s="15">
-        <v>1.6625000000000001E-19</v>
-      </c>
-      <c r="AE72" s="14">
-        <v>1</v>
-      </c>
-      <c r="AF72" s="15">
-        <v>3.77</v>
-      </c>
+      <c r="X72" s="13"/>
+      <c r="Y72" s="12"/>
+      <c r="Z72" s="12"/>
+      <c r="AA72" s="12"/>
+      <c r="AB72" s="13"/>
+      <c r="AC72" s="14"/>
+      <c r="AD72" s="15"/>
+      <c r="AE72" s="14"/>
+      <c r="AF72" s="15"/>
     </row>
     <row r="73" spans="2:32">
       <c r="B73" s="2">
@@ -4665,33 +4005,15 @@
       <c r="I73" s="7"/>
       <c r="V73" s="12"/>
       <c r="W73" s="12"/>
-      <c r="X73" s="13">
-        <v>36</v>
-      </c>
-      <c r="Y73" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z73" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA73" s="12">
-        <v>10.27</v>
-      </c>
-      <c r="AB73" s="13">
-        <v>3.71957E-5</v>
-      </c>
-      <c r="AC73" s="14">
-        <v>55.2</v>
-      </c>
-      <c r="AD73" s="15">
-        <v>8.2434999999999997E-19</v>
-      </c>
-      <c r="AE73" s="14">
-        <v>5</v>
-      </c>
-      <c r="AF73" s="15">
-        <v>2.91</v>
-      </c>
+      <c r="X73" s="13"/>
+      <c r="Y73" s="12"/>
+      <c r="Z73" s="12"/>
+      <c r="AA73" s="12"/>
+      <c r="AB73" s="13"/>
+      <c r="AC73" s="14"/>
+      <c r="AD73" s="15"/>
+      <c r="AE73" s="14"/>
+      <c r="AF73" s="15"/>
     </row>
     <row r="74" spans="2:32">
       <c r="B74" s="2">
@@ -4716,33 +4038,15 @@
       <c r="I74" s="7"/>
       <c r="V74" s="12"/>
       <c r="W74" s="12"/>
-      <c r="X74" s="13">
-        <v>37</v>
-      </c>
-      <c r="Y74" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z74" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA74" s="12">
-        <v>6.63</v>
-      </c>
-      <c r="AB74" s="13">
-        <v>5.7616900000000001E-5</v>
-      </c>
-      <c r="AC74" s="14">
-        <v>256.10000000000002</v>
-      </c>
-      <c r="AD74" s="15">
-        <v>3.3280000000000002E-19</v>
-      </c>
-      <c r="AE74" s="14">
-        <v>2</v>
-      </c>
-      <c r="AF74" s="15">
-        <v>3.87</v>
-      </c>
+      <c r="X74" s="13"/>
+      <c r="Y74" s="12"/>
+      <c r="Z74" s="12"/>
+      <c r="AA74" s="12"/>
+      <c r="AB74" s="13"/>
+      <c r="AC74" s="14"/>
+      <c r="AD74" s="15"/>
+      <c r="AE74" s="14"/>
+      <c r="AF74" s="15"/>
     </row>
     <row r="75" spans="2:32">
       <c r="B75" s="2">
@@ -4767,33 +4071,15 @@
       <c r="I75" s="7"/>
       <c r="V75" s="12"/>
       <c r="W75" s="12"/>
-      <c r="X75" s="13">
-        <v>38</v>
-      </c>
-      <c r="Y75" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z75" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA75" s="12">
-        <v>9.93</v>
-      </c>
-      <c r="AB75" s="13">
-        <v>3.8469300000000001E-5</v>
-      </c>
-      <c r="AC75" s="14">
-        <v>270.2</v>
-      </c>
-      <c r="AD75" s="15">
-        <v>1.6853E-19</v>
-      </c>
-      <c r="AE75" s="14">
-        <v>1</v>
-      </c>
-      <c r="AF75" s="15">
-        <v>5.19</v>
-      </c>
+      <c r="X75" s="13"/>
+      <c r="Y75" s="12"/>
+      <c r="Z75" s="12"/>
+      <c r="AA75" s="12"/>
+      <c r="AB75" s="13"/>
+      <c r="AC75" s="14"/>
+      <c r="AD75" s="15"/>
+      <c r="AE75" s="14"/>
+      <c r="AF75" s="15"/>
     </row>
     <row r="76" spans="2:32">
       <c r="B76" s="2">
@@ -4818,33 +4104,15 @@
       <c r="I76" s="7"/>
       <c r="V76" s="12"/>
       <c r="W76" s="12"/>
-      <c r="X76" s="13">
-        <v>39</v>
-      </c>
-      <c r="Y76" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z76" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA76" s="12">
-        <v>18.13</v>
-      </c>
-      <c r="AB76" s="13">
-        <v>2.107E-5</v>
-      </c>
-      <c r="AC76" s="14">
-        <v>58.7</v>
-      </c>
-      <c r="AD76" s="15">
-        <v>3.1245000000000002E-19</v>
-      </c>
-      <c r="AE76" s="14">
-        <v>2</v>
-      </c>
-      <c r="AF76" s="15">
-        <v>2.46</v>
-      </c>
+      <c r="X76" s="13"/>
+      <c r="Y76" s="12"/>
+      <c r="Z76" s="12"/>
+      <c r="AA76" s="12"/>
+      <c r="AB76" s="13"/>
+      <c r="AC76" s="14"/>
+      <c r="AD76" s="15"/>
+      <c r="AE76" s="14"/>
+      <c r="AF76" s="15"/>
     </row>
     <row r="77" spans="2:32">
       <c r="B77" s="2">
@@ -4869,33 +4137,15 @@
       <c r="I77" s="7"/>
       <c r="V77" s="12"/>
       <c r="W77" s="12"/>
-      <c r="X77" s="13">
-        <v>40</v>
-      </c>
-      <c r="Y77" s="12">
-        <v>1</v>
-      </c>
-      <c r="Z77" s="12">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA77" s="12">
-        <v>23.57</v>
-      </c>
-      <c r="AB77" s="13">
-        <v>1.6206999999999999E-5</v>
-      </c>
-      <c r="AC77" s="14">
-        <v>80.599999999999994</v>
-      </c>
-      <c r="AD77" s="15">
-        <v>1.5583000000000001E-19</v>
-      </c>
-      <c r="AE77" s="14">
-        <v>1</v>
-      </c>
-      <c r="AF77" s="14">
-        <v>2.72</v>
-      </c>
+      <c r="X77" s="13"/>
+      <c r="Y77" s="12"/>
+      <c r="Z77" s="12"/>
+      <c r="AA77" s="12"/>
+      <c r="AB77" s="13"/>
+      <c r="AC77" s="14"/>
+      <c r="AD77" s="15"/>
+      <c r="AE77" s="14"/>
+      <c r="AF77" s="14"/>
     </row>
     <row r="78" spans="2:32">
       <c r="B78" s="2">
@@ -4918,33 +4168,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I78" s="7"/>
-      <c r="X78">
-        <v>41</v>
-      </c>
-      <c r="Y78">
-        <v>1</v>
-      </c>
-      <c r="Z78">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA78">
-        <v>14.91</v>
-      </c>
-      <c r="AB78" s="10">
-        <v>2.56204E-5</v>
-      </c>
-      <c r="AC78">
-        <v>81.3</v>
-      </c>
-      <c r="AD78" s="10">
-        <v>3.1053999999999998E-19</v>
-      </c>
-      <c r="AE78">
-        <v>2</v>
-      </c>
-      <c r="AF78">
-        <v>3.08</v>
-      </c>
+      <c r="AB78" s="10"/>
+      <c r="AD78" s="10"/>
     </row>
     <row r="79" spans="2:32">
       <c r="B79" s="2">
@@ -4967,33 +4192,8 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I79" s="7"/>
-      <c r="X79">
-        <v>42</v>
-      </c>
-      <c r="Y79">
-        <v>1</v>
-      </c>
-      <c r="Z79">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA79">
-        <v>7.26</v>
-      </c>
-      <c r="AB79" s="10">
-        <v>5.2617100000000001E-5</v>
-      </c>
-      <c r="AC79">
-        <v>230.7</v>
-      </c>
-      <c r="AD79" s="10">
-        <v>3.278E-19</v>
-      </c>
-      <c r="AE79">
-        <v>2</v>
-      </c>
-      <c r="AF79">
-        <v>2.31</v>
-      </c>
+      <c r="AB79" s="10"/>
+      <c r="AD79" s="10"/>
     </row>
     <row r="80" spans="2:32">
       <c r="B80" s="2">
@@ -5016,35 +4216,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I80" s="7"/>
-      <c r="X80">
-        <v>43</v>
-      </c>
-      <c r="Y80">
-        <v>1</v>
-      </c>
-      <c r="Z80">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA80">
-        <v>15.32</v>
-      </c>
-      <c r="AB80" s="10">
-        <v>2.49347E-5</v>
-      </c>
-      <c r="AC80">
-        <v>75.8</v>
-      </c>
-      <c r="AD80" s="10">
-        <v>3.1090000000000002E-19</v>
-      </c>
-      <c r="AE80">
-        <v>2</v>
-      </c>
-      <c r="AF80">
-        <v>2.93</v>
-      </c>
-    </row>
-    <row r="81" spans="2:32">
+      <c r="AB80" s="10"/>
+      <c r="AD80" s="10"/>
+    </row>
+    <row r="81" spans="2:30">
       <c r="B81" s="2">
         <v>79</v>
       </c>
@@ -5065,35 +4240,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I81" s="7"/>
-      <c r="X81">
-        <v>44</v>
-      </c>
-      <c r="Y81">
-        <v>1</v>
-      </c>
-      <c r="Z81">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA81">
-        <v>10.75</v>
-      </c>
-      <c r="AB81" s="10">
-        <v>3.5534899999999998E-5</v>
-      </c>
-      <c r="AC81">
-        <v>49.5</v>
-      </c>
-      <c r="AD81" s="10">
-        <v>8.3390000000000005E-19</v>
-      </c>
-      <c r="AE81">
-        <v>5</v>
-      </c>
-      <c r="AF81">
-        <v>4.12</v>
-      </c>
-    </row>
-    <row r="82" spans="2:32">
+      <c r="AB81" s="10"/>
+      <c r="AD81" s="10"/>
+    </row>
+    <row r="82" spans="2:30">
       <c r="B82" s="2">
         <v>80</v>
       </c>
@@ -5114,35 +4264,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I82" s="7"/>
-      <c r="X82">
-        <v>45</v>
-      </c>
-      <c r="Y82">
-        <v>1</v>
-      </c>
-      <c r="Z82">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA82">
-        <v>16.170000000000002</v>
-      </c>
-      <c r="AB82" s="10">
-        <v>2.3623999999999999E-5</v>
-      </c>
-      <c r="AC82">
-        <v>137.9</v>
-      </c>
-      <c r="AD82" s="10">
-        <v>1.6425000000000001E-19</v>
-      </c>
-      <c r="AE82">
-        <v>1</v>
-      </c>
-      <c r="AF82">
-        <v>2.52</v>
-      </c>
-    </row>
-    <row r="83" spans="2:32">
+      <c r="AB82" s="10"/>
+      <c r="AD82" s="10"/>
+    </row>
+    <row r="83" spans="2:30">
       <c r="B83" s="2">
         <v>81</v>
       </c>
@@ -5163,35 +4288,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I83" s="7"/>
-      <c r="X83">
-        <v>46</v>
-      </c>
-      <c r="Y83">
-        <v>1</v>
-      </c>
-      <c r="Z83">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA83">
-        <v>6.35</v>
-      </c>
-      <c r="AB83" s="10">
-        <v>6.0157500000000001E-5</v>
-      </c>
-      <c r="AC83">
-        <v>262.39999999999998</v>
-      </c>
-      <c r="AD83" s="10">
-        <v>3.321E-19</v>
-      </c>
-      <c r="AE83">
-        <v>2</v>
-      </c>
-      <c r="AF83">
-        <v>3.65</v>
-      </c>
-    </row>
-    <row r="84" spans="2:32">
+      <c r="AB83" s="10"/>
+      <c r="AD83" s="10"/>
+    </row>
+    <row r="84" spans="2:30">
       <c r="B84" s="2">
         <v>82</v>
       </c>
@@ -5212,35 +4312,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I84" s="7"/>
-      <c r="X84">
-        <v>47</v>
-      </c>
-      <c r="Y84">
-        <v>1</v>
-      </c>
-      <c r="Z84">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA84">
-        <v>11.1</v>
-      </c>
-      <c r="AB84" s="10">
-        <v>3.44144E-5</v>
-      </c>
-      <c r="AC84">
-        <v>63.3</v>
-      </c>
-      <c r="AD84" s="10">
-        <v>6.1550000000000002E-19</v>
-      </c>
-      <c r="AE84">
-        <v>4</v>
-      </c>
-      <c r="AF84">
-        <v>3.94</v>
-      </c>
-    </row>
-    <row r="85" spans="2:32">
+      <c r="AB84" s="10"/>
+      <c r="AD84" s="10"/>
+    </row>
+    <row r="85" spans="2:30">
       <c r="B85" s="2">
         <v>83</v>
       </c>
@@ -5261,35 +4336,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I85" s="7"/>
-      <c r="X85">
-        <v>48</v>
-      </c>
-      <c r="Y85">
-        <v>1</v>
-      </c>
-      <c r="Z85">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA85">
-        <v>17.78</v>
-      </c>
-      <c r="AB85" s="10">
-        <v>2.1484800000000001E-5</v>
-      </c>
-      <c r="AC85">
-        <v>43.5</v>
-      </c>
-      <c r="AD85" s="10">
-        <v>4.4980000000000001E-19</v>
-      </c>
-      <c r="AE85">
-        <v>3</v>
-      </c>
-      <c r="AF85">
-        <v>6.41</v>
-      </c>
-    </row>
-    <row r="86" spans="2:32">
+      <c r="AB85" s="10"/>
+      <c r="AD85" s="10"/>
+    </row>
+    <row r="86" spans="2:30">
       <c r="B86" s="2">
         <v>84</v>
       </c>
@@ -5310,35 +4360,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I86" s="7"/>
-      <c r="X86">
-        <v>49</v>
-      </c>
-      <c r="Y86">
-        <v>1</v>
-      </c>
-      <c r="Z86">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA86">
-        <v>11.82</v>
-      </c>
-      <c r="AB86" s="10">
-        <v>3.2318099999999998E-5</v>
-      </c>
-      <c r="AC86">
-        <v>43.1</v>
-      </c>
-      <c r="AD86" s="10">
-        <v>8.3580000000000001E-19</v>
-      </c>
-      <c r="AE86">
-        <v>5</v>
-      </c>
-      <c r="AF86">
-        <v>4.34</v>
-      </c>
-    </row>
-    <row r="87" spans="2:32">
+      <c r="AB86" s="10"/>
+      <c r="AD86" s="10"/>
+    </row>
+    <row r="87" spans="2:30">
       <c r="B87" s="2">
         <v>85</v>
       </c>
@@ -5359,35 +4384,10 @@
         <v>#DIV/0!</v>
       </c>
       <c r="I87" s="7"/>
-      <c r="X87">
-        <v>50</v>
-      </c>
-      <c r="Y87">
-        <v>1</v>
-      </c>
-      <c r="Z87">
-        <v>3.8200000000000002E-4</v>
-      </c>
-      <c r="AA87">
-        <v>18.440000000000001</v>
-      </c>
-      <c r="AB87" s="10">
-        <v>2.0715799999999999E-5</v>
-      </c>
-      <c r="AC87">
-        <v>53</v>
-      </c>
-      <c r="AD87" s="10">
-        <v>3.3449999999999998E-19</v>
-      </c>
-      <c r="AE87">
-        <v>2</v>
-      </c>
-      <c r="AF87">
-        <v>4.4000000000000004</v>
-      </c>
-    </row>
-    <row r="88" spans="2:32">
+      <c r="AB87" s="10"/>
+      <c r="AD87" s="10"/>
+    </row>
+    <row r="88" spans="2:30">
       <c r="B88" s="2">
         <v>86</v>
       </c>
@@ -5409,7 +4409,7 @@
       </c>
       <c r="I88" s="7"/>
     </row>
-    <row r="89" spans="2:32">
+    <row r="89" spans="2:30">
       <c r="B89" s="2">
         <v>87</v>
       </c>
@@ -5431,7 +4431,7 @@
       </c>
       <c r="I89" s="7"/>
     </row>
-    <row r="90" spans="2:32">
+    <row r="90" spans="2:30">
       <c r="B90" s="2">
         <v>88</v>
       </c>
@@ -5453,7 +4453,7 @@
       </c>
       <c r="I90" s="7"/>
     </row>
-    <row r="91" spans="2:32">
+    <row r="91" spans="2:30">
       <c r="B91" s="2">
         <v>89</v>
       </c>
@@ -5475,7 +4475,7 @@
       </c>
       <c r="I91" s="7"/>
     </row>
-    <row r="92" spans="2:32">
+    <row r="92" spans="2:30">
       <c r="B92" s="2">
         <v>90</v>
       </c>
@@ -5497,7 +4497,7 @@
       </c>
       <c r="I92" s="7"/>
     </row>
-    <row r="93" spans="2:32">
+    <row r="93" spans="2:30">
       <c r="B93" s="2">
         <v>91</v>
       </c>
@@ -5519,7 +4519,7 @@
       </c>
       <c r="I93" s="7"/>
     </row>
-    <row r="94" spans="2:32">
+    <row r="94" spans="2:30">
       <c r="B94" s="2">
         <v>92</v>
       </c>
@@ -5541,7 +4541,7 @@
       </c>
       <c r="I94" s="7"/>
     </row>
-    <row r="95" spans="2:32">
+    <row r="95" spans="2:30">
       <c r="B95" s="2">
         <v>93</v>
       </c>
@@ -5563,7 +4563,7 @@
       </c>
       <c r="I95" s="7"/>
     </row>
-    <row r="96" spans="2:32">
+    <row r="96" spans="2:30">
       <c r="B96" s="2">
         <v>94</v>
       </c>
